--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:J70" headerRowCount="1">
-  <autoFilter ref="A1:J70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:J73" headerRowCount="1">
+  <autoFilter ref="A1:J73"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>A-Living (Areeiro) (Planeamento)</t>
+          <t>A-Living (Areeiro) (Planeamento) | Parque da Cidade (Setúbal) (Em construção)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Sharp Developers</t>
+          <t>Royal Ventures</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2258,17 +2258,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>+351 933 078 094</t>
+          <t>+351 916 770 322</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>info@sharpdevelopers.pt</t>
+          <t>alex@royal-ventures.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sharpdevelopers.pt</t>
+          <t>royal-ventures.com</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2283,24 +2283,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
+          <t>Edifício Oceanus, Av. da Boavista 3227, 4100-137</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Residencial de luxo Porto (Em construção)</t>
+          <t>Reabilitação centro histórico do Porto (Em construção)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>CEO Carla Luís</t>
+          <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SILCOGE / Grupo SIL</t>
+          <t>Sharp Developers</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2310,49 +2310,49 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>+351 210 124 500</t>
+          <t>+351 933 078 094</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>info@sil.pt</t>
+          <t>info@sharpdevelopers.pt</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sil.pt</t>
+          <t>sharpdevelopers.pt</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
+          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Grande Lisboa (Em construção)</t>
+          <t>Residencial de luxo Porto (Em construção)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Promoção imobiliária desde 1949</t>
+          <t>CEO Carla Luís</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SOLYD Property Developers</t>
+          <t>SILCOGE / Grupo SIL</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>+351 211 214 926</t>
+          <t>+351 210 124 500</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>info@elou-solyd.pt</t>
+          <t>info@sil.pt</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>solyd.pt</t>
+          <t>sil.pt</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2387,24 +2387,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
+          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Luz Altear (Alta de Lisboa) (Em construção)</t>
+          <t>Grande Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
+          <t>Promoção imobiliária desde 1949</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Stone Capital</t>
+          <t>SOLYD Property Developers</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2414,22 +2414,22 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>+351 210 416 350</t>
+          <t>+351 211 214 926</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>info@stonecapital.pt</t>
+          <t>info@elou-solyd.pt</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>stonecapital.pt</t>
+          <t>solyd.pt</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2439,24 +2439,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 240, 1250-096</t>
+          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
+          <t>Luz Altear (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Tel. móvel 965 915 993</t>
+          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Teixeira Duarte Real Estate</t>
+          <t>Stone Capital</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>+351 217 912 300</t>
+          <t>+351 210 416 350</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>info@tdimobiliaria.pt</t>
+          <t>info@stonecapital.pt</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>tdimobiliaria.pt</t>
+          <t>stonecapital.pt</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
+          <t>Av. da Liberdade 240, 1250-096</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
+          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do grupo Teixeira Duarte</t>
+          <t>Tel. móvel 965 915 993</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Thomas &amp; Piron Portugal</t>
+          <t>Teixeira Duarte Real Estate</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2518,49 +2518,49 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>+351 214 422 464</t>
+          <t>+351 217 912 300</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>infopt@thomas-piron.eu</t>
+          <t>info@tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>thomas-piron.pt</t>
+          <t>tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Escritórios em Matosinhos e Sacavém</t>
+          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
+          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
+          <t>Braço imobiliário do grupo Teixeira Duarte</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Properties</t>
+          <t>Thomas &amp; Piron Portugal</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2570,49 +2570,49 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>+351 215 814 094</t>
+          <t>+351 214 422 464</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>info@vangproperties.com</t>
+          <t>infopt@thomas-piron.eu</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>vangproperties.com</t>
+          <t>thomas-piron.pt</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
+          <t>Escritórios em Matosinhos e Sacavém</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
+          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
+          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>VIC Properties</t>
+          <t>Vanguard Properties</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>+351 219 347 112</t>
+          <t>+351 215 814 094</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>info@vic-properties.com</t>
+          <t>info@vangproperties.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>vic-properties.com</t>
+          <t>vangproperties.com</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2647,120 +2647,128 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Portefólio &gt;3B€. Fundada 2018</t>
+          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>VIC Properties</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>+351 219 347 112</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>info@vic-properties.com</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>vic-properties.com</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Portefólio &gt;3B€. Fundada 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>Vogue Homes</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>+351 213 461 246</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>comercial@vogue-homes.com</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>vogue-homes.com</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Rua Luz Soriano 15, 1200-246</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Dafundo 24 (Comercialização) | Bom Sucesso (Comercialização) | Westhouse (Cascais) (Comercialização)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>NIF 510933084. Tel. móvel 913 385 846</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Alecrim Real Estate (Lince Capital)</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>lince-capital.com</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Fortera</t>
+          <t>Alecrim Real Estate (Lince Capital)</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2770,37 +2778,41 @@
       </c>
       <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>lince-capital.com</t>
+        </is>
+      </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Porto / Gaia</t>
+          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
+          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
+          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Fortera</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2810,41 +2822,37 @@
       </c>
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>hines.com</t>
-        </is>
-      </c>
+      <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto / Gaia</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
+          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Gestora global · sem contacto PT publicado</t>
+          <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2856,35 +2864,39 @@
       <c r="D47" s="5" t="inlineStr"/>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>imolote.pt</t>
+          <t>hines.com</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
+          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
+          <t>Gestora global · sem contacto PT publicado</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Overseas</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2894,37 +2906,37 @@
       </c>
       <c r="C48" s="7" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
+          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Overseas</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2947,24 +2959,24 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
+          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/site publicados (APPII)</t>
+          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>Prime Portugal</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2974,11 +2986,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr"/>
       <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>roundhillcapital.com</t>
-        </is>
-      </c>
+      <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -2991,24 +2999,24 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Rua da Escola Politécnica 38, 1250-102</t>
+          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone PT publicado</t>
+          <t>Sem telefone/site publicados (APPII)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>United Investments Portugal (UIP)</t>
+          <t>Round Hill Capital</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3020,7 +3028,7 @@
       <c r="D51" s="5" t="inlineStr"/>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>uip.pt</t>
+          <t>roundhillcapital.com</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -3035,24 +3043,24 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Rua da Escola Politécnica 38, 1250-102</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Fundada 1985 · sem telefone publicado</t>
+          <t>Sem telefone PT publicado</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Screendomus (Grupo Teixeira)</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -3063,12 +3071,12 @@
       <c r="C52" s="7" t="inlineStr"/>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>privacidade@vizta.pt</t>
+          <t>geral@screendomus.com</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>screendomus.com</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -3081,174 +3089,158 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+      <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Altus (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
+          <t>United Investments Portugal (UIP)</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>uip.pt</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Fundada 1985 · sem telefone publicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>VIZTA (ex-Nexity Portugal)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>Âncora Investments</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>info@ancora-inv.com</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>ancora-inv.com</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Antrix</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>info@antrix.pt</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>antrix.pt</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3258,22 +3250,22 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
+          <t>900 264 096 (ES)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>info@carvoeirobranco.com</t>
+          <t>info@aedashomes.com</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3283,24 +3275,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3310,49 +3302,49 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>casais@casais.pt</t>
+          <t>info@antrix.pt</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -3362,49 +3354,49 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3414,49 +3406,49 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 305 490</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -3466,45 +3458,49 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>+351 253 461 462</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>geral@castro-group.pt</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3514,49 +3510,49 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
+          <t>+351 234 480 570</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>geral@garcia.pt</t>
+          <t>info@civilria.pt</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -3566,49 +3562,45 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>aca@grupo-aca.com</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3618,49 +3610,49 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -3670,49 +3662,49 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -3722,45 +3714,49 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>+351 253 685 109</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>acrescentar@grupoacrescentar.pt</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3770,17 +3766,17 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 253 105 331</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>info@pinehill.pt</t>
+          <t>geral@arliz.co</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3793,22 +3789,26 @@
           <t>Braga</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
+        </is>
+      </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3818,168 +3818,316 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>info@quintadolago.com</t>
-        </is>
-      </c>
+          <t>273 332 784 (confirmar)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Almancil</t>
+          <t>Parque Empresarial A32, Vila Maior</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>JHOMEA Invest</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>+351 934 175 642</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>jhomea.pt</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Vacivus (Porto) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Pine Hill</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>+351 910 936 732</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>info@pinehill.pt</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>pinehill.pt</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Quinta do Lago Resort</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>+351 289 390 700</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>quintadolago.com</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Resort residencial/golfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>+351 255 433 572</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>geral@tps.com.pt</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>tps.com.pt</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>Amarante</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr"/>
-      <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>andreguimaraes.com.br</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr"/>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr"/>
-      <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>ombria.com</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>Loulé</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>Loulé</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
@@ -4025,7 +4173,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -4035,7 +4183,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -4045,7 +4193,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -4055,7 +4203,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,9 +191,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:J73" headerRowCount="1">
-  <autoFilter ref="A1:J73"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M73" headerRowCount="1">
+  <autoFilter ref="A1:M73"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
     <tableColumn id="3" name="Telefone"/>
@@ -204,6 +204,9 @@
     <tableColumn id="8" name="Morada Completa"/>
     <tableColumn id="9" name="Empreendimentos Ativos"/>
     <tableColumn id="10" name="Notas"/>
+    <tableColumn id="11" name="CEO"/>
+    <tableColumn id="12" name="LinkedIn CEO"/>
+    <tableColumn id="13" name="Instagram CEO"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -498,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -511,6 +514,9 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -564,6 +570,21 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn CEO</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Instagram CEO</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -616,6 +637,9 @@
           <t>Private equity com foco imobiliário. Fonte: APPII</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -668,6 +692,17 @@
           <t>Fundada 2022, ligada à Panhard. Tel. móvel 914 192 506</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Morgado (Diretor Executivo)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cafmorgado/</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -720,6 +755,17 @@
           <t>Telefone é da linha comercial Quinta do Alverde</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Alejandro Martins (Founder &amp; CEO)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alejandro-martins-74b18590/</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -772,6 +818,17 @@
           <t>Promotor de referência Lisboa/Porto</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Aniceto Viegas (CEO)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/aniceto-viegas-02586a1</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -820,6 +877,13 @@
           <t>Só telefone UK publicado</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Fredrick J. Benoit II (Director/co-fundador, 50% com Matthew Lavin)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -872,6 +936,17 @@
           <t>Promotor pan-europeu (grupo BESIX)</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Nicolas Goffin (Country Director Portugal· CEO do grupo é Gabriel Uzgen, Bruxelas)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicolas-goffin-32707487/</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -924,6 +999,17 @@
           <t>Desde 2015, sócios com &gt;500M€ promovidos</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Celma de Almeida Lavradio (Co-Founder &amp; CEO)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/celma-de-almeida-lavradio-645baa43</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -972,6 +1058,17 @@
           <t>Gestora regulada CMVM, capital internacional</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Paulo Loureiro (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulo-loureiro-8a46016/</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1024,6 +1121,13 @@
           <t>Promotor de Lisboa desde 2004</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Ferreira (fundador e CEO, homónimos sem confirmação total)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1076,6 +1180,13 @@
           <t>20 anos em Príncipe Real, &gt;20 edifícios</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Tiago Eiró (CEO)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1128,6 +1239,17 @@
           <t>Promotora do grupo Mota-Engil</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Vitor Paulo Pinho (CEO)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vitor-paulo-pinho-0a7952173/</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1176,6 +1298,13 @@
           <t>Luxo desde 1981. Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Mário Almeida (Administrador)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1228,6 +1357,9 @@
           <t>Braço imobiliário da Fidelidade. Projeto: info@entrecampos.pt</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1276,6 +1408,9 @@
           <t>Projeto concreto não nomeado nas fontes</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1328,6 +1463,13 @@
           <t>Presidente António Parente. Tel. móvel 914 070 350</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Dias (Diretor Geral da Madre Imobiliário· presidente do grupo é António Parente)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1380,6 +1522,13 @@
           <t>Fundada 2001 · inclui Habitat Ventures/Project/Property/Broker</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Luís Corrêa de Barros (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1432,6 +1581,9 @@
           <t>Fundada 1960, alvará ICC 12463. Tel. móvel 961 682 789</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1484,6 +1636,17 @@
           <t>Promotora com construtora e imobiliária próprias</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>João Sousa (CEO)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/joao-sousa-7802352a</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1536,6 +1699,17 @@
           <t>Belga, em Portugal desde 2014</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Claude Kandiyoti (CEO)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claude-kandiyoti-287b9298/</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -1584,6 +1758,17 @@
           <t>Entidade KIG Portugal (NIF 514667265)</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Rui Meneses Ferreira (CEO)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rui-meneses-ferreira-97057825/</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1636,6 +1821,13 @@
           <t>Constituída em Macau 2015</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Eduardo Kol Netto de Almeida (CEO)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -1688,6 +1880,13 @@
           <t>18 projetos no Algarve, &gt;800 unidades entregues · ISO 14001</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>António Gonçalves (Fundador)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1740,6 +1939,17 @@
           <t>&gt;100M€ anunciados 2026. Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Costa (CEO, confiança baixa — só rocketreach)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/gabriel-costa-7436b5158</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1792,6 +2002,13 @@
           <t>Capital social 5M€. Fonte: idealista/news ago/2026</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Teixeira Paredes (CEO)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1844,6 +2061,17 @@
           <t>Grupo suíço, 250M€ em Portugal, 71.000 m²</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Suter (Founding Member/Partner, Suíça)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-suter-78564b9/</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -1892,6 +2120,17 @@
           <t>Gestora de investimento (2,1B€) que também promove</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Mateus (CEO, recém-nomeado)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-mateus-608b616/</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1944,6 +2183,17 @@
           <t>Promotor desde 1986</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Sanches (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/pedro-sanches-77205825</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -1996,6 +2246,17 @@
           <t>1,7B€ investidos · PT e Turquia</t>
         </is>
       </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>William Tonnard (President &amp; COO· Chairman é Hakan Kodal)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-tonnard/</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2040,6 +2301,9 @@
           <t>Telefone do registo comercial (einforma). Comercialização JLL/Predibisa</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -2092,6 +2356,17 @@
           <t>Com Tikehau Capital. &gt;1B€ sob gestão</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Vasconcellos (Founding Partner, CEO exato não confirmado)</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vasconcelloscarlos/</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2144,6 +2419,17 @@
           <t>NIF 516390350, capital 800k€. Fonte: construir.pt abr/2026</t>
         </is>
       </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Gonçalves Pereira (CEO)</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hugogpereira/</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -2196,6 +2482,9 @@
           <t>Grupo nascido em Monção, liderado por Nuno Afonso. Fonte: idealista/news jun/2026, Público</t>
         </is>
       </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2244,6 +2533,17 @@
           <t>ATENÇÃO: é gestor de projeto/serviços, não promotor puro</t>
         </is>
       </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>José Pedro Almeida Guerra (Diretor Geral)</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/josé-pedro-almeida-guerra-20723679</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -2296,6 +2596,17 @@
           <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Udi Yadin (fundador/General Partner)</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/udiyadin/</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2348,6 +2659,17 @@
           <t>CEO Carla Luís</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Carla Luís (CEO/cofundadora)</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carla-luís-b14a7616/</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -2400,6 +2722,17 @@
           <t>Promoção imobiliária desde 1949</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Silveira (acionista maioritário/ex-Chairman, destituído judicialmente mai/2025, em recurso)</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-silveira-88822a20/</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -2452,6 +2785,17 @@
           <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Gonçalo Cadete (CEO)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gon%C3%A7alo-cadete-260692/</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -2504,6 +2848,13 @@
           <t>Tel. móvel 965 915 993</t>
         </is>
       </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Geoffroy Moreno (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2556,6 +2907,9 @@
           <t>Braço imobiliário do grupo Teixeira Duarte</t>
         </is>
       </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -2608,6 +2962,17 @@
           <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>David Carreira (Diretor Geral/Country Manager)</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>https://lu.linkedin.com/in/david-carreira-a4082050</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2660,6 +3025,17 @@
           <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
         </is>
       </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Henrique Rodrigues da Silva (CEO desde fev/2026)</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henrique-rodrigues-da-silva-b396643/</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -2712,6 +3088,17 @@
           <t>Portefólio &gt;3B€. Fundada 2018</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>João Cabaça (Co-fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/jo%C3%A3o-caba%C3%A7a-6b293614b</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2764,6 +3151,17 @@
           <t>NIF 510933084. Tel. móvel 913 385 846</t>
         </is>
       </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Joaquim Lico (CEO)</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joaquim-lico-4383239/</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -2808,6 +3206,17 @@
           <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
         </is>
       </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -2848,6 +3257,13 @@
           <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
         </is>
       </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -2892,6 +3308,13 @@
           <t>Gestora global · sem contacto PT publicado</t>
         </is>
       </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2932,6 +3355,13 @@
           <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
         </is>
       </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -2972,6 +3402,17 @@
           <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
         </is>
       </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Pedro Vicente (CEO)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -3012,6 +3453,13 @@
           <t>Sem telefone/site publicados (APPII)</t>
         </is>
       </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Federico Rosales (cofundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -3056,6 +3504,13 @@
           <t>Sem telefone PT publicado</t>
         </is>
       </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -3100,6 +3555,13 @@
           <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
         </is>
       </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -3144,6 +3606,17 @@
           <t>Fundada 1985 · sem telefone publicado</t>
         </is>
       </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Leal (CEO)</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -3192,6 +3665,17 @@
           <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
         </is>
       </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -3236,6 +3720,17 @@
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tamir-luria/</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -3288,6 +3783,17 @@
           <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -3340,6 +3846,17 @@
           <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -3392,6 +3909,17 @@
           <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Erik de Vlieger (CEO)</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -3444,6 +3972,13 @@
           <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -3496,6 +4031,17 @@
           <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Paulo Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -3548,6 +4094,17 @@
           <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
         </is>
       </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -3596,6 +4153,17 @@
           <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Reinaldo Teixeira (Administrador)</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -3648,6 +4216,13 @@
           <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -3700,6 +4275,17 @@
           <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -3752,6 +4338,13 @@
           <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -3804,6 +4397,17 @@
           <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
         </is>
       </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -3852,6 +4456,13 @@
           <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -3904,6 +4515,13 @@
           <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>José Miguel Afonso (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -3952,6 +4570,17 @@
           <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
         </is>
       </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Pinheiro (fundador)</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -4004,6 +4633,17 @@
           <t>Resort residencial/golfe</t>
         </is>
       </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -4056,6 +4696,13 @@
           <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -4088,6 +4735,13 @@
           <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -4132,6 +4786,17 @@
           <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
       </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4147,7 +4812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4207,18 +4872,50 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="n"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Com nome de CEO/administrador identificado</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
+          <t>Com LinkedIn pessoal do CEO confirmado</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Linhas com fundo laranja claro na folha 'Promotoras' não têm telefone confirmado — use o email, o site ou o LinkedIn indicado nas Notas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Nota CEO/LinkedIn/Instagram</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Nenhum handle de Instagram pessoal foi encontrado com confiança para nenhum CEO — por isso a coluna vem vazia em todas as linhas (não foi inventado nenhum perfil). Alguns nomes de CEO/LinkedIn têm confiança moderada — ver texto entre parênteses na coluna CEO.</t>
         </is>
       </c>
     </row>

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M73" headerRowCount="1">
-  <autoFilter ref="A1:M73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M148" headerRowCount="1">
+  <autoFilter ref="A1:M148"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15 projetos em desenvolvimento (Em construção)</t>
+          <t>15 projetos em desenvolvimento (Em construção) | ALMAR SOUTH LIVING (Almada) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Optylon Krea</t>
+          <t>Névoa, S.A.</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2208,17 +2208,13 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>+351 212 400 124</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>sales@optylonkrea.com</t>
-        </is>
-      </c>
+          <t>+351 253 240 010</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>optylonkrea.com</t>
+          <t>nevoa.pt</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2231,37 +2227,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 50, 10º/11º, 1250-096</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Ando Living – Alfama Club e Liberdade Club (Em construção) | Augusta Townhouse + Santos Townhouse (Comercialização)</t>
+          <t>Portfólio nacional de empreendimentos (Comercialização)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,7B€ investidos · PT e Turquia</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>William Tonnard (President &amp; COO· Chairman é Hakan Kodal)</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/william-tonnard/</t>
-        </is>
-      </c>
+          <t>Fonte: vidaimobiliaria.com, racius.com</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Qualive</t>
+          <t>Optylon Krea</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2271,44 +2255,60 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>+351 226 090 545</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
+          <t>+351 212 400 124</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>sales@optylonkrea.com</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>optylonkrea.com</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Rua D. Pedro V 410, 2º, 4150-601</t>
+          <t>Rua Alexandre Herculano 50, 10º/11º, 1250-096</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Fábrica do Prado (Matosinhos) (Em construção)</t>
+          <t>Ando Living – Alfama Club e Liberdade Club (Em construção) | Augusta Townhouse + Santos Townhouse (Comercialização)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Telefone do registo comercial (einforma). Comercialização JLL/Predibisa</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>1,7B€ investidos · PT e Turquia</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>William Tonnard (President &amp; COO· Chairman é Hakan Kodal)</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-tonnard/</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Quest Capital</t>
+          <t>Qualive</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2318,60 +2318,44 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>+351 213 472 435</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>info@questcapital.eu</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>questcapital.eu</t>
-        </is>
-      </c>
+          <t>+351 226 090 545</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Rua António Maria Cardoso 2, 1200-027 (escritório Porto: Rua Fernandes Tomás 546)</t>
+          <t>Rua D. Pedro V 410, 2º, 4150-601</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Antas Atrium (Porto, antigo estádio) (Em construção)</t>
+          <t>Fábrica do Prado (Matosinhos) (Em construção)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Com Tikehau Capital. &gt;1B€ sob gestão</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Carlos Vasconcellos (Founding Partner, CEO exato não confirmado)</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/vasconcelloscarlos/</t>
-        </is>
-      </c>
+          <t>Telefone do registo comercial (einforma). Comercialização JLL/Predibisa</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ReVentures – Property Developers</t>
+          <t>Quest Capital</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2381,17 +2365,17 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>+351 212 402 489</t>
+          <t>+351 213 472 435</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>info@reventures.pt</t>
+          <t>info@questcapital.eu</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>reventures.pt</t>
+          <t>questcapital.eu</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2406,27 +2390,27 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Campo Grande 28, 3º A, 1700-093</t>
+          <t>Rua António Maria Cardoso 2, 1200-027 (escritório Porto: Rua Fernandes Tomás 546)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7 residências de estudantes (rede nacional) (Em construção) | Senior Living (Planeamento)</t>
+          <t>Antas Atrium (Porto, antigo estádio) (Em construção)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>NIF 516390350, capital 800k€. Fonte: construir.pt abr/2026</t>
+          <t>Com Tikehau Capital. &gt;1B€ sob gestão</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Hugo Gonçalves Pereira (CEO)</t>
+          <t>Carlos Vasconcellos (Founding Partner, CEO exato não confirmado)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hugogpereira/</t>
+          <t>https://www.linkedin.com/in/vasconcelloscarlos/</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
@@ -2434,7 +2418,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Rio Capital / Grupo Rio</t>
+          <t>ReVentures – Property Developers</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2444,17 +2428,17 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>+351 213 861 065</t>
+          <t>+351 212 402 489</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>geral@riocapital.pt</t>
+          <t>info@reventures.pt</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>riocapital.pt</t>
+          <t>reventures.pt</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2469,27 +2453,35 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Av. Duarte Pacheco, Amoreiras Torre 2, 14º D</t>
+          <t>Campo Grande 28, 3º A, 1700-093</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21 projetos residenciais Grande Porto (Em construção) | Velaris (Porto) (Planeamento) | São Vicente (Maia) (Planeamento) | Metropólis Estúdio Residence (Matosinhos) (Planeamento)</t>
+          <t>7 residências de estudantes (rede nacional) (Em construção) | Senior Living (Planeamento)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Grupo nascido em Monção, liderado por Nuno Afonso. Fonte: idealista/news jun/2026, Público</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>NIF 516390350, capital 800k€. Fonte: construir.pt abr/2026</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Gonçalves Pereira (CEO)</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hugogpereira/</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Rockbuilding – Soluções Imobiliárias</t>
+          <t>Rio Capital / Grupo Rio</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2499,13 +2491,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>+351 217 996 700</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>+351 213 861 065</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>geral@riocapital.pt</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>rockbuilding.com</t>
+          <t>riocapital.pt</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2520,35 +2516,27 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, 7º A, 1070-374</t>
+          <t>Av. Duarte Pacheco, Amoreiras Torre 2, 14º D</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Serviços de desenvolvimento para promotores (Em construção)</t>
+          <t>21 projetos residenciais Grande Porto (Em construção) | Velaris (Porto) (Planeamento) | São Vicente (Maia) (Planeamento) | Metropólis Estúdio Residence (Matosinhos) (Planeamento)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>ATENÇÃO: é gestor de projeto/serviços, não promotor puro</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>José Pedro Almeida Guerra (Diretor Geral)</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/josé-pedro-almeida-guerra-20723679</t>
-        </is>
-      </c>
+          <t>Grupo nascido em Monção, liderado por Nuno Afonso. Fonte: idealista/news jun/2026, Público</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Royal Ventures</t>
+          <t>Rockbuilding – Soluções Imobiliárias</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2558,52 +2546,48 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>+351 916 770 322</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>alex@royal-ventures.com</t>
-        </is>
-      </c>
+          <t>+351 217 996 700</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>royal-ventures.com</t>
+          <t>rockbuilding.com</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Edifício Oceanus, Av. da Boavista 3227, 4100-137</t>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, 7º A, 1070-374</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação centro histórico do Porto (Em construção)</t>
+          <t>Serviços de desenvolvimento para promotores (Em construção)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
+          <t>ATENÇÃO: é gestor de projeto/serviços, não promotor puro</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Udi Yadin (fundador/General Partner)</t>
+          <t>José Pedro Almeida Guerra (Diretor Geral)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/udiyadin/</t>
+          <t>https://pt.linkedin.com/in/josé-pedro-almeida-guerra-20723679</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
@@ -2611,7 +2595,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Sharp Developers</t>
+          <t>Royal Ventures</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2621,17 +2605,17 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>+351 933 078 094</t>
+          <t>+351 916 770 322</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>info@sharpdevelopers.pt</t>
+          <t>alex@royal-ventures.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sharpdevelopers.pt</t>
+          <t>royal-ventures.com</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2646,27 +2630,27 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
+          <t>Edifício Oceanus, Av. da Boavista 3227, 4100-137</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Residencial de luxo Porto (Em construção)</t>
+          <t>Reabilitação centro histórico do Porto (Em construção)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>CEO Carla Luís</t>
+          <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Carla Luís (CEO/cofundadora)</t>
+          <t>Udi Yadin (fundador/General Partner)</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/carla-luís-b14a7616/</t>
+          <t>https://www.linkedin.com/in/udiyadin/</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
@@ -2674,7 +2658,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SILCOGE / Grupo SIL</t>
+          <t>Sharp Developers</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2684,52 +2668,52 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>+351 210 124 500</t>
+          <t>+351 933 078 094</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>info@sil.pt</t>
+          <t>info@sharpdevelopers.pt</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sil.pt</t>
+          <t>sharpdevelopers.pt</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
+          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Grande Lisboa (Em construção)</t>
+          <t>Residencial de luxo Porto (Em construção)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Promoção imobiliária desde 1949</t>
+          <t>CEO Carla Luís</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Pedro Silveira (acionista maioritário/ex-Chairman, destituído judicialmente mai/2025, em recurso)</t>
+          <t>Carla Luís (CEO/cofundadora)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pedro-silveira-88822a20/</t>
+          <t>https://www.linkedin.com/in/carla-luís-b14a7616/</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
@@ -2737,7 +2721,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SOLYD Property Developers</t>
+          <t>SILCOGE / Grupo SIL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2747,22 +2731,22 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>+351 211 214 926</t>
+          <t>+351 210 124 500</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>info@elou-solyd.pt</t>
+          <t>info@sil.pt</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>solyd.pt</t>
+          <t>sil.pt</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2772,27 +2756,27 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
+          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Luz Altear (Alta de Lisboa) (Em construção)</t>
+          <t>Grande Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
+          <t>Promoção imobiliária desde 1949</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Gonçalo Cadete (CEO)</t>
+          <t>Pedro Silveira (acionista maioritário/ex-Chairman, destituído judicialmente mai/2025, em recurso)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gon%C3%A7alo-cadete-260692/</t>
+          <t>https://www.linkedin.com/in/pedro-silveira-88822a20/</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
@@ -2800,7 +2784,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Stone Capital</t>
+          <t>SOLYD Property Developers</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2810,22 +2794,22 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>+351 210 416 350</t>
+          <t>+351 211 214 926</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>info@stonecapital.pt</t>
+          <t>info@elou-solyd.pt</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>stonecapital.pt</t>
+          <t>solyd.pt</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2835,31 +2819,35 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 240, 1250-096</t>
+          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
+          <t>Luz Altear (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Tel. móvel 965 915 993</t>
+          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Geoffroy Moreno (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>Gonçalo Cadete (CEO)</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gon%C3%A7alo-cadete-260692/</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Teixeira Duarte Real Estate</t>
+          <t>Stone Capital</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2869,22 +2857,22 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>+351 217 912 300</t>
+          <t>+351 210 416 350</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>info@tdimobiliaria.pt</t>
+          <t>info@stonecapital.pt</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>tdimobiliaria.pt</t>
+          <t>stonecapital.pt</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2894,27 +2882,31 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
+          <t>Av. da Liberdade 240, 1250-096</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
+          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do grupo Teixeira Duarte</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
+          <t>Tel. móvel 965 915 993</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Geoffroy Moreno (Co-Founder)</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Thomas &amp; Piron Portugal</t>
+          <t>Teixeira Duarte Real Estate</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2924,60 +2916,52 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>+351 214 422 464</t>
+          <t>+351 217 912 300</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>infopt@thomas-piron.eu</t>
+          <t>info@tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>thomas-piron.pt</t>
+          <t>tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Escritórios em Matosinhos e Sacavém</t>
+          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
+          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>David Carreira (Diretor Geral/Country Manager)</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>https://lu.linkedin.com/in/david-carreira-a4082050</t>
-        </is>
-      </c>
+          <t>Braço imobiliário do grupo Teixeira Duarte</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Properties</t>
+          <t>Thomas &amp; Piron Portugal</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2987,52 +2971,52 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>+351 215 814 094</t>
+          <t>+351 214 422 464</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>info@vangproperties.com</t>
+          <t>infopt@thomas-piron.eu</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>vangproperties.com</t>
+          <t>thomas-piron.pt</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
+          <t>Escritórios em Matosinhos e Sacavém</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
+          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
+          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Henrique Rodrigues da Silva (CEO desde fev/2026)</t>
+          <t>David Carreira (Diretor Geral/Country Manager)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/henrique-rodrigues-da-silva-b396643/</t>
+          <t>https://lu.linkedin.com/in/david-carreira-a4082050</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
@@ -3040,7 +3024,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>VIC Properties</t>
+          <t>Vanguard Properties</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3050,17 +3034,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>+351 219 347 112</t>
+          <t>+351 215 814 094</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>info@vic-properties.com</t>
+          <t>info@vangproperties.com</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>vic-properties.com</t>
+          <t>vangproperties.com</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3075,27 +3059,27 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Portefólio &gt;3B€. Fundada 2018</t>
+          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>João Cabaça (Co-fundador e CEO)</t>
+          <t>Henrique Rodrigues da Silva (CEO desde fev/2026)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/jo%C3%A3o-caba%C3%A7a-6b293614b</t>
+          <t>https://www.linkedin.com/in/henrique-rodrigues-da-silva-b396643/</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -3103,125 +3087,133 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>VIC Properties</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>+351 219 347 112</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>info@vic-properties.com</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>vic-properties.com</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Portefólio &gt;3B€. Fundada 2018</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>João Cabaça (Co-fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/jo%C3%A3o-caba%C3%A7a-6b293614b</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>Vogue Homes</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>+351 213 461 246</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>comercial@vogue-homes.com</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>vogue-homes.com</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Rua Luz Soriano 15, 1200-246</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>Dafundo 24 (Comercialização) | Bom Sucesso (Comercialização) | Westhouse (Cascais) (Comercialização)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>NIF 510933084. Tel. móvel 913 385 846</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>Joaquim Lico (CEO)</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/joaquim-lico-4383239/</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Alecrim Real Estate (Lince Capital)</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>lince-capital.com</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Fortera</t>
+          <t>AFA (Grupo AFA)</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -3234,41 +3226,33 @@
       <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>Porto / Gaia</t>
-        </is>
-      </c>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
+          <t>Savoy Residence D'Ávila (Em construção)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
-        </is>
-      </c>
+          <t>Fonte: diarioimobiliario.pt</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Alecrim Real Estate (Lince Capital)</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -3280,7 +3264,7 @@
       <c r="D47" s="5" t="inlineStr"/>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>hines.com</t>
+          <t>lince-capital.com</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3295,31 +3279,35 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
+          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Gestora global · sem contacto PT publicado</t>
+          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
+          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
+        </is>
+      </c>
       <c r="M47" s="5" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Arts Investments, SA</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3331,42 +3319,38 @@
       <c r="D48" s="5" t="inlineStr"/>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>imolote.pt</t>
+          <t>artsinvestments.com</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
+          <t>3 projetos em curso (nomes não encontrados) (Em construção/desenvolvimento)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
-        </is>
-      </c>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Overseas</t>
+          <t>Ceetrus / Nhood Portugal</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -3384,40 +3368,28 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
-        </is>
-      </c>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+          <t>Pipeline nacional 15 cidades (nomes não encontrados) (Planeamento)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>Pedro Vicente (CEO)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -3430,41 +3402,33 @@
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+          <t>Fábrica Vilar (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/site publicados (APPII)</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>Federico Rosales (cofundador e CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: viva-porto.pt</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>Fortera</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3474,39 +3438,35 @@
       </c>
       <c r="C51" s="7" t="inlineStr"/>
       <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>roundhillcapital.com</t>
-        </is>
-      </c>
+      <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Rua da Escola Politécnica 38, 1250-102</t>
+          <t>Porto / Gaia</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone PT publicado</t>
+          <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
+          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
@@ -3515,7 +3475,7 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Screendomus (Grupo Teixeira)</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -3524,14 +3484,10 @@
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>geral@screendomus.com</t>
-        </is>
-      </c>
+      <c r="D52" s="5" t="inlineStr"/>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>screendomus.com</t>
+          <t>hines.com</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -3544,20 +3500,24 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Altus (Alta de Lisboa) (Em construção)</t>
+          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
+          <t>Gestora global · sem contacto PT publicado</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
@@ -3566,7 +3526,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>United Investments Portugal (UIP)</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -3578,50 +3538,42 @@
       <c r="D53" s="5" t="inlineStr"/>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>uip.pt</t>
+          <t>imolote.pt</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Fundada 1985 · sem telefone publicado</t>
+          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Carlos Leal (CEO)</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
-        </is>
-      </c>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3630,57 +3582,37 @@
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>vizta.pt</t>
-        </is>
-      </c>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Vasco Costa (CEO)</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -3689,785 +3621,605 @@
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>info@ancora-inv.com</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>ancora-inv.com</t>
-        </is>
-      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
+          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Overseas</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Pedro Vicente (CEO)</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Portaviv</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Prime Portugal</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Sem telefone/site publicados (APPII)</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Federico Rosales (cofundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>RAR Imobiliária</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Matosinhos</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>RM Villas (Início obra 1T2026)</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Round Hill Capital</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>roundhillcapital.com</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Rua da Escola Politécnica 38, 1250-102</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Sem telefone PT publicado</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Screendomus (Grupo Teixeira)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>geral@screendomus.com</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>screendomus.com</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Altus (Alta de Lisboa) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Taga Urbanic</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Maia</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Verde Vale (Em construção)</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>United Investments Portugal (UIP)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>uip.pt</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Fundada 1985 · sem telefone publicado</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Leal (CEO)</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>grupovisabeira.com</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Areeiro Select (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>VIZTA (ex-Nexity Portugal)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>info@ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Antrix</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>info@antrix.pt</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>antrix.pt</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Carvoeiro Branco – Propriedades</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>info@carvoeirobranco.com</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>carvoeirobranco.com</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Erik de Vlieger (CEO)</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>+351 253 305 490</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>casais@casais.pt</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>casais.pt</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Castro Group</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>+351 253 461 462</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>geral@castro-group.pt</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>castro-group.pt</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>50 anos de história. Fonte: APPII</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Paulo Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Civilria</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>+351 234 480 570</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>info@civilria.pt</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>civilria.pt</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Portefólio Aveiro (Em construção)</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Artur Varum (CEO)</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>+351 289 381 550</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>enolagest.pt</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Greens Vilamoura (Em construção)</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Garcia Garcia</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>+351 253 560 230</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>geral@garcia.pt</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>garcia.pt</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Santo Tirso</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>+351 252 308 250</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>aca@grupo-aca.com</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>grupo-aca.com</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Vila Nova de Famalicão</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Grupo Acrescentar</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>+351 253 685 109</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>grupoacrescentar.pt</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Grupo Arliz</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>+351 253 105 331</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>geral@arliz.co</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>grupoarliz.pt</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Arc Living (Porto) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Domingos Correia (CEO)</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>cvmnet.com</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Santa Maria da Feira</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -4477,56 +4229,60 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
+          <t>900 264 096 (ES)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>geral@jhomea.pt</t>
+          <t>info@aedashomes.com</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -4536,48 +4292,52 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>info@pinehill.pt</t>
+          <t>info@antrix.pt</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+        </is>
+      </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
@@ -4585,7 +4345,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -4595,208 +4355,3541 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>info@quintadolago.com</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Almancil</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Sean Moriarty (CEO)</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
-        </is>
-      </c>
+          <t>Fonte: diarioimobiliario.pt</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>Carvoeiro Branco – Propriedades</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>+351 917 498 714</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>info@carvoeirobranco.com</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>carvoeirobranco.com</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Lagoa</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Erik de Vlieger (CEO)</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Casais Imobiliária (Grupo Casais)</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>+351 253 305 490</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>casais@casais.pt</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>casais.pt</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Castro Group</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>+351 253 461 462</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>geral@castro-group.pt</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>castro-group.pt</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>50 anos de história. Fonte: APPII</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Paulo Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Civilria</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>+351 234 480 570</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>info@civilria.pt</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>civilria.pt</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Portefólio Aveiro (Em construção)</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Dipe Real Estate</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>+351 253 089 932</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>dipe.pt</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Guimarães</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>enolagest.pt</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Greens Vilamoura (Em construção)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Reinaldo Teixeira (Administrador)</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Garcia Garcia</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>+351 253 560 230</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>geral@garcia.pt</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>garcia.pt</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Santo Tirso</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>+351 252 308 250</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>aca@grupo-aca.com</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>grupo-aca.com</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Acrescentar</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>+351 253 685 109</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>acrescentar@grupoacrescentar.pt</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>grupoacrescentar.pt</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Arliz</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>+351 253 105 331</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>geral@arliz.co</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>grupoarliz.pt</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Arc Living (Porto) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Grupo CVM (Construções Vila Maior)</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>273 332 784 (confirmar)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>cvmnet.com</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Santa Maria da Feira</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>HomeLovers Investment</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>homelovers.pt</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: sapo.pt</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>JHOMEA Invest</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>+351 934 175 642</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>jhomea.pt</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Vacivus (Porto) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>José Miguel Afonso (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Pine Hill</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>+351 910 936 732</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>info@pinehill.pt</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>pinehill.pt</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Pinheiro (fundador)</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Quinta do Lago Resort</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>+351 289 390 700</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>quintadolago.com</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Resort residencial/golfe</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Salk Properties Portugal</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>+351 939 443 765</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>salkproperties.com</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Scale Property Development</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>+351 219 362 960</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>scalepropertydevelopment.com</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>+351 255 433 572</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>geral@tps.com.pt</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>tps.com.pt</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>Amarante</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: omirante.pt</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Algarve Property Shops</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr"/>
+      <c r="D90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Tavira</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr"/>
+      <c r="L90" s="5" t="inlineStr"/>
+      <c r="M90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Amorim Luxury</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa/Grândola/Lagoa</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr"/>
+      <c r="L91" s="5" t="inlineStr"/>
+      <c r="M91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Aresta Vitalicia</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr"/>
+      <c r="D92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>WeBuild Castelo (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr"/>
+      <c r="M92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Arrow Global Portugal</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr"/>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>The Shore Residences (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr"/>
+      <c r="L93" s="5" t="inlineStr"/>
+      <c r="M93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Baltor – Engenharia e Construção</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr"/>
+      <c r="D94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal (sede Viana do Castelo)</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Branco Real Estate</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr"/>
+      <c r="D95" s="5" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr"/>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Domus (Em construção)</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr"/>
+      <c r="L95" s="5" t="inlineStr"/>
+      <c r="M95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Casas do Sotavento</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr"/>
+      <c r="D96" s="5" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Tavira</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: boavistaoceantavira.com</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr"/>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr"/>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Silves</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr"/>
+      <c r="M97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>CS Ribeiro</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr"/>
+      <c r="D98" s="5" t="inlineStr"/>
+      <c r="E98" s="5" t="inlineStr"/>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Guarda (atua Viseu/Coimbra)</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Guarda</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr"/>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: diariocoimbra.pt</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr"/>
+      <c r="L98" s="5" t="inlineStr"/>
+      <c r="M98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Discovery Land Company</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr"/>
+      <c r="D99" s="5" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Grândola (Melides)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr"/>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: brainsre.news</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr"/>
+      <c r="L99" s="5" t="inlineStr"/>
+      <c r="M99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>DUJA – Sociedade de Construções, Lda</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr"/>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>Tavira</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr"/>
+      <c r="L100" s="5" t="inlineStr"/>
+      <c r="M100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Emblezart</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr"/>
+      <c r="D101" s="5" t="inlineStr"/>
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>Guimarães</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr"/>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr"/>
+      <c r="L101" s="5" t="inlineStr"/>
+      <c r="M101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Encobarra</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr"/>
+      <c r="D102" s="5" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr"/>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Aveiro (Aradas)</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Quinta da Pinheira (Em construção)</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr"/>
+      <c r="L102" s="5" t="inlineStr"/>
+      <c r="M102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Estrutural Group</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr"/>
+      <c r="D103" s="5" t="inlineStr"/>
+      <c r="E103" s="5" t="inlineStr"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Vila Franca de Xira</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr"/>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Vila Viva (Em construção)</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr"/>
+      <c r="L103" s="5" t="inlineStr"/>
+      <c r="M103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Explorer Investments (Explorer Real Estate)</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr"/>
+      <c r="D104" s="5" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>Sintra</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr"/>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr"/>
+      <c r="L104" s="5" t="inlineStr"/>
+      <c r="M104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Finangeste, S.A.</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr"/>
+      <c r="D105" s="5" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr"/>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>PUVA (Planeamento/Em construção)</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr"/>
+      <c r="L105" s="5" t="inlineStr"/>
+      <c r="M105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>FourPromo, Lda (Grupo M2O)</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr"/>
+      <c r="D106" s="5" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Loulé (Vilamoura)</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr"/>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Rivus (Em construção/Comercialização)</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: construir.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr"/>
+      <c r="L106" s="5" t="inlineStr"/>
+      <c r="M106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Foz Gala Investments</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr"/>
+      <c r="D107" s="5" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Figueira da Foz</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr"/>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr"/>
+      <c r="L107" s="5" t="inlineStr"/>
+      <c r="M107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr"/>
+      <c r="D108" s="5" t="inlineStr"/>
+      <c r="E108" s="5" t="inlineStr"/>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Albufeira</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr"/>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Quinta Dourada (Em construção)</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr"/>
+      <c r="L108" s="5" t="inlineStr"/>
+      <c r="M108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Genuino Investments</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr"/>
+      <c r="D109" s="5" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>genuinoinvestments.com</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Portimão</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr"/>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: genuinoinvestments.com</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr"/>
+      <c r="L109" s="5" t="inlineStr"/>
+      <c r="M109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr"/>
+      <c r="D110" s="5" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>Faro/Loulé</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr"/>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr"/>
+      <c r="L110" s="5" t="inlineStr"/>
+      <c r="M110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Glowing</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr"/>
+      <c r="D111" s="5" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>glowing.pt</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr"/>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>FiniSal (Em construção/Comercialização)</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr"/>
+      <c r="L111" s="5" t="inlineStr"/>
+      <c r="M111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Grupo A. Silva &amp; Silva</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr"/>
+      <c r="D112" s="5" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr"/>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>Seixal</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr"/>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Seixal Baía (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr"/>
+      <c r="L112" s="5" t="inlineStr"/>
+      <c r="M112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr"/>
+      <c r="D113" s="5" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr">
         <is>
           <t>andreguimaraes.com.br</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr"/>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
+      <c r="I113" s="5" t="inlineStr">
         <is>
           <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J113" s="5" t="inlineStr">
         <is>
           <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K113" s="5" t="inlineStr">
         <is>
           <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr"/>
+      <c r="M113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Grupo André Jordan</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr"/>
+      <c r="D114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>Sintra</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr"/>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr"/>
+      <c r="L114" s="5" t="inlineStr"/>
+      <c r="M114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr"/>
+      <c r="D115" s="5" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr"/>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr"/>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr"/>
+      <c r="L115" s="5" t="inlineStr"/>
+      <c r="M115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Azinor</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr"/>
+      <c r="D116" s="5" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr"/>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>Oeiras</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr"/>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr"/>
+      <c r="L116" s="5" t="inlineStr"/>
+      <c r="M116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Mais Empresas / Construções Mais</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr"/>
+      <c r="D117" s="5" t="inlineStr"/>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>grupomaisempresas.pt</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Golden Wolf (Em construção)</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr"/>
+      <c r="L117" s="5" t="inlineStr"/>
+      <c r="M117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Grupo NB Portugal</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr"/>
+      <c r="D118" s="5" t="inlineStr"/>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>gruponbportugal.pt</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: gruponb.pt</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr"/>
+      <c r="L118" s="5" t="inlineStr"/>
+      <c r="M118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Pestana (Pestana Residences)</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr"/>
+      <c r="D119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>pestana.com</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>Sines/Lagoa</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr"/>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr"/>
+      <c r="L119" s="5" t="inlineStr"/>
+      <c r="M119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Hillside House Coimbra, Lda</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr"/>
+      <c r="D120" s="5" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>hillside.pt</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>Mealhada (projeto em Coimbra)</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr"/>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: remax.pt, hillside.pt</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr"/>
+      <c r="L120" s="5" t="inlineStr"/>
+      <c r="M120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr"/>
+      <c r="D121" s="5" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>zenithresidences.pt</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Portimão</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr"/>
+      <c r="L121" s="5" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Invesquart – Real Estate Promotor</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr"/>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr"/>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>Loulé (Quarteira)</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Terraços de Quarteira (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr"/>
+      <c r="L122" s="5" t="inlineStr"/>
+      <c r="M122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr"/>
+      <c r="D123" s="5" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>jpaiva.pt</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr"/>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: jpaiva.pt</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr"/>
+      <c r="L123" s="5" t="inlineStr"/>
+      <c r="M123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Lux Premium</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr"/>
+      <c r="D124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Coimbra Premium (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: luxpremium.net</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr"/>
+      <c r="L124" s="5" t="inlineStr"/>
+      <c r="M124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>MAJA Construções, S.A.</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr"/>
+      <c r="D125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr"/>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Albufeira</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Quinta Dourada (Em construção)</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: oconnormurphy.ie</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr"/>
+      <c r="L125" s="5" t="inlineStr"/>
+      <c r="M125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr"/>
+      <c r="D126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr"/>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr"/>
+      <c r="L126" s="5" t="inlineStr"/>
+      <c r="M126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Maven (Maven Invest)</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr"/>
+      <c r="D127" s="5" t="inlineStr"/>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>WeBuild Castelo (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: maveninvest.pt</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr"/>
+      <c r="L127" s="5" t="inlineStr"/>
+      <c r="M127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Mello RDC</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr"/>
+      <c r="D128" s="5" t="inlineStr"/>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>Grândola (Melides)</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr"/>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr"/>
+      <c r="L128" s="5" t="inlineStr"/>
+      <c r="M128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr"/>
+      <c r="D129" s="5" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr"/>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>Albufeira</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr"/>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Quinta Dourada (Em construção)</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: ireland-portugal.com</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr"/>
+      <c r="L129" s="5" t="inlineStr"/>
+      <c r="M129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Nova Atlantic</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr"/>
+      <c r="D130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr"/>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr"/>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr"/>
+      <c r="L130" s="5" t="inlineStr"/>
+      <c r="M130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>OCM Portugal (O'Connor Murphy)</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr"/>
+      <c r="D131" s="5" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Olhão</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr"/>
+      <c r="L131" s="5" t="inlineStr"/>
+      <c r="M131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr"/>
-      <c r="D73" s="5" t="inlineStr"/>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr"/>
+      <c r="D132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>ombria.com</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr">
         <is>
           <t>Loulé</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G132" s="7" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>Loulé</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J132" s="5" t="inlineStr">
         <is>
           <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="K132" s="5" t="inlineStr">
         <is>
           <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="L132" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/patricksfreeman/</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr"/>
+      <c r="M132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>PATRIMOINIMMO PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr"/>
+      <c r="D133" s="5" t="inlineStr"/>
+      <c r="E133" s="5" t="inlineStr"/>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Lagoa</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr"/>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr"/>
+      <c r="L133" s="5" t="inlineStr"/>
+      <c r="M133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134" ht="30" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr"/>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr"/>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>Palmela</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr"/>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Palmela Village (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr"/>
+      <c r="L134" s="5" t="inlineStr"/>
+      <c r="M134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Pensaplano</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr"/>
+      <c r="D135" s="5" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr"/>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr"/>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Eleven (Em construção)</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr"/>
+      <c r="L135" s="5" t="inlineStr"/>
+      <c r="M135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Portugal Slow Living</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr"/>
+      <c r="D136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr"/>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>Montijo</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr"/>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Monville (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr"/>
+      <c r="L136" s="5" t="inlineStr"/>
+      <c r="M136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Rivage Properties</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr"/>
+      <c r="D137" s="5" t="inlineStr"/>
+      <c r="E137" s="5" t="inlineStr"/>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>Gondomar</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>The View II (Em construção (conclusão 2026))</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr"/>
+      <c r="L137" s="5" t="inlineStr"/>
+      <c r="M137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr"/>
+      <c r="D138" s="5" t="inlineStr"/>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>rodriguesevermelho.com</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: sava.pt, thepreplan.com</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr"/>
+      <c r="L138" s="5" t="inlineStr"/>
+      <c r="M138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Soccal &amp; Vaz Invest</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr"/>
+      <c r="D139" s="5" t="inlineStr"/>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>soccal-vaz.com</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Sines</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>Brisa Mar (Em construção)</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: eco.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr"/>
+      <c r="L139" s="5" t="inlineStr"/>
+      <c r="M139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Solid Sentinel</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr"/>
+      <c r="D140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>solidsentinel.pt</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>Barreiro</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>NOOBA (Em construção/comercialização)</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
+      <c r="M140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>SOLUM PROGRESS</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr"/>
+      <c r="D141" s="5" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr"/>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr"/>
+      <c r="L141" s="5" t="inlineStr"/>
+      <c r="M141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Sonae Sierra</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr"/>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>sonaesierra.com</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa/Porto</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr"/>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Pulse Lisboa (Em construção)</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: rtp.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr"/>
+      <c r="L142" s="5" t="inlineStr"/>
+      <c r="M142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Southshore Investments</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr"/>
+      <c r="D143" s="5" t="inlineStr"/>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>southshoreinvest.com</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>Almada</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>Tejo City District (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: southshoreinvest.com</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr"/>
+      <c r="L143" s="5" t="inlineStr"/>
+      <c r="M143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Square View</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr"/>
+      <c r="D144" s="5" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa/Ericeira/Melides</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr"/>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="inlineStr"/>
+      <c r="L144" s="5" t="inlineStr"/>
+      <c r="M144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Terrace Benefit, Lda</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr"/>
+      <c r="D145" s="5" t="inlineStr"/>
+      <c r="E145" s="5" t="inlineStr"/>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>Loulé (Quarteira)</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr"/>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>Forte Novo (Em construção)</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: racius.com, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr"/>
+      <c r="L145" s="5" t="inlineStr"/>
+      <c r="M145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Udra – Grupo San José</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr"/>
+      <c r="D146" s="5" t="inlineStr"/>
+      <c r="E146" s="5" t="inlineStr"/>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr"/>
+      <c r="L146" s="5" t="inlineStr"/>
+      <c r="M146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Urban Green Private (UGP)</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr"/>
+      <c r="D147" s="5" t="inlineStr"/>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>ugp.ie</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr"/>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>The Shipyard (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="inlineStr"/>
+      <c r="L147" s="5" t="inlineStr"/>
+      <c r="M147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr"/>
+      <c r="D148" s="5" t="inlineStr"/>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr"/>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr"/>
+      <c r="L148" s="5" t="inlineStr"/>
+      <c r="M148" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4838,7 +7931,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>72</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
@@ -4848,7 +7941,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -4858,7 +7951,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>13</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +7961,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -3245,7 +3245,11 @@
           <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Victor de Sousa (Diretor-Geral AFA Real Estate)</t>
+        </is>
+      </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
     </row>
@@ -3421,7 +3425,11 @@
           <t>Fonte: viva-porto.pt</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
+        </is>
+      </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
     </row>
@@ -3605,7 +3613,11 @@
           <t>Fonte: construir.pt</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+        </is>
+      </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
     </row>
@@ -3644,7 +3656,11 @@
           <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+        </is>
+      </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
     </row>
@@ -3734,7 +3750,11 @@
           <t>Fonte: construir.pt</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Nuno Cunha (Managing Director)</t>
+        </is>
+      </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
     </row>
@@ -3820,7 +3840,11 @@
           <t>Fonte: dinheirovivo.pt, construir.pt</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Paula Fernandes (CEO)</t>
+        </is>
+      </c>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
     </row>
@@ -4098,8 +4122,16 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
+        </is>
+      </c>
       <c r="M65" s="5" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
@@ -4385,8 +4417,16 @@
           <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -4680,7 +4720,11 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Baptista Antunes (CEO)</t>
+        </is>
+      </c>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
     </row>
@@ -5085,8 +5129,16 @@
           <t>Fonte: sapo.pt</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
@@ -5313,7 +5365,11 @@
           <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
+        </is>
+      </c>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
@@ -5360,8 +5416,16 @@
           <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
@@ -5466,7 +5530,11 @@
           <t>Fonte: omirante.pt</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
@@ -5544,7 +5612,11 @@
           <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr"/>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
       <c r="L91" s="5" t="inlineStr"/>
       <c r="M91" s="5" t="inlineStr"/>
     </row>
@@ -5622,7 +5694,11 @@
           <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
         </is>
       </c>
-      <c r="K93" s="5" t="inlineStr"/>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="L93" s="5" t="inlineStr"/>
       <c r="M93" s="5" t="inlineStr"/>
     </row>
@@ -5665,7 +5741,11 @@
           <t>Fonte: ominho.pt</t>
         </is>
       </c>
-      <c r="K94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L94" s="5" t="inlineStr"/>
       <c r="M94" s="5" t="inlineStr"/>
     </row>
@@ -5946,8 +6026,16 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr"/>
-      <c r="L101" s="5" t="inlineStr"/>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
@@ -5985,7 +6073,11 @@
           <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
-      <c r="K102" s="5" t="inlineStr"/>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>Aristides Alferes (administrador)</t>
+        </is>
+      </c>
       <c r="L102" s="5" t="inlineStr"/>
       <c r="M102" s="5" t="inlineStr"/>
     </row>
@@ -6024,7 +6116,11 @@
           <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
-      <c r="K103" s="5" t="inlineStr"/>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
+        </is>
+      </c>
       <c r="L103" s="5" t="inlineStr"/>
       <c r="M103" s="5" t="inlineStr"/>
     </row>
@@ -6067,7 +6163,11 @@
           <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
-      <c r="K104" s="5" t="inlineStr"/>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="L104" s="5" t="inlineStr"/>
       <c r="M104" s="5" t="inlineStr"/>
     </row>
@@ -6106,7 +6206,11 @@
           <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
         </is>
       </c>
-      <c r="K105" s="5" t="inlineStr"/>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="5" t="inlineStr"/>
     </row>
@@ -6309,7 +6413,11 @@
           <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
         </is>
       </c>
-      <c r="K110" s="5" t="inlineStr"/>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L110" s="5" t="inlineStr"/>
       <c r="M110" s="5" t="inlineStr"/>
     </row>
@@ -6473,7 +6581,11 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K114" s="5" t="inlineStr"/>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
       <c r="L114" s="5" t="inlineStr"/>
       <c r="M114" s="5" t="inlineStr"/>
     </row>
@@ -6512,7 +6624,11 @@
           <t>Fonte: linkedin.com/company/grupo-aoc</t>
         </is>
       </c>
-      <c r="K115" s="5" t="inlineStr"/>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
       <c r="L115" s="5" t="inlineStr"/>
       <c r="M115" s="5" t="inlineStr"/>
     </row>
@@ -6551,8 +6667,16 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K116" s="5" t="inlineStr"/>
-      <c r="L116" s="5" t="inlineStr"/>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
@@ -6637,7 +6761,11 @@
           <t>Fonte: gruponb.pt</t>
         </is>
       </c>
-      <c r="K118" s="5" t="inlineStr"/>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
     </row>
@@ -6680,7 +6808,11 @@
           <t>Fonte: publico.pt, construir.pt</t>
         </is>
       </c>
-      <c r="K119" s="5" t="inlineStr"/>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L119" s="5" t="inlineStr"/>
       <c r="M119" s="5" t="inlineStr"/>
     </row>
@@ -6848,8 +6980,16 @@
           <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
-      <c r="K123" s="5" t="inlineStr"/>
-      <c r="L123" s="5" t="inlineStr"/>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M123" s="5" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
@@ -6891,7 +7031,11 @@
           <t>Fonte: luxpremium.net</t>
         </is>
       </c>
-      <c r="K124" s="5" t="inlineStr"/>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="L124" s="5" t="inlineStr"/>
       <c r="M124" s="5" t="inlineStr"/>
     </row>
@@ -6930,7 +7074,11 @@
           <t>Fonte: oconnormurphy.ie</t>
         </is>
       </c>
-      <c r="K125" s="5" t="inlineStr"/>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+        </is>
+      </c>
       <c r="L125" s="5" t="inlineStr"/>
       <c r="M125" s="5" t="inlineStr"/>
     </row>
@@ -7012,7 +7160,11 @@
           <t>Fonte: maveninvest.pt</t>
         </is>
       </c>
-      <c r="K127" s="5" t="inlineStr"/>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
@@ -7055,8 +7207,16 @@
           <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
-      <c r="K128" s="5" t="inlineStr"/>
-      <c r="L128" s="5" t="inlineStr"/>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M128" s="5" t="inlineStr"/>
     </row>
     <row r="129" ht="30" customHeight="1">
@@ -7133,7 +7293,11 @@
           <t>Fonte: jornaleconomico.sapo.pt</t>
         </is>
       </c>
-      <c r="K130" s="5" t="inlineStr"/>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
       <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="5" t="inlineStr"/>
     </row>
@@ -7309,7 +7473,11 @@
           <t>Fonte: racius.com, cnnportugal.iol.pt</t>
         </is>
       </c>
-      <c r="K134" s="5" t="inlineStr"/>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
@@ -7426,7 +7594,11 @@
           <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
-      <c r="K137" s="5" t="inlineStr"/>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
       <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
     </row>
@@ -7469,7 +7641,11 @@
           <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
-      <c r="K138" s="5" t="inlineStr"/>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
@@ -7512,8 +7688,16 @@
           <t>Fonte: eco.sapo.pt</t>
         </is>
       </c>
-      <c r="K139" s="5" t="inlineStr"/>
-      <c r="L139" s="5" t="inlineStr"/>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>António Vaz (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+        </is>
+      </c>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
@@ -7555,8 +7739,16 @@
           <t>Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
-      <c r="K140" s="5" t="inlineStr"/>
-      <c r="L140" s="5" t="inlineStr"/>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
@@ -7637,7 +7829,11 @@
           <t>Fonte: rtp.pt, idealista.pt</t>
         </is>
       </c>
-      <c r="K142" s="5" t="inlineStr"/>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
       <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
@@ -7723,7 +7919,11 @@
           <t>Fonte: squareview.pt</t>
         </is>
       </c>
-      <c r="K144" s="5" t="inlineStr"/>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
       <c r="L144" s="5" t="inlineStr"/>
       <c r="M144" s="5" t="inlineStr"/>
     </row>
@@ -7844,7 +8044,11 @@
           <t>Fonte: theshipyard.pt, barlavento.pt</t>
         </is>
       </c>
-      <c r="K147" s="5" t="inlineStr"/>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L147" s="5" t="inlineStr"/>
       <c r="M147" s="5" t="inlineStr"/>
     </row>
@@ -7971,7 +8175,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
@@ -7981,7 +8185,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M148" headerRowCount="1">
-  <autoFilter ref="A1:M148"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M155" headerRowCount="1">
+  <autoFilter ref="A1:M155"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1191,7 +1191,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EMERGE – Mota-Engil Real Estate</t>
+          <t>Easyliving</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>+351 225 190 362</t>
+          <t>+351 961 866 297</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>emerge@mota-engil.pt</t>
+          <t>info@easyliving.pt</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>emerge-realestate.pt</t>
+          <t>easyliving.pt</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1224,37 +1224,25 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Calçada do Rêgo Lameiro 38, 4300-454</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>OPO-City (Porto/Matosinhos) (Comercialização) | AURIOS (Comercialização)</t>
+          <t>Boavista Garden (Av. da Boavista) (Em construção) | Aspreladas Easy (Comercialização)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Promotora do grupo Mota-Engil</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Vitor Paulo Pinho (CEO)</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/vitor-paulo-pinho-0a7952173/</t>
-        </is>
-      </c>
+          <t>Compra, reabilitação e construção. Comercialização via RE/MAX Collection</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Fercopor</t>
+          <t>EMERGE – Mota-Engil Real Estate</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1264,13 +1252,17 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>+351 226 091 113</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>+351 225 190 362</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>emerge@mota-engil.pt</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>fercopor.pt</t>
+          <t>emerge-realestate.pt</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1285,31 +1277,35 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Av. da França 20, Sala 509, 4050-275</t>
+          <t>Calçada do Rêgo Lameiro 38, 4300-454</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Boavista (2 projetos) (Planeamento) | Vila do Conde (Planeamento)</t>
+          <t>OPO-City (Porto/Matosinhos) (Comercialização) | AURIOS (Comercialização)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Luxo desde 1981. Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Promotora do grupo Mota-Engil</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Mário Almeida (Administrador)</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>Vitor Paulo Pinho (CEO)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vitor-paulo-pinho-0a7952173/</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Fidelidade Property</t>
+          <t>Fercopor</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1319,52 +1315,52 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>+351 217 807 772</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>geral@fidelidadeproperty.pt</t>
-        </is>
-      </c>
+          <t>+351 226 091 113</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>fidelidadeproperty.pt</t>
+          <t>fercopor.pt</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Largo do Calhariz 30, 1249-001</t>
+          <t>Av. da França 20, Sala 509, 4050-275</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>EntreCampos (antiga Feira Popular) (Em construção)</t>
+          <t>Boavista (2 projetos) (Planeamento) | Vila do Conde (Planeamento)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário da Fidelidade. Projeto: info@entrecampos.pt</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>Luxo desde 1981. Fonte: reportugal.vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Mário Almeida (Administrador)</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FIDES – Investimentos e Gestão Imobiliária</t>
+          <t>Fidelidade Property</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1374,15 +1370,19 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>+351 213 877 749</t>
+          <t>+351 217 807 772</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>diogopintogoncalves@imofides.com</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+          <t>geral@fidelidadeproperty.pt</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>fidelidadeproperty.pt</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Rua Tierno Galvan, Amoreiras Torre 3, 6º, sala 607, 1070-274</t>
+          <t>Largo do Calhariz 30, 1249-001</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Promoção residencial (Em construção)</t>
+          <t>EntreCampos (antiga Feira Popular) (Em construção)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Projeto concreto não nomeado nas fontes</t>
+          <t>Braço imobiliário da Fidelidade. Projeto: info@entrecampos.pt</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Grupo Madre / Madre Imobiliário</t>
+          <t>FIDES – Investimentos e Gestão Imobiliária</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1425,19 +1425,15 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>+351 213 243 220</t>
+          <t>+351 213 877 749</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>geral@madreimobiliario.com</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>madreimobiliario.com</t>
-        </is>
-      </c>
+          <t>diogopintogoncalves@imofides.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -1450,31 +1446,27 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Campo Grande 28, 11º, 1700-093</t>
+          <t>Rua Tierno Galvan, Amoreiras Torre 3, 6º, sala 607, 1070-274</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>A-Living (Areeiro) (Planeamento) | Parque da Cidade (Setúbal) (Em construção)</t>
+          <t>Promoção residencial (Em construção)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Presidente António Parente. Tel. móvel 914 070 350</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Nuno Dias (Diretor Geral da Madre Imobiliário· presidente do grupo é António Parente)</t>
-        </is>
-      </c>
+          <t>Projeto concreto não nomeado nas fontes</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Habitat Invest</t>
+          <t>Grupo Madre / Madre Imobiliário</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1484,17 +1476,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>+351 213 461 024</t>
+          <t>+351 213 243 220</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>info@habitatinvest.pt</t>
+          <t>geral@madreimobiliario.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>habitatinvest.pt</t>
+          <t>madreimobiliario.com</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1509,22 +1501,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Rua da Moeda 4, 1200-275</t>
+          <t>Campo Grande 28, 11º, 1700-093</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15 projetos em desenvolvimento (Em construção) | ALMAR SOUTH LIVING (Almada) (Em construção/comercialização)</t>
+          <t>A-Living (Areeiro) (Planeamento) | Parque da Cidade (Setúbal) (Em construção)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Fundada 2001 · inclui Habitat Ventures/Project/Property/Broker</t>
+          <t>Presidente António Parente. Tel. móvel 914 070 350</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Luís Corrêa de Barros (fundador e CEO)</t>
+          <t>Nuno Dias (Diretor Geral da Madre Imobiliário· presidente do grupo é António Parente)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1533,7 +1525,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>J. Dias &amp; Dias</t>
+          <t>Habitat Invest</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1543,22 +1535,22 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>+351 214 422 593</t>
+          <t>+351 213 461 024</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>geral@jdiasdias.pt</t>
+          <t>info@habitatinvest.pt</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>jdiasdias.pt</t>
+          <t>habitatinvest.pt</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1568,27 +1560,31 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Av. Venceslau Balseiro da Grande Guerra, Quinta das Marianas, Parede</t>
+          <t>Rua da Moeda 4, 1200-275</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Urban Living (Carcavelos/Parede) (Comercialização)</t>
+          <t>15 projetos em desenvolvimento (Em construção) | ALMAR SOUTH LIVING (Almada) (Em construção/comercialização) | AURYA (Santo António dos Cavaleiros, Loures) (Em construção)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Fundada 1960, alvará ICC 12463. Tel. móvel 961 682 789</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>Fundada 2001 · inclui Habitat Ventures/Project/Property/Broker</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Luís Corrêa de Barros (fundador e CEO)</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>JPS Group</t>
+          <t>J. Dias &amp; Dias</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1598,22 +1594,22 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>+351 218 371 025</t>
+          <t>+351 214 422 593</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>secretariado@jpsgroup.pt</t>
+          <t>geral@jdiasdias.pt</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>jpsgroup.pt</t>
+          <t>jdiasdias.pt</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1623,35 +1619,27 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Av. Almirante Gago Coutinho 126</t>
+          <t>Av. Venceslau Balseiro da Grande Guerra, Quinta das Marianas, Parede</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>SkyCity (Carnaxide) (Em construção) | Herdade Real de Santiago (Comercialização) | Terraços de São Francisco (Comercialização)</t>
+          <t>Urban Living (Carcavelos/Parede) (Comercialização)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Promotora com construtora e imobiliária próprias</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>João Sousa (CEO)</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/joao-sousa-7802352a</t>
-        </is>
-      </c>
+          <t>Fundada 1960, alvará ICC 12463. Tel. móvel 961 682 789</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Krest Investments</t>
+          <t>JPS Group</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1661,17 +1649,17 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>+351 215 873 920</t>
+          <t>+351 218 371 025</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>info@krestinvestments.com</t>
+          <t>secretariado@jpsgroup.pt</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>krestinvestments.com</t>
+          <t>jpsgroup.pt</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1686,27 +1674,27 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Av. Eng.º Duarte Pacheco, Amoreiras Torre 1, piso 14, sala 2, 1070-101</t>
+          <t>Av. Almirante Gago Coutinho 126</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Lisboa / Porto / Algarve (Comercialização)</t>
+          <t>SkyCity (Carnaxide) (Em construção) | Herdade Real de Santiago (Comercialização) | Terraços de São Francisco (Comercialização)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Belga, em Portugal desde 2014</t>
+          <t>Promotora com construtora e imobiliária próprias</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Claude Kandiyoti (CEO)</t>
+          <t>João Sousa (CEO)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/claude-kandiyoti-287b9298/</t>
+          <t>https://pt.linkedin.com/in/joao-sousa-7802352a</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
@@ -1714,7 +1702,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Kronos Homes Portugal</t>
+          <t>Krest Investments</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1724,13 +1712,17 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>+351 211 227 710</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>+351 215 873 920</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>info@krestinvestments.com</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>kronoshomes.com</t>
+          <t>krestinvestments.com</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1745,27 +1737,27 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 245, 1250-143</t>
+          <t>Av. Eng.º Duarte Pacheco, Amoreiras Torre 1, piso 14, sala 2, 1070-101</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>The One (Lisboa) (Comercialização) | Lagos e Alcantarilha (Comercialização) | Flamingos Salgados (Comercialização) | Monte Santo (Carvoeiro) (Comercialização)</t>
+          <t>Lisboa / Porto / Algarve (Comercialização)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Entidade KIG Portugal (NIF 514667265)</t>
+          <t>Belga, em Portugal desde 2014</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Rui Meneses Ferreira (CEO)</t>
+          <t>Claude Kandiyoti (CEO)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rui-meneses-ferreira-97057825/</t>
+          <t>https://www.linkedin.com/in/claude-kandiyoti-287b9298/</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
@@ -1773,7 +1765,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Lantia</t>
+          <t>Kronos Homes Portugal</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1783,17 +1775,13 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>+351 211 165 360</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>geral@lantia.pt</t>
-        </is>
-      </c>
+          <t>+351 211 227 710</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>lantia.pt</t>
+          <t>kronoshomes.com</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1808,31 +1796,35 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Praça Duque de Saldanha 1, 4F, 1050-054</t>
+          <t>Av. da Liberdade 245, 1250-143</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Residencial e turístico Grande Lisboa (Em construção)</t>
+          <t>The One (Lisboa) (Comercialização) | Lagos e Alcantarilha (Comercialização) | Flamingos Salgados (Comercialização) | Monte Santo (Carvoeiro) (Comercialização)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Constituída em Macau 2015</t>
+          <t>Entidade KIG Portugal (NIF 514667265)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Eduardo Kol Netto de Almeida (CEO)</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>Rui Meneses Ferreira (CEO)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rui-meneses-ferreira-97057825/</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Libertas – Investimentos Imobiliários</t>
+          <t>Lantia</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1842,17 +1834,17 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>+351 213 243 050</t>
+          <t>+351 211 165 360</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>libertas@libertas.pt</t>
+          <t>geral@lantia.pt</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>libertas.pt</t>
+          <t>lantia.pt</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1867,22 +1859,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 129, 8º A, 1250-140</t>
+          <t>Praça Duque de Saldanha 1, 4F, 1050-054</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Lux Garden EVO (Faro) (Em construção) | Novos projetos Algarve (Planeamento)</t>
+          <t>Residencial e turístico Grande Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18 projetos no Algarve, &gt;800 unidades entregues · ISO 14001</t>
+          <t>Constituída em Macau 2015</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>António Gonçalves (Fundador)</t>
+          <t>Eduardo Kol Netto de Almeida (CEO)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
@@ -1891,7 +1883,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Major Development</t>
+          <t>Libertas – Investimentos Imobiliários</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1901,17 +1893,17 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>+351 210 912 130</t>
+          <t>+351 213 243 050</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>contacto@majordevelop.com</t>
+          <t>libertas@libertas.pt</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>majordevelop.com</t>
+          <t>libertas.pt</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1926,35 +1918,31 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Cais do Gás, Armazém H, 1200-109</t>
+          <t>Av. da Liberdade 129, 8º A, 1250-140</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Garden Cascais (Planeamento) | Solo Oeiras (Planeamento) | Vistabella (Oeiras) (Planeamento) | Santa Apolónia (Planeamento) | Nouveau Lisboa (Av. Berna) (Concluído)</t>
+          <t>Lux Garden EVO (Faro) (Em construção) | Novos projetos Algarve (Planeamento)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>&gt;100M€ anunciados 2026. Fonte: diarioimobiliario.pt</t>
+          <t>18 projetos no Algarve, &gt;800 unidades entregues · ISO 14001</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Costa (CEO, confiança baixa — só rocketreach)</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/gabriel-costa-7436b5158</t>
-        </is>
-      </c>
+          <t>António Gonçalves (Fundador)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Mesmo Valor (Mesmovalor, S.A.)</t>
+          <t>Major Development</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1964,56 +1952,60 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>+351 223 274 626</t>
+          <t>+351 210 912 130</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>geral@mesmovalor.pt</t>
+          <t>contacto@majordevelop.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>mesmovalor.pt</t>
+          <t>majordevelop.com</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Rua do Pinheiro Manso 147, 4100-412</t>
+          <t>Cais do Gás, Armazém H, 1200-109</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Boavista Tower (Comercialização)</t>
+          <t>Garden Cascais (Planeamento) | Solo Oeiras (Planeamento) | Vistabella (Oeiras) (Planeamento) | Santa Apolónia (Planeamento) | Nouveau Lisboa (Av. Berna) (Concluído)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€. Fonte: idealista/news ago/2026</t>
+          <t>&gt;100M€ anunciados 2026. Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Pedro Teixeira Paredes (CEO)</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>Gabriel Costa (CEO, confiança baixa — só rocketreach)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/gabriel-costa-7436b5158</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MEXTO Property Investment</t>
+          <t>Mesmo Valor (Mesmovalor, S.A.)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2023,60 +2015,56 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>+351 213 461 050</t>
+          <t>+351 223 274 626</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>info@mexto.pt</t>
+          <t>geral@mesmovalor.pt</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>mexto.pt</t>
+          <t>mesmovalor.pt</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Rua Nova do Almada 81, 4º Dto</t>
+          <t>Rua do Pinheiro Manso 147, 4100-412</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Castilho 3 (Em construção) | São Gens (Graça) (Em construção)</t>
+          <t>Boavista Tower (Comercialização)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Grupo suíço, 250M€ em Portugal, 71.000 m²</t>
+          <t>Capital social 5M€. Fonte: idealista/news ago/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Tomas Suter (Founding Member/Partner, Suíça)</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/tomas-suter-78564b9/</t>
-        </is>
-      </c>
+          <t>Pedro Teixeira Paredes (CEO)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Norfin</t>
+          <t>MEXTO Property Investment</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2086,13 +2074,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>+351 213 182 520</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>+351 213 461 050</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>info@mexto.pt</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>norfin.pt</t>
+          <t>mexto.pt</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2107,27 +2099,27 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Av. Almirante Gago Coutinho 30, piso 0, 1000-017</t>
+          <t>Rua Nova do Almada 81, 4º Dto</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Lisbon Heights (Alta de Lisboa) (Comercialização) | Lote Alta de Lisboa (Planeamento) | Oriente Green Campus / Campo Novo (Em construção)</t>
+          <t>Castilho 3 (Em construção) | São Gens (Graça) (Em construção)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Gestora de investimento (2,1B€) que também promove</t>
+          <t>Grupo suíço, 250M€ em Portugal, 71.000 m²</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Miguel Mateus (CEO, recém-nomeado)</t>
+          <t>Tomas Suter (Founding Member/Partner, Suíça)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/miguel-mateus-608b616/</t>
+          <t>https://www.linkedin.com/in/tomas-suter-78564b9/</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
@@ -2135,7 +2127,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Noronha Sanches</t>
+          <t>Norfin</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2145,17 +2137,13 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>+351 217 220 620</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>sales@noronhasanches.com</t>
-        </is>
-      </c>
+          <t>+351 213 182 520</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>noronhasanches.com</t>
+          <t>norfin.pt</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2170,27 +2158,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Campo Grande 28, 3º G, 1700-093</t>
+          <t>Av. Almirante Gago Coutinho 30, piso 0, 1000-017</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>One Lush (Caxias) (Em construção) | Vila Praia (Comercialização) | Marinha Prime (Comercialização)</t>
+          <t>Lisbon Heights (Alta de Lisboa) (Comercialização) | Lote Alta de Lisboa (Planeamento) | Oriente Green Campus / Campo Novo (Em construção)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Promotor desde 1986</t>
+          <t>Gestora de investimento (2,1B€) que também promove</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Pedro Sanches (CEO/fundador)</t>
+          <t>Miguel Mateus (CEO, recém-nomeado)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/pedro-sanches-77205825</t>
+          <t>https://www.linkedin.com/in/miguel-mateus-608b616/</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
@@ -2198,7 +2186,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Névoa, S.A.</t>
+          <t>Noronha Sanches</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2208,13 +2196,17 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>+351 253 240 010</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
+          <t>+351 217 220 620</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>sales@noronhasanches.com</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>nevoa.pt</t>
+          <t>noronhasanches.com</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2227,25 +2219,37 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Campo Grande 28, 3º G, 1700-093</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Portfólio nacional de empreendimentos (Comercialização)</t>
+          <t>One Lush (Caxias) (Em construção) | Vila Praia (Comercialização) | Marinha Prime (Comercialização)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com, racius.com</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>Promotor desde 1986</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Sanches (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/pedro-sanches-77205825</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Optylon Krea</t>
+          <t>Névoa, S.A.</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2255,17 +2259,13 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>+351 212 400 124</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>sales@optylonkrea.com</t>
-        </is>
-      </c>
+          <t>+351 253 240 010</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>optylonkrea.com</t>
+          <t>nevoa.pt</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2278,37 +2278,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 50, 10º/11º, 1250-096</t>
-        </is>
-      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Ando Living – Alfama Club e Liberdade Club (Em construção) | Augusta Townhouse + Santos Townhouse (Comercialização)</t>
+          <t>Portfólio nacional de empreendimentos (Comercialização)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1,7B€ investidos · PT e Turquia</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>William Tonnard (President &amp; COO· Chairman é Hakan Kodal)</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/william-tonnard/</t>
-        </is>
-      </c>
+          <t>Fonte: vidaimobiliaria.com, racius.com</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Qualive</t>
+          <t>Optylon Krea</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2318,44 +2306,60 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>+351 226 090 545</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>+351 212 400 124</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>sales@optylonkrea.com</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>optylonkrea.com</t>
+        </is>
+      </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Rua D. Pedro V 410, 2º, 4150-601</t>
+          <t>Rua Alexandre Herculano 50, 10º/11º, 1250-096</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Fábrica do Prado (Matosinhos) (Em construção)</t>
+          <t>Ando Living – Alfama Club e Liberdade Club (Em construção) | Augusta Townhouse + Santos Townhouse (Comercialização)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Telefone do registo comercial (einforma). Comercialização JLL/Predibisa</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>1,7B€ investidos · PT e Turquia</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>William Tonnard (President &amp; COO· Chairman é Hakan Kodal)</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-tonnard/</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Quest Capital</t>
+          <t>Qualive</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2365,60 +2369,44 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>+351 213 472 435</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>info@questcapital.eu</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>questcapital.eu</t>
-        </is>
-      </c>
+          <t>+351 226 090 545</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Rua António Maria Cardoso 2, 1200-027 (escritório Porto: Rua Fernandes Tomás 546)</t>
+          <t>Rua D. Pedro V 410, 2º, 4150-601</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Antas Atrium (Porto, antigo estádio) (Em construção)</t>
+          <t>Fábrica do Prado (Matosinhos) (Em construção)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Com Tikehau Capital. &gt;1B€ sob gestão</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Carlos Vasconcellos (Founding Partner, CEO exato não confirmado)</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/vasconcelloscarlos/</t>
-        </is>
-      </c>
+          <t>Telefone do registo comercial (einforma). Comercialização JLL/Predibisa</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ReVentures – Property Developers</t>
+          <t>Quest Capital</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2428,17 +2416,17 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>+351 212 402 489</t>
+          <t>+351 213 472 435</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>info@reventures.pt</t>
+          <t>info@questcapital.eu</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>reventures.pt</t>
+          <t>questcapital.eu</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2453,27 +2441,27 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Campo Grande 28, 3º A, 1700-093</t>
+          <t>Rua António Maria Cardoso 2, 1200-027 (escritório Porto: Rua Fernandes Tomás 546)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7 residências de estudantes (rede nacional) (Em construção) | Senior Living (Planeamento)</t>
+          <t>Antas Atrium (Porto, antigo estádio) (Em construção)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>NIF 516390350, capital 800k€. Fonte: construir.pt abr/2026</t>
+          <t>Com Tikehau Capital. &gt;1B€ sob gestão</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Hugo Gonçalves Pereira (CEO)</t>
+          <t>Carlos Vasconcellos (Founding Partner, CEO exato não confirmado)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hugogpereira/</t>
+          <t>https://www.linkedin.com/in/vasconcelloscarlos/</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
@@ -2481,7 +2469,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Rio Capital / Grupo Rio</t>
+          <t>ReVentures – Property Developers</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2491,17 +2479,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>+351 213 861 065</t>
+          <t>+351 212 402 489</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>geral@riocapital.pt</t>
+          <t>info@reventures.pt</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>riocapital.pt</t>
+          <t>reventures.pt</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2516,27 +2504,35 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Av. Duarte Pacheco, Amoreiras Torre 2, 14º D</t>
+          <t>Campo Grande 28, 3º A, 1700-093</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21 projetos residenciais Grande Porto (Em construção) | Velaris (Porto) (Planeamento) | São Vicente (Maia) (Planeamento) | Metropólis Estúdio Residence (Matosinhos) (Planeamento)</t>
+          <t>7 residências de estudantes (rede nacional) (Em construção) | Senior Living (Planeamento)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Grupo nascido em Monção, liderado por Nuno Afonso. Fonte: idealista/news jun/2026, Público</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>NIF 516390350, capital 800k€. Fonte: construir.pt abr/2026</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Gonçalves Pereira (CEO)</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hugogpereira/</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Rockbuilding – Soluções Imobiliárias</t>
+          <t>Rio Capital / Grupo Rio</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2546,13 +2542,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>+351 217 996 700</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>+351 213 861 065</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>geral@riocapital.pt</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>rockbuilding.com</t>
+          <t>riocapital.pt</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2567,35 +2567,27 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, 7º A, 1070-374</t>
+          <t>Av. Duarte Pacheco, Amoreiras Torre 2, 14º D</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Serviços de desenvolvimento para promotores (Em construção)</t>
+          <t>21 projetos residenciais Grande Porto (Em construção) | Velaris (Porto) (Planeamento) | São Vicente (Maia) (Planeamento) | Metropólis Estúdio Residence (Matosinhos) (Planeamento)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>ATENÇÃO: é gestor de projeto/serviços, não promotor puro</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>José Pedro Almeida Guerra (Diretor Geral)</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/josé-pedro-almeida-guerra-20723679</t>
-        </is>
-      </c>
+          <t>Grupo nascido em Monção, liderado por Nuno Afonso. Fonte: idealista/news jun/2026, Público</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Royal Ventures</t>
+          <t>Rockbuilding – Soluções Imobiliárias</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2605,52 +2597,48 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>+351 916 770 322</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>alex@royal-ventures.com</t>
-        </is>
-      </c>
+          <t>+351 217 996 700</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>royal-ventures.com</t>
+          <t>rockbuilding.com</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Edifício Oceanus, Av. da Boavista 3227, 4100-137</t>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, 7º A, 1070-374</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação centro histórico do Porto (Em construção)</t>
+          <t>Serviços de desenvolvimento para promotores (Em construção)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
+          <t>ATENÇÃO: é gestor de projeto/serviços, não promotor puro</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Udi Yadin (fundador/General Partner)</t>
+          <t>José Pedro Almeida Guerra (Diretor Geral)</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/udiyadin/</t>
+          <t>https://pt.linkedin.com/in/josé-pedro-almeida-guerra-20723679</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
@@ -2658,7 +2646,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Sharp Developers</t>
+          <t>Royal Ventures</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2668,17 +2656,17 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>+351 933 078 094</t>
+          <t>+351 916 770 322</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>info@sharpdevelopers.pt</t>
+          <t>alex@royal-ventures.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sharpdevelopers.pt</t>
+          <t>royal-ventures.com</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2693,27 +2681,27 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
+          <t>Edifício Oceanus, Av. da Boavista 3227, 4100-137</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Residencial de luxo Porto (Em construção)</t>
+          <t>Reabilitação centro histórico do Porto (Em construção)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>CEO Carla Luís</t>
+          <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Carla Luís (CEO/cofundadora)</t>
+          <t>Udi Yadin (fundador/General Partner)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/carla-luís-b14a7616/</t>
+          <t>https://www.linkedin.com/in/udiyadin/</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
@@ -2721,7 +2709,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SILCOGE / Grupo SIL</t>
+          <t>Sharp Developers</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2731,52 +2719,52 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>+351 210 124 500</t>
+          <t>+351 933 078 094</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>info@sil.pt</t>
+          <t>info@sharpdevelopers.pt</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sil.pt</t>
+          <t>sharpdevelopers.pt</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
+          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Grande Lisboa (Em construção)</t>
+          <t>Residencial de luxo Porto (Em construção)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Promoção imobiliária desde 1949</t>
+          <t>CEO Carla Luís</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Pedro Silveira (acionista maioritário/ex-Chairman, destituído judicialmente mai/2025, em recurso)</t>
+          <t>Carla Luís (CEO/cofundadora)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pedro-silveira-88822a20/</t>
+          <t>https://www.linkedin.com/in/carla-luís-b14a7616/</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
@@ -2784,7 +2772,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SOLYD Property Developers</t>
+          <t>SILCOGE / Grupo SIL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2794,22 +2782,22 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>+351 211 214 926</t>
+          <t>+351 210 124 500</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>info@elou-solyd.pt</t>
+          <t>info@sil.pt</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>solyd.pt</t>
+          <t>sil.pt</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2819,27 +2807,27 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
+          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Luz Altear (Alta de Lisboa) (Em construção)</t>
+          <t>Grande Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
+          <t>Promoção imobiliária desde 1949</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Gonçalo Cadete (CEO)</t>
+          <t>Pedro Silveira (acionista maioritário/ex-Chairman, destituído judicialmente mai/2025, em recurso)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gon%C3%A7alo-cadete-260692/</t>
+          <t>https://www.linkedin.com/in/pedro-silveira-88822a20/</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
@@ -2847,7 +2835,7 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Stone Capital</t>
+          <t>SOLYD Property Developers</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2857,22 +2845,22 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>+351 210 416 350</t>
+          <t>+351 211 214 926</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>info@stonecapital.pt</t>
+          <t>info@elou-solyd.pt</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>stonecapital.pt</t>
+          <t>solyd.pt</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2882,31 +2870,35 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 240, 1250-096</t>
+          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
+          <t>Luz Altear (Alta de Lisboa) (Em construção) | ÉLOU (Santo António dos Cavaleiros, Loures) (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Tel. móvel 965 915 993</t>
+          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Geoffroy Moreno (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>Gonçalo Cadete (CEO)</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gon%C3%A7alo-cadete-260692/</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Teixeira Duarte Real Estate</t>
+          <t>Stone Capital</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2916,22 +2908,22 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>+351 217 912 300</t>
+          <t>+351 210 416 350</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>info@tdimobiliaria.pt</t>
+          <t>info@stonecapital.pt</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>tdimobiliaria.pt</t>
+          <t>stonecapital.pt</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2941,27 +2933,31 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
+          <t>Av. da Liberdade 240, 1250-096</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
+          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do grupo Teixeira Duarte</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
+          <t>Tel. móvel 965 915 993</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Geoffroy Moreno (Co-Founder)</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Thomas &amp; Piron Portugal</t>
+          <t>Teixeira Duarte Real Estate</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2971,60 +2967,52 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>+351 214 422 464</t>
+          <t>+351 217 912 300</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>infopt@thomas-piron.eu</t>
+          <t>info@tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>thomas-piron.pt</t>
+          <t>tdimobiliaria.pt</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Escritórios em Matosinhos e Sacavém</t>
+          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
+          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>David Carreira (Diretor Geral/Country Manager)</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>https://lu.linkedin.com/in/david-carreira-a4082050</t>
-        </is>
-      </c>
+          <t>Braço imobiliário do grupo Teixeira Duarte</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Properties</t>
+          <t>Thomas &amp; Piron Portugal</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3034,52 +3022,52 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>+351 215 814 094</t>
+          <t>+351 214 422 464</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>info@vangproperties.com</t>
+          <t>infopt@thomas-piron.eu</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>vangproperties.com</t>
+          <t>thomas-piron.pt</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
+          <t>Escritórios em Matosinhos e Sacavém</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
+          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
+          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Henrique Rodrigues da Silva (CEO desde fev/2026)</t>
+          <t>David Carreira (Diretor Geral/Country Manager)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/henrique-rodrigues-da-silva-b396643/</t>
+          <t>https://lu.linkedin.com/in/david-carreira-a4082050</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -3087,7 +3075,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>VIC Properties</t>
+          <t>Vanguard Properties</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3097,17 +3085,17 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>+351 219 347 112</t>
+          <t>+351 215 814 094</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>info@vic-properties.com</t>
+          <t>info@vangproperties.com</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>vic-properties.com</t>
+          <t>vangproperties.com</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -3122,27 +3110,27 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Portefólio &gt;3B€. Fundada 2018</t>
+          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>João Cabaça (Co-fundador e CEO)</t>
+          <t>Henrique Rodrigues da Silva (CEO desde fev/2026)</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/jo%C3%A3o-caba%C3%A7a-6b293614b</t>
+          <t>https://www.linkedin.com/in/henrique-rodrigues-da-silva-b396643/</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
@@ -3150,168 +3138,188 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>VIC Properties</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>+351 219 347 112</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>info@vic-properties.com</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>vic-properties.com</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Portefólio &gt;3B€. Fundada 2018</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>João Cabaça (Co-fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/jo%C3%A3o-caba%C3%A7a-6b293614b</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>Vogue Homes</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>+351 213 461 246</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>comercial@vogue-homes.com</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>vogue-homes.com</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Rua Luz Soriano 15, 1200-246</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Dafundo 24 (Comercialização) | Bom Sucesso (Comercialização) | Westhouse (Cascais) (Comercialização)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>NIF 510933084. Tel. móvel 913 385 846</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Joaquim Lico (CEO)</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/joaquim-lico-4383239/</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>AFA (Grupo AFA)</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>YARD Properties</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>Savoy Residence D'Ávila (Em construção)</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: diarioimobiliario.pt</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Victor de Sousa (Diretor-Geral AFA Real Estate)</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Alecrim Real Estate (Lince Capital)</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>lince-capital.com</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>+351 918 888 353</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>sales@355outubro.com</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>yardproperties.pt</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>355 Outubro (Av. 5 de Outubro, Lisboa) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Grupo israelita liderado por David Rabbi. Telefone é da linha comercial do projeto 355 Outubro</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>David Rabbi (fundador)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Arts Investments, SA</t>
+          <t>AFA (Grupo AFA)</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3321,11 +3329,7 @@
       </c>
       <c r="C48" s="7" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>artsinvestments.com</t>
-        </is>
-      </c>
+      <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -3339,22 +3343,26 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>3 projetos em curso (nomes não encontrados) (Em construção/desenvolvimento)</t>
+          <t>Savoy Residence D'Ávila (Em construção)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr"/>
+          <t>Fonte: diarioimobiliario.pt</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Victor de Sousa (Diretor-Geral AFA Real Estate)</t>
+        </is>
+      </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Ceetrus / Nhood Portugal</t>
+          <t>Alecrim Real Estate (Lince Capital)</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -3364,7 +3372,11 @@
       </c>
       <c r="C49" s="7" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>lince-capital.com</t>
+        </is>
+      </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -3372,28 +3384,40 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Pipeline nacional 15 cidades (nomes não encontrados) (Planeamento)</t>
+          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr"/>
+          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
+        </is>
+      </c>
       <c r="M49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
+          <t>Arts Investments, SA</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -3403,40 +3427,40 @@
       </c>
       <c r="C50" s="7" t="inlineStr"/>
       <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>artsinvestments.com</t>
+        </is>
+      </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Fábrica Vilar (Em desenvolvimento)</t>
+          <t>3 projetos em curso (nomes não encontrados) (Em construção/desenvolvimento)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Fonte: viva-porto.pt</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
-        </is>
-      </c>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Fortera</t>
+          <t>Ceetrus / Nhood Portugal</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3449,41 +3473,33 @@
       <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Porto / Gaia</t>
-        </is>
-      </c>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
+          <t>Pipeline nacional 15 cidades (nomes não encontrados) (Planeamento)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -3493,39 +3509,31 @@
       </c>
       <c r="C52" s="7" t="inlineStr"/>
       <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>hines.com</t>
-        </is>
-      </c>
+      <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
+          <t>Fábrica Vilar (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Gestora global · sem contacto PT publicado</t>
+          <t>Fonte: viva-porto.pt</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
+          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
@@ -3534,7 +3542,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Fortera</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -3544,35 +3552,35 @@
       </c>
       <c r="C53" s="7" t="inlineStr"/>
       <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>imolote.pt</t>
-        </is>
-      </c>
+      <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Porto / Gaia</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
+          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
+          <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
+          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
@@ -3581,7 +3589,7 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3591,31 +3599,39 @@
       </c>
       <c r="C54" s="7" t="inlineStr"/>
       <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>hines.com</t>
+        </is>
+      </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
+          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Gestora global · sem contacto PT publicado</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
@@ -3624,7 +3640,7 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>KKR Imo, S.A.</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -3634,31 +3650,35 @@
       </c>
       <c r="C55" s="7" t="inlineStr"/>
       <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
+          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
@@ -3667,7 +3687,7 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Overseas</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3680,45 +3700,37 @@
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Pedro Vicente (CEO)</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
-        </is>
-      </c>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3731,28 +3743,28 @@
       <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
+          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>Nuno Cunha (Managing Director)</t>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr"/>
@@ -3761,7 +3773,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Overseas</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3784,31 +3796,35 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
+          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/site publicados (APPII)</t>
+          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Federico Rosales (cofundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr"/>
+          <t>Pedro Vicente (CEO)</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
+        </is>
+      </c>
       <c r="M58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>RAR Imobiliária</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -3832,17 +3848,17 @@
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
+          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Paula Fernandes (CEO)</t>
+          <t>Nuno Cunha (Managing Director)</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr"/>
@@ -3851,7 +3867,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>Prime Portugal</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3864,33 +3880,41 @@
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
+        </is>
+      </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>RM Villas (Início obra 1T2026)</t>
+          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr"/>
+          <t>Sem telefone/site publicados (APPII)</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Federico Rosales (cofundador e CEO)</t>
+        </is>
+      </c>
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>RAR Imobiliária</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3900,39 +3924,31 @@
       </c>
       <c r="C61" s="7" t="inlineStr"/>
       <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>roundhillcapital.com</t>
-        </is>
-      </c>
+      <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>Rua da Escola Politécnica 38, 1250-102</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone PT publicado</t>
+          <t>Fonte: dinheirovivo.pt, construir.pt</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
+          <t>Paula Fernandes (CEO)</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr"/>
@@ -3941,7 +3957,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Screendomus (Grupo Teixeira)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3950,19 +3966,11 @@
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>geral@screendomus.com</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>screendomus.com</t>
-        </is>
-      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -3973,26 +3981,22 @@
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Altus (Alta de Lisboa) (Em construção)</t>
+          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
-        </is>
-      </c>
+          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr"/>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4005,7 +4009,7 @@
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -4016,12 +4020,12 @@
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>RM Villas (Início obra 1T2026)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr"/>
@@ -4031,7 +4035,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>United Investments Portugal (UIP)</t>
+          <t>Round Hill Capital</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4043,7 +4047,7 @@
       <c r="D64" s="5" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>uip.pt</t>
+          <t>roundhillcapital.com</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -4058,35 +4062,31 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Rua da Escola Politécnica 38, 1250-102</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Fundada 1985 · sem telefone publicado</t>
+          <t>Sem telefone PT publicado</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>Carlos Leal (CEO)</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
-        </is>
-      </c>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+          <t>Screendomus (Grupo Teixeira)</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -4095,10 +4095,14 @@
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr"/>
-      <c r="D65" s="5" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>geral@screendomus.com</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>grupovisabeira.com</t>
+          <t>screendomus.com</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4114,30 +4118,26 @@
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Areeiro Select (Comercialização)</t>
+          <t>Altus (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
-        </is>
-      </c>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -4146,57 +4146,45 @@
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>shaluinvest.pt</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+          <t>Fundador e Managing Director: Itai Fridman</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>Fernando Vasco Costa (CEO)</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
-        </is>
-      </c>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4205,19 +4193,11 @@
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>info@ancora-inv.com</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>ancora-inv.com</t>
-        </is>
-      </c>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -4228,274 +4208,242 @@
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
+          <t>Verde Vale (Em construção)</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>United Investments Portugal (UIP)</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>uip.pt</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Fundada 1985 · sem telefone publicado</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Leal (CEO)</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>grupovisabeira.com</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Areeiro Select (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>VIZTA (ex-Nexity Portugal)</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>info@ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Antrix</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>info@antrix.pt</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>antrix.pt</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Arish Capital Partners</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>arishcapitalpartners.com</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Grândola</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Fonte: diarioimobiliario.pt</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Carvoeiro Branco – Propriedades</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>info@carvoeirobranco.com</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>carvoeirobranco.com</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Erik de Vlieger (CEO)</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+      <c r="M71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -4505,56 +4453,60 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
+          <t>900 264 096 (ES)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>casais@casais.pt</t>
+          <t>info@aedashomes.com</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr"/>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
+        </is>
+      </c>
       <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -4564,52 +4516,52 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>info@antrix.pt</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
@@ -4617,7 +4569,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -4627,52 +4579,44 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>info@civilria.pt</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
@@ -4680,7 +4624,7 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4690,48 +4634,60 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>+351 917 498 714</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>info@carvoeirobranco.com</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr"/>
+          <t>Erik de Vlieger (CEO)</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+        </is>
+      </c>
       <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4741,56 +4697,56 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+          <t>+351 253 305 490</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>casais@casais.pt</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
-        </is>
-      </c>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4800,56 +4756,60 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
+          <t>+351 253 461 462</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>geral@garcia.pt</t>
+          <t>geral@castro-group.pt</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
+          <t>Paulo Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4859,52 +4819,52 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
+          <t>+351 234 480 570</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>aca@grupo-aca.com</t>
+          <t>info@civilria.pt</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
+          <t>Artur Varum (CEO)</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
@@ -4912,7 +4872,7 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4922,47 +4882,39 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
-        </is>
-      </c>
+          <t>+351 253 089 932</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
+          <t>Guimarães</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
-        </is>
-      </c>
+      <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+          <t>Diogo Baptista Antunes (CEO)</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr"/>
@@ -4971,7 +4923,7 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4981,52 +4933,48 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>geral@arliz.co</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
+          <t>Reinaldo Teixeira (Administrador)</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
@@ -5034,7 +4982,7 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -5044,43 +4992,47 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>+351 253 560 230</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>geral@garcia.pt</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
@@ -5089,7 +5041,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5099,44 +5051,52 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>+351 252 308 250</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>aca@grupo-aca.com</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Vila Nova de Famalicão</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
@@ -5144,7 +5104,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5154,47 +5114,47 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
+          <t>+351 253 685 109</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>geral@jhomea.pt</t>
+          <t>acrescentar@grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr"/>
@@ -5203,7 +5163,7 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5213,17 +5173,17 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 253 105 331</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>info@pinehill.pt</t>
+          <t>geral@arliz.co</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -5236,25 +5196,29 @@
           <t>Braga</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
+        </is>
+      </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
+          <t>Domingos Correia (CEO)</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -5262,7 +5226,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5272,60 +5236,52 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>info@quintadolago.com</t>
-        </is>
-      </c>
+          <t>273 332 784 (confirmar)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Almancil</t>
+          <t>Parque Empresarial A32, Vila Maior</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5335,18 +5291,18 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
+          <t>+351 913 470 147</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5357,26 +5313,30 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5386,52 +5346,56 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr"/>
+          <t>+351 934 175 642</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+        </is>
+      </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>José Miguel Afonso (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5441,47 +5405,43 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr"/>
@@ -5490,7 +5450,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5500,298 +5460,390 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
+          <t>+351 910 936 732</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>info@pinehill.pt</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Pinheiro (fundador)</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Quinta do Lago Resort</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>+351 289 390 700</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>quintadolago.com</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Resort residencial/golfe</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Royal Prime</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>royalprime.pt</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Covilhã</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Salk Properties Portugal</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>+351 939 443 765</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>salkproperties.com</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Scale Property Development</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>+351 219 362 960</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>scalepropertydevelopment.com</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>tps.com.pt</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
           <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>Fonte: omirante.pt</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr"/>
-      <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr"/>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K90" s="5" t="inlineStr"/>
-      <c r="L90" s="5" t="inlineStr"/>
-      <c r="M90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr"/>
-      <c r="D91" s="5" t="inlineStr"/>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa/Grândola/Lagoa</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="L91" s="5" t="inlineStr"/>
-      <c r="M91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Aresta Vitalicia</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr"/>
-      <c r="D92" s="5" t="inlineStr"/>
-      <c r="E92" s="5" t="inlineStr"/>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>WeBuild Castelo (Comercialização)</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K92" s="5" t="inlineStr"/>
-      <c r="L92" s="5" t="inlineStr"/>
-      <c r="M92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Arrow Global Portugal</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr"/>
-      <c r="D93" s="5" t="inlineStr"/>
-      <c r="E93" s="5" t="inlineStr"/>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>The Shore Residences (Comercialização)</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
-      <c r="L93" s="5" t="inlineStr"/>
-      <c r="M93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Baltor – Engenharia e Construção</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr"/>
-      <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: ominho.pt</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="inlineStr">
-        <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
-      <c r="L94" s="5" t="inlineStr"/>
-      <c r="M94" s="5" t="inlineStr"/>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Branco Real Estate</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr"/>
-      <c r="D95" s="5" t="inlineStr"/>
-      <c r="E95" s="5" t="inlineStr"/>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Lagos</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Domus (Em construção)</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="inlineStr"/>
-      <c r="L95" s="5" t="inlineStr"/>
-      <c r="M95" s="5" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -5801,11 +5853,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr"/>
       <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Tavira</t>
@@ -5819,12 +5867,12 @@
       <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr"/>
@@ -5834,7 +5882,7 @@
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -5847,33 +5895,37 @@
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
       <c r="L97" s="5" t="inlineStr"/>
       <c r="M97" s="5" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5886,23 +5938,23 @@
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr"/>
@@ -5912,7 +5964,7 @@
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -5922,40 +5974,40 @@
       </c>
       <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="5" t="inlineStr"/>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="L99" s="5" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -5965,36 +6017,44 @@
       </c>
       <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="5" t="inlineStr"/>
-      <c r="E100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L100" s="5" t="inlineStr"/>
       <c r="M100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6007,7 +6067,7 @@
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -6018,30 +6078,22 @@
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr"/>
+      <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6054,37 +6106,33 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="5" t="inlineStr"/>
       <c r="M102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6094,40 +6142,40 @@
       </c>
       <c r="C103" s="7" t="inlineStr"/>
       <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr"/>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="inlineStr">
-        <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
+          <t>Fonte: boavistaoceantavira.com</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr"/>
       <c r="L103" s="5" t="inlineStr"/>
       <c r="M103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6137,44 +6185,36 @@
       </c>
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K104" s="5" t="inlineStr">
-        <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
-        </is>
-      </c>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr"/>
       <c r="L104" s="5" t="inlineStr"/>
       <c r="M104" s="5" t="inlineStr"/>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6187,37 +6227,33 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: diariocoimbra.pt</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr"/>
       <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6227,26 +6263,30 @@
       </c>
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
+          <t>Fonte: brainsre.news</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr"/>
@@ -6256,7 +6296,7 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6269,23 +6309,23 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
+          <t>Fonte: remax.pt, tavitel.pt</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -6295,7 +6335,7 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6308,33 +6348,41 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
-        </is>
-      </c>
-      <c r="K108" s="5" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M108" s="5" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6344,40 +6392,40 @@
       </c>
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr"/>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>Aristides Alferes (administrador)</t>
+        </is>
+      </c>
       <c r="L109" s="5" t="inlineStr"/>
       <c r="M109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6387,35 +6435,31 @@
       </c>
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr"/>
@@ -6424,7 +6468,7 @@
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6436,38 +6480,42 @@
       <c r="D111" s="5" t="inlineStr"/>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>explorerinvestments.com</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="L111" s="5" t="inlineStr"/>
       <c r="M111" s="5" t="inlineStr"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6480,33 +6528,37 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
-        </is>
-      </c>
-      <c r="K112" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L112" s="5" t="inlineStr"/>
       <c r="M112" s="5" t="inlineStr"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6516,36 +6568,36 @@
       </c>
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr"/>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr"/>
-      <c r="G113" s="7" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr"/>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Loulé (Vilamoura)</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="inlineStr"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6555,44 +6607,36 @@
       </c>
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
+      <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr"/>
       <c r="L114" s="5" t="inlineStr"/>
       <c r="M114" s="5" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6605,37 +6649,33 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr">
-        <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
-        </is>
-      </c>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr"/>
       <c r="L115" s="5" t="inlineStr"/>
       <c r="M115" s="5" t="inlineStr"/>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6645,44 +6685,40 @@
       </c>
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr"/>
-      <c r="E116" s="5" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>genuinoinvestments.com</t>
+        </is>
+      </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L116" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Fonte: genuinoinvestments.com</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr"/>
+      <c r="L116" s="5" t="inlineStr"/>
       <c r="M116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6694,38 +6730,42 @@
       <c r="D117" s="5" t="inlineStr"/>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>grupomaisempresas.pt</t>
+          <t>ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L117" s="5" t="inlineStr"/>
       <c r="M117" s="5" t="inlineStr"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6737,42 +6777,38 @@
       <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>gruponbportugal.pt</t>
+          <t>glowing.pt</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr"/>
       <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -6782,14 +6818,10 @@
       </c>
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>pestana.com</t>
-        </is>
-      </c>
+      <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -6800,26 +6832,22 @@
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr"/>
       <c r="L119" s="5" t="inlineStr"/>
       <c r="M119" s="5" t="inlineStr"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -6831,38 +6859,34 @@
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>Mealhada (projeto em Coimbra)</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr"/>
+      <c r="G120" s="7" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr"/>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
+        </is>
+      </c>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -6874,38 +6898,42 @@
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>andrejordangroup.pt</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -6918,33 +6946,37 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="inlineStr"/>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
       <c r="L122" s="5" t="inlineStr"/>
       <c r="M122" s="5" t="inlineStr"/>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -6954,40 +6986,36 @@
       </c>
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>Igor Castro (CEO)</t>
+          <t>Carlos Silva Neves (administrador)</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr"/>
@@ -6995,7 +7023,7 @@
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7007,42 +7035,38 @@
       <c r="D124" s="5" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr"/>
       <c r="L124" s="5" t="inlineStr"/>
       <c r="M124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7052,31 +7076,35 @@
       </c>
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>gruponbportugal.pt</t>
+        </is>
+      </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
+          <t>Fonte: gruponb.pt</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+          <t>Ioav Blanche (presidente)</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr"/>
@@ -7085,7 +7113,7 @@
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7095,36 +7123,44 @@
       </c>
       <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>pestana.com</t>
+        </is>
+      </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K126" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7136,42 +7172,38 @@
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>maveninvest.pt</t>
+          <t>hillside.pt</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, hillside.pt</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr"/>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7183,46 +7215,38 @@
       <c r="D128" s="5" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>mellordc.pt</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L128" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr"/>
+      <c r="L128" s="5" t="inlineStr"/>
       <c r="M128" s="5" t="inlineStr"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7235,7 +7259,7 @@
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -7246,12 +7270,12 @@
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr"/>
@@ -7261,7 +7285,7 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7271,40 +7295,48 @@
       </c>
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>jpaiva.pt</t>
+        </is>
+      </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
-      <c r="L130" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7316,38 +7348,42 @@
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>oconnormurphy.ie</t>
+          <t>luxpremium.net</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
-        </is>
-      </c>
-      <c r="K131" s="5" t="inlineStr"/>
+          <t>Fonte: luxpremium.net</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="L131" s="5" t="inlineStr"/>
       <c r="M131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7357,14 +7393,10 @@
       </c>
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>ombria.com</t>
-        </is>
-      </c>
+      <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -7372,37 +7404,29 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+      <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+          <t>Fonte: oconnormurphy.ie</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L132" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7415,23 +7439,23 @@
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr"/>
@@ -7441,7 +7465,7 @@
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7451,10 +7475,14 @@
       </c>
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -7465,17 +7493,17 @@
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+          <t>Fonte: maveninvest.pt</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
         <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+          <t>Yehonatan Gourvitch (CEO)</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr"/>
@@ -7484,7 +7512,7 @@
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7494,36 +7522,48 @@
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr"/>
-      <c r="L135" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M135" s="5" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7536,23 +7576,23 @@
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: ireland-portugal.com</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr"/>
@@ -7562,7 +7602,7 @@
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7575,28 +7615,28 @@
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+          <t>Matan Amitai (co-fundador)</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr"/>
@@ -7605,7 +7645,7 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7617,12 +7657,12 @@
       <c r="D138" s="5" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>rodriguesevermelho.com</t>
+          <t>oconnormurphy.ie</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -7633,26 +7673,22 @@
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr"/>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7664,38 +7700,42 @@
       <c r="D139" s="5" t="inlineStr"/>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>soccal-vaz.com</t>
+          <t>ombria.com</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
         </is>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
         </is>
       </c>
       <c r="M139" s="5" t="inlineStr"/>
@@ -7703,7 +7743,7 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7713,48 +7753,36 @@
       </c>
       <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>solidsentinel.pt</t>
-        </is>
-      </c>
+      <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
-        </is>
-      </c>
+          <t>Fonte: ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7767,33 +7795,37 @@
       <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L141" s="5" t="inlineStr"/>
       <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -7803,44 +7835,36 @@
       </c>
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>sonaesierra.com</t>
-        </is>
-      </c>
+      <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr"/>
       <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -7850,14 +7874,10 @@
       </c>
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>southshoreinvest.com</t>
-        </is>
-      </c>
+      <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
@@ -7868,12 +7888,12 @@
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr"/>
@@ -7883,7 +7903,7 @@
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -7893,35 +7913,31 @@
       </c>
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>squareview.pt</t>
-        </is>
-      </c>
+      <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr"/>
@@ -7930,7 +7946,7 @@
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -7940,10 +7956,14 @@
       </c>
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr"/>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>rodriguesevermelho.com</t>
+        </is>
+      </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -7954,22 +7974,26 @@
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K145" s="5" t="inlineStr"/>
+          <t>Fonte: sava.pt, thepreplan.com</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
       <c r="L145" s="5" t="inlineStr"/>
       <c r="M145" s="5" t="inlineStr"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -7979,10 +8003,14 @@
       </c>
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr"/>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>soccal-vaz.com</t>
+        </is>
+      </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -7993,22 +8021,30 @@
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K146" s="5" t="inlineStr"/>
-      <c r="L146" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>António Vaz (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+        </is>
+      </c>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8020,42 +8056,46 @@
       <c r="D147" s="5" t="inlineStr"/>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>ugp.ie</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
-      <c r="L147" s="5" t="inlineStr"/>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M147" s="5" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8065,35 +8105,336 @@
       </c>
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>vilagale.com</t>
-        </is>
-      </c>
+      <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr"/>
       <c r="L148" s="5" t="inlineStr"/>
       <c r="M148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Sonae Sierra</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr"/>
+      <c r="D149" s="5" t="inlineStr"/>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>sonaesierra.com</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa/Porto</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Pulse Lisboa (Em construção)</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: rtp.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr"/>
+      <c r="M149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="30" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Southshore Investments</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr"/>
+      <c r="D150" s="5" t="inlineStr"/>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>southshoreinvest.com</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>Almada</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr"/>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Tejo City District (Planeamento)</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: southshoreinvest.com</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr"/>
+      <c r="L150" s="5" t="inlineStr"/>
+      <c r="M150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Square View</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr"/>
+      <c r="D151" s="5" t="inlineStr"/>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa/Ericeira/Melides</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr"/>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr"/>
+      <c r="M151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Terrace Benefit, Lda</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr"/>
+      <c r="D152" s="5" t="inlineStr"/>
+      <c r="E152" s="5" t="inlineStr"/>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>Loulé (Quarteira)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr"/>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Forte Novo (Em construção)</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: racius.com, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr"/>
+      <c r="L152" s="5" t="inlineStr"/>
+      <c r="M152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Udra – Grupo San José</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr"/>
+      <c r="D153" s="5" t="inlineStr"/>
+      <c r="E153" s="5" t="inlineStr"/>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr"/>
+      <c r="L153" s="5" t="inlineStr"/>
+      <c r="M153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Urban Green Private (UGP)</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr"/>
+      <c r="D154" s="5" t="inlineStr"/>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>ugp.ie</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>The Shipyard (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr"/>
+      <c r="M154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr"/>
+      <c r="D155" s="5" t="inlineStr"/>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr"/>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr"/>
+      <c r="L155" s="5" t="inlineStr"/>
+      <c r="M155" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8135,7 +8476,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
@@ -8145,7 +8486,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -8155,7 +8496,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -8165,7 +8506,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -8175,7 +8516,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M155" headerRowCount="1">
-  <autoFilter ref="A1:M155"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M156" headerRowCount="1">
+  <autoFilter ref="A1:M156"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3773,7 +3773,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Overseas</t>
+          <t>Neptune Developments</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3783,10 +3783,14 @@
       </c>
       <c r="C58" s="7" t="inlineStr"/>
       <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>neptune-developments.com</t>
+        </is>
+      </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -3794,37 +3798,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
-        </is>
-      </c>
+      <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+          <t>BellaMary (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>Pedro Vicente (CEO)</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
-        </is>
-      </c>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Overseas</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -3837,37 +3829,45 @@
       <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
+          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Nuno Cunha (Managing Director)</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr"/>
+          <t>Pedro Vicente (CEO)</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
+        </is>
+      </c>
       <c r="M59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3880,32 +3880,28 @@
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/site publicados (APPII)</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>Federico Rosales (cofundador e CEO)</t>
+          <t>Nuno Cunha (Managing Director)</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr"/>
@@ -3914,7 +3910,7 @@
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>RAR Imobiliária</t>
+          <t>Prime Portugal</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3927,28 +3923,32 @@
       <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
+          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+          <t>Sem telefone/site publicados (APPII)</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>Paula Fernandes (CEO)</t>
+          <t>Federico Rosales (cofundador e CEO)</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr"/>
@@ -3957,7 +3957,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>RAR Imobiliária</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3970,33 +3970,37 @@
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
+          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr"/>
+          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Paula Fernandes (CEO)</t>
+        </is>
+      </c>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4009,23 +4013,23 @@
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>RM Villas (Início obra 1T2026)</t>
+          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr"/>
@@ -4035,7 +4039,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4045,48 +4049,36 @@
       </c>
       <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>roundhillcapital.com</t>
-        </is>
-      </c>
+      <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>Rua da Escola Politécnica 38, 1250-102</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+          <t>RM Villas (Início obra 1T2026)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone PT publicado</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr"/>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Screendomus (Grupo Teixeira)</t>
+          <t>Round Hill Capital</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -4095,14 +4087,10 @@
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr"/>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>geral@screendomus.com</t>
-        </is>
-      </c>
+      <c r="D65" s="5" t="inlineStr"/>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>screendomus.com</t>
+          <t>roundhillcapital.com</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4115,20 +4103,24 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Rua da Escola Politécnica 38, 1250-102</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Altus (Alta de Lisboa) (Em construção)</t>
+          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
+          <t>Sem telefone PT publicado</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr"/>
@@ -4137,7 +4129,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>Screendomus (Grupo Teixeira)</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -4146,36 +4138,40 @@
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>geral@screendomus.com</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>shaluinvest.pt</t>
+          <t>screendomus.com</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
+          <t>Altus (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Fundador e Managing Director: Itai Fridman</t>
+          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
@@ -4184,7 +4180,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4194,10 +4190,14 @@
       </c>
       <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -4208,22 +4208,26 @@
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr"/>
+          <t>Fundador e Managing Director: Itai Fridman</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>United Investments Portugal (UIP)</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -4233,52 +4237,36 @@
       </c>
       <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>uip.pt</t>
-        </is>
-      </c>
+      <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+          <t>Verde Vale (Em construção)</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Fundada 1985 · sem telefone publicado</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>Carlos Leal (CEO)</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
-        </is>
-      </c>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+          <t>United Investments Portugal (UIP)</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4290,7 +4278,7 @@
       <c r="D69" s="5" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>grupovisabeira.com</t>
+          <t>uip.pt</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -4303,25 +4291,29 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Areeiro Select (Comercialização)</t>
+          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fundada 1985 · sem telefone publicado</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
+          <t>Carlos Leal (CEO)</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
+          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr"/>
@@ -4329,7 +4321,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Visabeira Imobiliária (Visabeirahouse)</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4338,14 +4330,10 @@
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr"/>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="D70" s="5" t="inlineStr"/>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>grupovisabeira.com</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4358,29 +4346,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+      <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Areeiro Select (Comercialização)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Fernando Vasco Costa (CEO)</t>
+          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr"/>
@@ -4388,7 +4372,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>VIZTA (ex-Nexity Portugal)</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4399,114 +4383,110 @@
       <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="5" t="inlineStr">
         <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
           <t>info@ancora-inv.com</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>ancora-inv.com</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Antrix</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -4516,22 +4496,22 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
+          <t>900 264 096 (ES)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>info@antrix.pt</t>
+          <t>info@aedashomes.com</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>antrix.pt</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -4541,27 +4521,27 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
@@ -4569,7 +4549,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Arish Capital Partners</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -4579,44 +4559,52 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>+351 917 498 714</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>info@antrix.pt</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>arishcapitalpartners.com</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Grândola</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+        </is>
+      </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Fonte: diarioimobiliario.pt</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
@@ -4624,7 +4612,7 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4634,52 +4622,44 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>info@carvoeirobranco.com</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (CEO)</t>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
@@ -4687,7 +4667,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4697,56 +4677,60 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>casais@casais.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
+          <t>Erik de Vlieger (CEO)</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+        </is>
+      </c>
       <c r="M76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4756,17 +4740,17 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 253 305 490</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4781,35 +4765,31 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
-        </is>
-      </c>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4819,52 +4799,52 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 461 462</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>geral@castro-group.pt</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
+          <t>Paulo Castro (CEO)</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
@@ -4872,7 +4852,7 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4882,48 +4862,60 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
+          <t>+351 234 480 570</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>info@civilria.pt</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+        </is>
+      </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr"/>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
       <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4933,56 +4925,48 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
+          <t>+351 253 089 932</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
-        </is>
-      </c>
+          <t>Diogo Baptista Antunes (CEO)</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4992,56 +4976,56 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>geral@garcia.pt</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr"/>
+          <t>Reinaldo Teixeira (Administrador)</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+        </is>
+      </c>
       <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5051,60 +5035,56 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>aca@grupo-aca.com</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
-        </is>
-      </c>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5114,56 +5094,60 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+        </is>
+      </c>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5173,17 +5157,17 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 253 685 109</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>acrescentar@grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -5198,35 +5182,31 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
-        </is>
-      </c>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5236,52 +5216,60 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
+          <t>+351 253 105 331</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>geral@arliz.co</t>
+        </is>
+      </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr"/>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5291,52 +5279,52 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>273 332 784 (confirmar)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5346,56 +5334,52 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5405,43 +5389,47 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
+          <t>+351 934 175 642</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>José Miguel Afonso (CEO/fundador)</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr"/>
@@ -5450,7 +5438,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5460,56 +5448,52 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>info@pinehill.pt</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+        </is>
+      </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5519,52 +5503,48 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>info@quintadolago.com</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Almancil</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
+          <t>Nuno Pinheiro (fundador)</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
@@ -5572,7 +5552,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5582,52 +5562,60 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 289 390 700</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@quintadolago.com</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+          <t>Almancil</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
+          <t>Resort residencial/golfe</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5637,48 +5625,52 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5688,18 +5680,18 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
+          <t>+351 939 443 765</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -5710,7 +5702,7 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5720,20 +5712,16 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5743,56 +5731,52 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 219 362 960</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5802,87 +5786,107 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>tps.com.pt</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Fonte: omirante.pt</t>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K96" s="5" t="inlineStr"/>
-      <c r="L96" s="5" t="inlineStr"/>
-      <c r="M96" s="5" t="inlineStr"/>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: omirante.pt</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Amorim Luxury</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -5895,37 +5899,33 @@
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Grândola/Lagoa</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr"/>
       <c r="L97" s="5" t="inlineStr"/>
       <c r="M97" s="5" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5938,33 +5938,37 @@
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
       <c r="L98" s="5" t="inlineStr"/>
       <c r="M98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -5977,37 +5981,33 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr"/>
       <c r="L99" s="5" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6017,35 +6017,31 @@
       </c>
       <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="5" t="inlineStr"/>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+          <t>João Bugalho (CEO)</t>
         </is>
       </c>
       <c r="L100" s="5" t="inlineStr"/>
@@ -6054,7 +6050,7 @@
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6064,36 +6060,44 @@
       </c>
       <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="5" t="inlineStr"/>
-      <c r="E101" s="5" t="inlineStr"/>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6106,23 +6110,23 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr"/>
@@ -6132,7 +6136,7 @@
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6142,14 +6146,10 @@
       </c>
       <c r="C103" s="7" t="inlineStr"/>
       <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -6160,12 +6160,12 @@
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr"/>
@@ -6175,7 +6175,7 @@
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6185,10 +6185,14 @@
       </c>
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -6199,12 +6203,12 @@
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr"/>
@@ -6214,7 +6218,7 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6227,23 +6231,23 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr"/>
@@ -6253,7 +6257,7 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6263,30 +6267,26 @@
       </c>
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: diariocoimbra.pt</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr"/>
@@ -6296,7 +6296,7 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6306,26 +6306,30 @@
       </c>
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="5" t="inlineStr"/>
-      <c r="E107" s="5" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: brainsre.news</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -6335,7 +6339,7 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6348,41 +6352,33 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K108" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr"/>
+      <c r="L108" s="5" t="inlineStr"/>
       <c r="M108" s="5" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6395,37 +6391,41 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
-      <c r="L109" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6438,28 +6438,28 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6478,14 +6478,10 @@
       </c>
       <c r="C111" s="7" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr"/>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -6496,17 +6492,17 @@
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr"/>
@@ -6515,7 +6511,7 @@
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6525,31 +6521,35 @@
       </c>
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr"/>
-      <c r="E112" s="5" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6571,7 +6571,7 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -6582,22 +6582,26 @@
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="inlineStr"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6610,23 +6614,23 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr"/>
@@ -6636,7 +6640,7 @@
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6649,23 +6653,23 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr"/>
@@ -6675,7 +6679,7 @@
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6685,14 +6689,10 @@
       </c>
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr"/>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -6703,12 +6703,12 @@
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr"/>
@@ -6718,7 +6718,7 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6730,12 +6730,12 @@
       <c r="D117" s="5" t="inlineStr"/>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>ferreirabuildpower.com</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -6746,26 +6746,22 @@
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: genuinoinvestments.com</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr"/>
       <c r="L117" s="5" t="inlineStr"/>
       <c r="M117" s="5" t="inlineStr"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6777,38 +6773,42 @@
       <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -6818,10 +6818,14 @@
       </c>
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>glowing.pt</t>
+        </is>
+      </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -6832,12 +6836,12 @@
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr"/>
@@ -6847,7 +6851,7 @@
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -6857,36 +6861,36 @@
       </c>
       <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="5" t="inlineStr"/>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr"/>
-      <c r="G120" s="7" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr"/>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>Seixal</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr"/>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -6898,33 +6902,25 @@
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="inlineStr">
-        <is>
-          <t>Sintra</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr"/>
+      <c r="G121" s="7" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
         <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="L121" s="5" t="inlineStr"/>
@@ -6933,7 +6929,7 @@
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -6943,31 +6939,35 @@
       </c>
       <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr"/>
-      <c r="E122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr"/>
@@ -6976,7 +6976,7 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -6989,41 +6989,37 @@
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L123" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr"/>
       <c r="M123" s="5" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7033,25 +7029,21 @@
       </c>
       <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
+      <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
@@ -7059,14 +7051,22 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K124" s="5" t="inlineStr"/>
-      <c r="L124" s="5" t="inlineStr"/>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7078,42 +7078,38 @@
       <c r="D125" s="5" t="inlineStr"/>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>gruponbportugal.pt</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr"/>
       <c r="L125" s="5" t="inlineStr"/>
       <c r="M125" s="5" t="inlineStr"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7125,33 +7121,33 @@
       <c r="D126" s="5" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
+          <t>Fonte: gruponb.pt</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
+          <t>Ioav Blanche (presidente)</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr"/>
@@ -7160,7 +7156,7 @@
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7172,38 +7168,42 @@
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7215,28 +7215,28 @@
       <c r="D128" s="5" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>hillside.pt</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+          <t>Fonte: remax.pt, hillside.pt</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr"/>
@@ -7246,7 +7246,7 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7256,10 +7256,14 @@
       </c>
       <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="5" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>zenithresidences.pt</t>
+        </is>
+      </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -7270,12 +7274,12 @@
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr"/>
@@ -7285,7 +7289,7 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7295,48 +7299,36 @@
       </c>
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K130" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L130" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr"/>
+      <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7348,7 +7340,7 @@
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -7364,26 +7356,30 @@
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
-      <c r="L131" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7393,31 +7389,35 @@
       </c>
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
+          <t>Fonte: luxpremium.net</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+          <t>Claude Berda (fundador)</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr"/>
@@ -7426,7 +7426,7 @@
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7439,33 +7439,37 @@
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K133" s="5" t="inlineStr"/>
+          <t>Fonte: oconnormurphy.ie</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+        </is>
+      </c>
       <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7475,44 +7479,36 @@
       </c>
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr"/>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7524,12 +7520,12 @@
       <c r="D135" s="5" t="inlineStr"/>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>mellordc.pt</t>
+          <t>maveninvest.pt</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -7540,30 +7536,26 @@
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: maveninvest.pt</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L135" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr"/>
       <c r="M135" s="5" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7573,36 +7565,48 @@
       </c>
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
-        </is>
-      </c>
-      <c r="K136" s="5" t="inlineStr"/>
-      <c r="L136" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M136" s="5" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7615,37 +7619,33 @@
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr">
-        <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: ireland-portugal.com</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr"/>
       <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7655,40 +7655,40 @@
       </c>
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr"/>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7700,12 +7700,12 @@
       <c r="D139" s="5" t="inlineStr"/>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>ombria.com</t>
+          <t>oconnormurphy.ie</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -7713,37 +7713,25 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+      <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr"/>
+      <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7753,10 +7741,14 @@
       </c>
       <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -7764,25 +7756,37 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr"/>
-      <c r="L140" s="5" t="inlineStr"/>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7795,37 +7799,33 @@
       <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr"/>
       <c r="L141" s="5" t="inlineStr"/>
       <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -7838,33 +7838,37 @@
       <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -7877,23 +7881,23 @@
       <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: idealista.pt, construir.pt</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr"/>
@@ -7903,7 +7907,7 @@
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -7916,37 +7920,33 @@
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K144" s="5" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="inlineStr"/>
       <c r="L144" s="5" t="inlineStr"/>
       <c r="M144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -7956,35 +7956,31 @@
       </c>
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E145" s="5" t="inlineStr"/>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
         </is>
       </c>
       <c r="L145" s="5" t="inlineStr"/>
@@ -7993,7 +7989,7 @@
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -8005,46 +8001,42 @@
       <c r="D146" s="5" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>soccal-vaz.com</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr"/>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8056,12 +8048,12 @@
       <c r="D147" s="5" t="inlineStr"/>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>soccal-vaz.com</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
@@ -8072,22 +8064,22 @@
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: eco.sapo.pt</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
+          <t>António Vaz (fundador e CEO)</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
         </is>
       </c>
       <c r="M147" s="5" t="inlineStr"/>
@@ -8095,7 +8087,7 @@
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8105,36 +8097,48 @@
       </c>
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr"/>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>solidsentinel.pt</t>
+        </is>
+      </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K148" s="5" t="inlineStr"/>
-      <c r="L148" s="5" t="inlineStr"/>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M148" s="5" t="inlineStr"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8144,44 +8148,36 @@
       </c>
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>sonaesierra.com</t>
-        </is>
-      </c>
+      <c r="E149" s="5" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K149" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr"/>
       <c r="L149" s="5" t="inlineStr"/>
       <c r="M149" s="5" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8193,38 +8189,42 @@
       <c r="D150" s="5" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>southshoreinvest.com</t>
+          <t>sonaesierra.com</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr"/>
+          <t>Fonte: rtp.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
       <c r="L150" s="5" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8236,42 +8236,38 @@
       <c r="D151" s="5" t="inlineStr"/>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>southshoreinvest.com</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: southshoreinvest.com</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr"/>
       <c r="L151" s="5" t="inlineStr"/>
       <c r="M151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8281,36 +8277,44 @@
       </c>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr"/>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K152" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
       <c r="L152" s="5" t="inlineStr"/>
       <c r="M152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8323,23 +8327,23 @@
       <c r="E153" s="5" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: racius.com, idealista.pt</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr"/>
@@ -8349,7 +8353,7 @@
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8359,44 +8363,36 @@
       </c>
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="5" t="inlineStr"/>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>ugp.ie</t>
-        </is>
-      </c>
+      <c r="E154" s="5" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K154" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr"/>
       <c r="L154" s="5" t="inlineStr"/>
       <c r="M154" s="5" t="inlineStr"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8408,33 +8404,80 @@
       <c r="D155" s="5" t="inlineStr"/>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>vilagale.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>The Shipyard (Comercialização)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K155" s="5" t="inlineStr"/>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L155" s="5" t="inlineStr"/>
       <c r="M155" s="5" t="inlineStr"/>
+    </row>
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr"/>
+      <c r="D156" s="5" t="inlineStr"/>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr"/>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr"/>
+      <c r="L156" s="5" t="inlineStr"/>
+      <c r="M156" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8476,7 +8519,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
@@ -8496,7 +8539,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -8506,7 +8549,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M156" headerRowCount="1">
-  <autoFilter ref="A1:M156"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M158" headerRowCount="1">
+  <autoFilter ref="A1:M158"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3816,7 +3816,7 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Overseas</t>
+          <t>Onyria Group</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -3826,10 +3826,14 @@
       </c>
       <c r="C59" s="7" t="inlineStr"/>
       <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>onyriagroup.com</t>
+        </is>
+      </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3837,37 +3841,29 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
-        </is>
-      </c>
+      <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+          <t>Onyria Quinta da Marinha Residences (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
+          <t>Grupo hoteleiro+imobiliário fundado 1986 por José Carlos Pinto Coelho</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Pedro Vicente (CEO)</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
-        </is>
-      </c>
+          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Overseas</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3880,37 +3876,45 @@
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
+        </is>
+      </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
+          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>Nuno Cunha (Managing Director)</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr"/>
+          <t>Pedro Vicente (CEO)</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
+        </is>
+      </c>
       <c r="M60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3923,32 +3927,28 @@
       <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/site publicados (APPII)</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>Federico Rosales (cofundador e CEO)</t>
+          <t>Nuno Cunha (Managing Director)</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr"/>
@@ -3957,7 +3957,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>RAR Imobiliária</t>
+          <t>Prime Portugal</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3970,28 +3970,32 @@
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
+        </is>
+      </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
+          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+          <t>Sem telefone/site publicados (APPII)</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>Paula Fernandes (CEO)</t>
+          <t>Federico Rosales (cofundador e CEO)</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr"/>
@@ -4000,7 +4004,7 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>RAR Imobiliária</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4013,33 +4017,37 @@
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
+          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr"/>
+          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Paula Fernandes (CEO)</t>
+        </is>
+      </c>
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4052,23 +4060,23 @@
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>RM Villas (Início obra 1T2026)</t>
+          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr"/>
@@ -4078,7 +4086,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -4088,48 +4096,36 @@
       </c>
       <c r="C65" s="7" t="inlineStr"/>
       <c r="D65" s="5" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>roundhillcapital.com</t>
-        </is>
-      </c>
+      <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Rua da Escola Politécnica 38, 1250-102</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+          <t>RM Villas (Início obra 1T2026)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone PT publicado</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Screendomus (Grupo Teixeira)</t>
+          <t>Round Hill Capital</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -4138,14 +4134,10 @@
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>geral@screendomus.com</t>
-        </is>
-      </c>
+      <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>screendomus.com</t>
+          <t>roundhillcapital.com</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -4158,20 +4150,24 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Rua da Escola Politécnica 38, 1250-102</t>
+        </is>
+      </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Altus (Alta de Lisboa) (Em construção)</t>
+          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
+          <t>Sem telefone PT publicado</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
@@ -4180,7 +4176,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>Screendomus (Grupo Teixeira)</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4189,36 +4185,40 @@
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>geral@screendomus.com</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>shaluinvest.pt</t>
+          <t>screendomus.com</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
+          <t>Altus (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Fundador e Managing Director: Itai Fridman</t>
+          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
@@ -4227,7 +4227,7 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -4237,10 +4237,14 @@
       </c>
       <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
@@ -4251,22 +4255,26 @@
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr"/>
+          <t>Fundador e Managing Director: Itai Fridman</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>United Investments Portugal (UIP)</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4276,52 +4284,36 @@
       </c>
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>uip.pt</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+          <t>Verde Vale (Em construção)</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Fundada 1985 · sem telefone publicado</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>Carlos Leal (CEO)</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
-        </is>
-      </c>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr"/>
+      <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+          <t>United Investments Portugal (UIP)</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4333,7 +4325,7 @@
       <c r="D70" s="5" t="inlineStr"/>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>grupovisabeira.com</t>
+          <t>uip.pt</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4346,25 +4338,29 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Areeiro Select (Comercialização)</t>
+          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fundada 1985 · sem telefone publicado</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
+          <t>Carlos Leal (CEO)</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
+          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr"/>
@@ -4372,7 +4368,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Visabeira Imobiliária (Visabeirahouse)</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4381,14 +4377,10 @@
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr"/>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="D71" s="5" t="inlineStr"/>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>grupovisabeira.com</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4401,29 +4393,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+      <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Areeiro Select (Comercialização)</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>Fernando Vasco Costa (CEO)</t>
+          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr"/>
@@ -4431,7 +4419,7 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>VIZTA (ex-Nexity Portugal)</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -4442,114 +4430,110 @@
       <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
           <t>info@ancora-inv.com</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>ancora-inv.com</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+      <c r="M73" s="5" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Antrix</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -4559,22 +4543,22 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
+          <t>900 264 096 (ES)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>info@antrix.pt</t>
+          <t>info@aedashomes.com</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>antrix.pt</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -4584,27 +4568,27 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
@@ -4612,7 +4596,7 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Arish Capital Partners</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4622,44 +4606,52 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>+351 917 498 714</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>info@antrix.pt</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>arishcapitalpartners.com</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Grândola</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Fonte: diarioimobiliario.pt</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
@@ -4667,7 +4659,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4677,52 +4669,44 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>info@carvoeirobranco.com</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (CEO)</t>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
@@ -4730,7 +4714,7 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4740,56 +4724,60 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>casais@casais.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
+          <t>Erik de Vlieger (CEO)</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4799,17 +4787,17 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 253 305 490</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -4824,35 +4812,31 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
-        </is>
-      </c>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4862,52 +4846,52 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 461 462</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>geral@castro-group.pt</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
+          <t>Paulo Castro (CEO)</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
@@ -4915,7 +4899,7 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4925,48 +4909,60 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>+351 234 480 570</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>info@civilria.pt</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+        </is>
+      </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4976,56 +4972,48 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
+          <t>+351 253 089 932</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
-        </is>
-      </c>
+          <t>Diogo Baptista Antunes (CEO)</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5035,56 +5023,56 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>geral@garcia.pt</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
+          <t>Reinaldo Teixeira (Administrador)</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+        </is>
+      </c>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5094,60 +5082,56 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>aca@grupo-aca.com</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
-        </is>
-      </c>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5157,56 +5141,60 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5216,17 +5204,17 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 253 685 109</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>acrescentar@grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -5241,35 +5229,31 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
-        </is>
-      </c>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5279,52 +5263,60 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
+          <t>+351 253 105 331</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>geral@arliz.co</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5334,52 +5326,52 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>273 332 784 (confirmar)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5389,56 +5381,52 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5448,43 +5436,47 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
+          <t>+351 934 175 642</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>José Miguel Afonso (CEO/fundador)</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr"/>
@@ -5493,7 +5485,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5503,56 +5495,52 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>info@pinehill.pt</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+        </is>
+      </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5562,52 +5550,48 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>info@quintadolago.com</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Almancil</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
+          <t>Nuno Pinheiro (fundador)</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
@@ -5615,7 +5599,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5625,52 +5609,60 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 289 390 700</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@quintadolago.com</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+          <t>Almancil</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
+          <t>Resort residencial/golfe</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5680,48 +5672,52 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5731,18 +5727,18 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
+          <t>+351 939 443 765</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -5753,7 +5749,7 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5763,20 +5759,16 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5786,56 +5778,52 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 219 362 960</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5845,87 +5833,107 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>tps.com.pt</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Fonte: omirante.pt</t>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
-      <c r="D97" s="5" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr"/>
-      <c r="L97" s="5" t="inlineStr"/>
-      <c r="M97" s="5" t="inlineStr"/>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: omirante.pt</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Amorim Luxury</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5938,37 +5946,33 @@
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Grândola/Lagoa</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr"/>
       <c r="L98" s="5" t="inlineStr"/>
       <c r="M98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -5981,33 +5985,37 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
       <c r="L99" s="5" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6020,37 +6028,33 @@
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="5" t="inlineStr"/>
       <c r="M100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6060,35 +6064,31 @@
       </c>
       <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="5" t="inlineStr"/>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+          <t>João Bugalho (CEO)</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr"/>
@@ -6097,7 +6097,7 @@
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6107,36 +6107,44 @@
       </c>
       <c r="C102" s="7" t="inlineStr"/>
       <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L102" s="5" t="inlineStr"/>
       <c r="M102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6149,23 +6157,23 @@
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr"/>
@@ -6175,7 +6183,7 @@
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6185,14 +6193,10 @@
       </c>
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -6203,12 +6207,12 @@
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr"/>
@@ -6218,7 +6222,7 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6228,10 +6232,14 @@
       </c>
       <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="5" t="inlineStr"/>
-      <c r="E105" s="5" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -6242,12 +6250,12 @@
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr"/>
@@ -6257,7 +6265,7 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6270,23 +6278,23 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr"/>
@@ -6296,7 +6304,7 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6306,30 +6314,26 @@
       </c>
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="5" t="inlineStr"/>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: diariocoimbra.pt</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -6339,7 +6343,7 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6349,26 +6353,30 @@
       </c>
       <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: brainsre.news</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr"/>
@@ -6378,7 +6386,7 @@
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6391,41 +6399,33 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr"/>
+      <c r="L109" s="5" t="inlineStr"/>
       <c r="M109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6438,37 +6438,41 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
-      <c r="L110" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6481,28 +6485,28 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr"/>
@@ -6511,7 +6515,7 @@
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6521,14 +6525,10 @@
       </c>
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr"/>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -6539,17 +6539,17 @@
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6568,31 +6568,35 @@
       </c>
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr"/>
-      <c r="E113" s="5" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr"/>
@@ -6601,7 +6605,7 @@
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6614,7 +6618,7 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -6625,22 +6629,26 @@
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L114" s="5" t="inlineStr"/>
       <c r="M114" s="5" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6653,23 +6661,23 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr"/>
@@ -6679,7 +6687,7 @@
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6692,23 +6700,23 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr"/>
@@ -6718,7 +6726,7 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6728,14 +6736,10 @@
       </c>
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr"/>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -6746,12 +6750,12 @@
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr"/>
@@ -6761,7 +6765,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6773,12 +6777,12 @@
       <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>ferreirabuildpower.com</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -6789,26 +6793,22 @@
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: genuinoinvestments.com</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr"/>
       <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -6820,38 +6820,42 @@
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L119" s="5" t="inlineStr"/>
       <c r="M119" s="5" t="inlineStr"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -6861,10 +6865,14 @@
       </c>
       <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="5" t="inlineStr"/>
-      <c r="E120" s="5" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>glowing.pt</t>
+        </is>
+      </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -6875,12 +6883,12 @@
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr"/>
@@ -6890,7 +6898,7 @@
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -6900,36 +6908,36 @@
       </c>
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="5" t="inlineStr"/>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="inlineStr"/>
-      <c r="G121" s="7" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr"/>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Seixal</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr"/>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -6941,33 +6949,25 @@
       <c r="D122" s="5" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>Sintra</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr"/>
@@ -6976,7 +6976,7 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -6986,31 +6986,35 @@
       </c>
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr"/>
@@ -7019,7 +7023,7 @@
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7032,41 +7036,37 @@
       <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L124" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr"/>
       <c r="M124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7076,25 +7076,21 @@
       </c>
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
+      <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
@@ -7102,14 +7098,22 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K125" s="5" t="inlineStr"/>
-      <c r="L125" s="5" t="inlineStr"/>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M125" s="5" t="inlineStr"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7121,42 +7125,38 @@
       <c r="D126" s="5" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>gruponbportugal.pt</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
-        </is>
-      </c>
-      <c r="K126" s="5" t="inlineStr">
-        <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr"/>
       <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7168,33 +7168,33 @@
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
+          <t>Fonte: gruponb.pt</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
+          <t>Ioav Blanche (presidente)</t>
         </is>
       </c>
       <c r="L127" s="5" t="inlineStr"/>
@@ -7203,7 +7203,7 @@
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7215,38 +7215,42 @@
       <c r="D128" s="5" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L128" s="5" t="inlineStr"/>
       <c r="M128" s="5" t="inlineStr"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7258,28 +7262,28 @@
       <c r="D129" s="5" t="inlineStr"/>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>hillside.pt</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+          <t>Fonte: remax.pt, hillside.pt</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr"/>
@@ -7289,7 +7293,7 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7299,10 +7303,14 @@
       </c>
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>zenithresidences.pt</t>
+        </is>
+      </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -7313,12 +7321,12 @@
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr"/>
@@ -7328,7 +7336,7 @@
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7338,48 +7346,36 @@
       </c>
       <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="5" t="inlineStr"/>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="E131" s="5" t="inlineStr"/>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K131" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L131" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr"/>
+      <c r="L131" s="5" t="inlineStr"/>
       <c r="M131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7391,7 +7387,7 @@
       <c r="D132" s="5" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -7407,26 +7403,30 @@
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
-      <c r="L132" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7436,31 +7436,35 @@
       </c>
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr"/>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
+          <t>Fonte: luxpremium.net</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+          <t>Claude Berda (fundador)</t>
         </is>
       </c>
       <c r="L133" s="5" t="inlineStr"/>
@@ -7469,7 +7473,7 @@
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7482,33 +7486,37 @@
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr"/>
+          <t>Fonte: oconnormurphy.ie</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+        </is>
+      </c>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7518,44 +7526,36 @@
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr">
-        <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr"/>
       <c r="L135" s="5" t="inlineStr"/>
       <c r="M135" s="5" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7567,12 +7567,12 @@
       <c r="D136" s="5" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>mellordc.pt</t>
+          <t>maveninvest.pt</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -7583,30 +7583,26 @@
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: maveninvest.pt</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr"/>
       <c r="M136" s="5" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7616,36 +7612,48 @@
       </c>
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr"/>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr"/>
-      <c r="L137" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7658,37 +7666,33 @@
       <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr">
-        <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: ireland-portugal.com</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr"/>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7698,40 +7702,40 @@
       </c>
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="E139" s="5" t="inlineStr"/>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr"/>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
       <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7743,12 +7747,12 @@
       <c r="D140" s="5" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>ombria.com</t>
+          <t>oconnormurphy.ie</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -7756,37 +7760,25 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+      <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7796,10 +7788,14 @@
       </c>
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -7807,25 +7803,37 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H141" s="5" t="inlineStr"/>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr"/>
-      <c r="L141" s="5" t="inlineStr"/>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -7838,37 +7846,33 @@
       <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr"/>
       <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -7881,33 +7885,37 @@
       <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K143" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L143" s="5" t="inlineStr"/>
       <c r="M143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -7920,23 +7928,23 @@
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: idealista.pt, construir.pt</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr"/>
@@ -7946,7 +7954,7 @@
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -7959,37 +7967,33 @@
       <c r="E145" s="5" t="inlineStr"/>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K145" s="5" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr"/>
       <c r="L145" s="5" t="inlineStr"/>
       <c r="M145" s="5" t="inlineStr"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -7999,35 +8003,31 @@
       </c>
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E146" s="5" t="inlineStr"/>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr"/>
@@ -8036,7 +8036,7 @@
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8048,46 +8048,42 @@
       <c r="D147" s="5" t="inlineStr"/>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>soccal-vaz.com</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L147" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr"/>
       <c r="M147" s="5" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8099,12 +8095,12 @@
       <c r="D148" s="5" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>soccal-vaz.com</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -8115,22 +8111,22 @@
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: eco.sapo.pt</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
+          <t>António Vaz (fundador e CEO)</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
         </is>
       </c>
       <c r="M148" s="5" t="inlineStr"/>
@@ -8138,7 +8134,7 @@
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8148,36 +8144,48 @@
       </c>
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="5" t="inlineStr"/>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>solidsentinel.pt</t>
+        </is>
+      </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K149" s="5" t="inlineStr"/>
-      <c r="L149" s="5" t="inlineStr"/>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M149" s="5" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8187,44 +8195,36 @@
       </c>
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="5" t="inlineStr"/>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>sonaesierra.com</t>
-        </is>
-      </c>
+      <c r="E150" s="5" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr"/>
       <c r="L150" s="5" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8236,38 +8236,42 @@
       <c r="D151" s="5" t="inlineStr"/>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>southshoreinvest.com</t>
+          <t>sonaesierra.com</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr"/>
+          <t>Fonte: rtp.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
       <c r="L151" s="5" t="inlineStr"/>
       <c r="M151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8279,42 +8283,38 @@
       <c r="D152" s="5" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>southshoreinvest.com</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
-        </is>
-      </c>
-      <c r="K152" s="5" t="inlineStr">
-        <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: southshoreinvest.com</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr"/>
       <c r="M152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8324,36 +8324,44 @@
       </c>
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr"/>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K153" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
       <c r="L153" s="5" t="inlineStr"/>
       <c r="M153" s="5" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8366,23 +8374,23 @@
       <c r="E154" s="5" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: racius.com, idealista.pt</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr"/>
@@ -8392,7 +8400,7 @@
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8402,44 +8410,36 @@
       </c>
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="5" t="inlineStr"/>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>ugp.ie</t>
-        </is>
-      </c>
+      <c r="E155" s="5" t="inlineStr"/>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K155" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr"/>
       <c r="L155" s="5" t="inlineStr"/>
       <c r="M155" s="5" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -8451,33 +8451,127 @@
       <c r="D156" s="5" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>vilagale.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>The Shipyard (Comercialização)</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K156" s="5" t="inlineStr"/>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L156" s="5" t="inlineStr"/>
       <c r="M156" s="5" t="inlineStr"/>
+    </row>
+    <row r="157" ht="30" customHeight="1">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr"/>
+      <c r="D157" s="5" t="inlineStr"/>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>Parque do Golfe</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr"/>
+      <c r="L157" s="5" t="inlineStr"/>
+      <c r="M157" s="5" t="inlineStr"/>
+    </row>
+    <row r="158" ht="30" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr"/>
+      <c r="D158" s="5" t="inlineStr"/>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr"/>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr"/>
+      <c r="L158" s="5" t="inlineStr"/>
+      <c r="M158" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8519,7 +8613,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
@@ -8539,7 +8633,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -8549,7 +8643,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -8559,7 +8653,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M158" headerRowCount="1">
-  <autoFilter ref="A1:M158"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M161" headerRowCount="1">
+  <autoFilter ref="A1:M161"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5013,7 +5013,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>DST Real Estate (Grupo dst)</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5023,56 +5023,52 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>+351 253 307 200</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>geral@dstsgps.com</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dstsgps.com</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
+          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Museu no centro histórico de Braga (Em construção)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
-        </is>
-      </c>
+          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5082,56 +5078,56 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>geral@garcia.pt</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
+          <t>Reinaldo Teixeira (Administrador)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+        </is>
+      </c>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5141,60 +5137,56 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>aca@grupo-aca.com</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
-        </is>
-      </c>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5204,56 +5196,60 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr"/>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+        </is>
+      </c>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5263,17 +5259,17 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 253 685 109</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>acrescentar@grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -5288,35 +5284,31 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
-        </is>
-      </c>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5326,52 +5318,60 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr"/>
+          <t>+351 253 105 331</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>geral@arliz.co</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr"/>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5381,52 +5381,52 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>273 332 784 (confirmar)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5436,56 +5436,52 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5495,43 +5491,47 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
+          <t>+351 934 175 642</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>José Miguel Afonso (CEO/fundador)</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr"/>
@@ -5540,7 +5540,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5550,56 +5550,52 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>info@pinehill.pt</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+        </is>
+      </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5609,52 +5605,48 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>info@quintadolago.com</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Almancil</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
+          <t>Nuno Pinheiro (fundador)</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
@@ -5662,7 +5654,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5672,52 +5664,60 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 289 390 700</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@quintadolago.com</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+          <t>Almancil</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
+          <t>Resort residencial/golfe</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5727,48 +5727,52 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5778,18 +5782,18 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
+          <t>+351 939 443 765</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -5800,7 +5804,7 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5810,20 +5814,16 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5833,56 +5833,52 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 219 362 960</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5892,87 +5888,107 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>tps.com.pt</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr"/>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Fonte: omirante.pt</t>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr"/>
-      <c r="D98" s="5" t="inlineStr"/>
-      <c r="E98" s="5" t="inlineStr"/>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr"/>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="inlineStr"/>
-      <c r="L98" s="5" t="inlineStr"/>
-      <c r="M98" s="5" t="inlineStr"/>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: omirante.pt</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Amorim Luxury</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -5985,37 +6001,33 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Grândola/Lagoa</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr"/>
       <c r="L99" s="5" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6028,33 +6040,37 @@
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
       <c r="L100" s="5" t="inlineStr"/>
       <c r="M100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6067,37 +6083,33 @@
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6107,35 +6119,31 @@
       </c>
       <c r="C102" s="7" t="inlineStr"/>
       <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+          <t>João Bugalho (CEO)</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr"/>
@@ -6144,7 +6152,7 @@
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6154,36 +6162,44 @@
       </c>
       <c r="C103" s="7" t="inlineStr"/>
       <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr"/>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L103" s="5" t="inlineStr"/>
       <c r="M103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6196,23 +6212,23 @@
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr"/>
@@ -6222,7 +6238,7 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6232,14 +6248,10 @@
       </c>
       <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="5" t="inlineStr"/>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -6250,12 +6262,12 @@
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr"/>
@@ -6265,7 +6277,7 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6275,10 +6287,14 @@
       </c>
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -6289,12 +6305,12 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr"/>
@@ -6304,7 +6320,7 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6317,23 +6333,23 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -6343,7 +6359,7 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6353,30 +6369,26 @@
       </c>
       <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: diariocoimbra.pt</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr"/>
@@ -6386,7 +6398,7 @@
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6396,26 +6408,30 @@
       </c>
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="5" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: brainsre.news</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr"/>
@@ -6425,7 +6441,7 @@
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6438,41 +6454,33 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K110" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L110" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr"/>
+      <c r="L110" s="5" t="inlineStr"/>
       <c r="M110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6485,37 +6493,41 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M111" s="5" t="inlineStr"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6528,28 +6540,28 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr"/>
@@ -6558,7 +6570,7 @@
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6568,14 +6580,10 @@
       </c>
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr"/>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -6586,17 +6594,17 @@
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr"/>
@@ -6605,7 +6613,7 @@
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6615,31 +6623,35 @@
       </c>
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr"/>
@@ -6648,7 +6660,7 @@
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6661,7 +6673,7 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
@@ -6672,22 +6684,26 @@
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L115" s="5" t="inlineStr"/>
       <c r="M115" s="5" t="inlineStr"/>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6700,23 +6716,23 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr"/>
@@ -6726,7 +6742,7 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6739,23 +6755,23 @@
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr"/>
@@ -6765,7 +6781,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6775,14 +6791,10 @@
       </c>
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="5" t="inlineStr"/>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
@@ -6793,12 +6805,12 @@
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr"/>
@@ -6808,7 +6820,7 @@
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -6820,12 +6832,12 @@
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>ferreirabuildpower.com</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -6836,26 +6848,22 @@
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: genuinoinvestments.com</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr"/>
       <c r="L119" s="5" t="inlineStr"/>
       <c r="M119" s="5" t="inlineStr"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -6867,38 +6875,42 @@
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -6908,10 +6920,14 @@
       </c>
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="5" t="inlineStr"/>
-      <c r="E121" s="5" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>glowing.pt</t>
+        </is>
+      </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -6922,12 +6938,12 @@
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr"/>
@@ -6937,7 +6953,7 @@
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -6947,36 +6963,36 @@
       </c>
       <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr"/>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr"/>
-      <c r="G122" s="7" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr"/>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>Seixal</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr"/>
       <c r="L122" s="5" t="inlineStr"/>
       <c r="M122" s="5" t="inlineStr"/>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -6988,33 +7004,25 @@
       <c r="D123" s="5" t="inlineStr"/>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>Sintra</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr"/>
+      <c r="G123" s="7" t="inlineStr"/>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr"/>
@@ -7023,7 +7031,7 @@
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7033,31 +7041,35 @@
       </c>
       <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr"/>
@@ -7066,7 +7078,7 @@
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7079,41 +7091,37 @@
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L125" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr"/>
       <c r="M125" s="5" t="inlineStr"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7123,25 +7131,21 @@
       </c>
       <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
+      <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
@@ -7149,14 +7153,22 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K126" s="5" t="inlineStr"/>
-      <c r="L126" s="5" t="inlineStr"/>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7168,42 +7180,38 @@
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>gruponbportugal.pt</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr"/>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7215,33 +7223,33 @@
       <c r="D128" s="5" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
+          <t>Fonte: gruponb.pt</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
+          <t>Ioav Blanche (presidente)</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr"/>
@@ -7250,7 +7258,7 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7262,38 +7270,42 @@
       <c r="D129" s="5" t="inlineStr"/>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K129" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L129" s="5" t="inlineStr"/>
       <c r="M129" s="5" t="inlineStr"/>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7305,28 +7317,28 @@
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>hillside.pt</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+          <t>Fonte: remax.pt, hillside.pt</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr"/>
@@ -7336,7 +7348,7 @@
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7346,10 +7358,14 @@
       </c>
       <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="5" t="inlineStr"/>
-      <c r="E131" s="5" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>zenithresidences.pt</t>
+        </is>
+      </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -7360,12 +7376,12 @@
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr"/>
@@ -7375,7 +7391,7 @@
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7385,48 +7401,36 @@
       </c>
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L132" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr"/>
+      <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7438,7 +7442,7 @@
       <c r="D133" s="5" t="inlineStr"/>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -7454,26 +7458,30 @@
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
-      <c r="L133" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M133" s="5" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7483,10 +7491,14 @@
       </c>
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
@@ -7497,26 +7509,22 @@
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
+          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr"/>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7526,36 +7534,44 @@
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr"/>
+          <t>Fonte: luxpremium.net</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="L135" s="5" t="inlineStr"/>
       <c r="M135" s="5" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7565,35 +7581,31 @@
       </c>
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
+          <t>Fonte: oconnormurphy.ie</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr"/>
@@ -7602,7 +7614,7 @@
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7612,48 +7624,36 @@
       </c>
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr">
-        <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L137" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr"/>
+      <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7663,36 +7663,44 @@
       </c>
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr"/>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr"/>
+          <t>Fonte: maveninvest.pt</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7702,40 +7710,48 @@
       </c>
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr"/>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr"/>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7745,14 +7761,10 @@
       </c>
       <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -7763,12 +7775,12 @@
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
+          <t>Fonte: ireland-portugal.com</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr"/>
@@ -7778,7 +7790,7 @@
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7788,52 +7800,40 @@
       </c>
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>ombria.com</t>
-        </is>
-      </c>
+      <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L141" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
+      <c r="L141" s="5" t="inlineStr"/>
       <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -7843,10 +7843,14 @@
       </c>
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
@@ -7857,12 +7861,12 @@
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr"/>
@@ -7872,7 +7876,7 @@
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -7882,40 +7886,52 @@
       </c>
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr"/>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
-      <c r="L143" s="5" t="inlineStr"/>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -7928,23 +7944,23 @@
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
+          <t>Fonte: ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr"/>
@@ -7954,7 +7970,7 @@
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -7967,7 +7983,7 @@
       <c r="E145" s="5" t="inlineStr"/>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -7978,22 +7994,26 @@
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K145" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L145" s="5" t="inlineStr"/>
       <c r="M145" s="5" t="inlineStr"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -8006,37 +8026,33 @@
       <c r="E146" s="5" t="inlineStr"/>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K146" s="5" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr"/>
       <c r="L146" s="5" t="inlineStr"/>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8046,44 +8062,36 @@
       </c>
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="5" t="inlineStr"/>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E147" s="5" t="inlineStr"/>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
-        </is>
-      </c>
-      <c r="K147" s="5" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="inlineStr"/>
       <c r="L147" s="5" t="inlineStr"/>
       <c r="M147" s="5" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8093,48 +8101,40 @@
       </c>
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>soccal-vaz.com</t>
-        </is>
-      </c>
+      <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L148" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr"/>
       <c r="M148" s="5" t="inlineStr"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8146,46 +8146,42 @@
       <c r="D149" s="5" t="inlineStr"/>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
-        </is>
-      </c>
-      <c r="L149" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
-        </is>
-      </c>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr"/>
       <c r="M149" s="5" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8195,36 +8191,48 @@
       </c>
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="5" t="inlineStr"/>
-      <c r="E150" s="5" t="inlineStr"/>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>soccal-vaz.com</t>
+        </is>
+      </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr"/>
-      <c r="L150" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>António Vaz (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+        </is>
+      </c>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8236,42 +8244,46 @@
       <c r="D151" s="5" t="inlineStr"/>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
-        </is>
-      </c>
-      <c r="L151" s="5" t="inlineStr"/>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8281,30 +8293,26 @@
       </c>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>southshoreinvest.com</t>
-        </is>
-      </c>
+      <c r="E152" s="5" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr"/>
@@ -8314,7 +8322,7 @@
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8326,33 +8334,33 @@
       <c r="D153" s="5" t="inlineStr"/>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>sonaesierra.com</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
+          <t>Fonte: rtp.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
         </is>
       </c>
       <c r="L153" s="5" t="inlineStr"/>
@@ -8361,7 +8369,7 @@
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8371,26 +8379,30 @@
       </c>
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="5" t="inlineStr"/>
-      <c r="E154" s="5" t="inlineStr"/>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>southshoreinvest.com</t>
+        </is>
+      </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
+          <t>Fonte: southshoreinvest.com</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr"/>
@@ -8400,7 +8412,7 @@
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8410,36 +8422,44 @@
       </c>
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="5" t="inlineStr"/>
-      <c r="E155" s="5" t="inlineStr"/>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K155" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
       <c r="L155" s="5" t="inlineStr"/>
       <c r="M155" s="5" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -8449,14 +8469,10 @@
       </c>
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="5" t="inlineStr"/>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>ugp.ie</t>
-        </is>
-      </c>
+      <c r="E156" s="5" t="inlineStr"/>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
@@ -8467,26 +8483,22 @@
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K156" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: racius.com, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr"/>
       <c r="L156" s="5" t="inlineStr"/>
       <c r="M156" s="5" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -8498,32 +8510,28 @@
       <c r="D157" s="5" t="inlineStr"/>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>valedolobo.com</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr">
-        <is>
-          <t>Parque do Golfe</t>
-        </is>
-      </c>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr"/>
@@ -8533,7 +8541,7 @@
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -8543,25 +8551,21 @@
       </c>
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="5" t="inlineStr"/>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>vilagale.com</t>
-        </is>
-      </c>
+      <c r="E158" s="5" t="inlineStr"/>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
@@ -8572,6 +8576,143 @@
       <c r="K158" s="5" t="inlineStr"/>
       <c r="L158" s="5" t="inlineStr"/>
       <c r="M158" s="5" t="inlineStr"/>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Urban Green Private (UGP)</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr"/>
+      <c r="D159" s="5" t="inlineStr"/>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>ugp.ie</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>The Shipyard (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
+      <c r="L159" s="5" t="inlineStr"/>
+      <c r="M159" s="5" t="inlineStr"/>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr"/>
+      <c r="D160" s="5" t="inlineStr"/>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>Parque do Golfe</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr"/>
+      <c r="L160" s="5" t="inlineStr"/>
+      <c r="M160" s="5" t="inlineStr"/>
+    </row>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr"/>
+      <c r="D161" s="5" t="inlineStr"/>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr"/>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="inlineStr"/>
+      <c r="L161" s="5" t="inlineStr"/>
+      <c r="M161" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8613,7 +8754,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
@@ -8623,7 +8764,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -8633,7 +8774,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M161" headerRowCount="1">
-  <autoFilter ref="A1:M161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M162" headerRowCount="1">
+  <autoFilter ref="A1:M162"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3589,7 +3589,7 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Fungepi (Grupo Novo Banco)</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3599,11 +3599,7 @@
       </c>
       <c r="C54" s="7" t="inlineStr"/>
       <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>hines.com</t>
-        </is>
-      </c>
+      <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -3616,31 +3612,27 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Rua de Artilharia 1, Campolide</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
+          <t>Urbanização Artilharia Um / Amoreiras (Campolide) (Planeamento (consulta pública fev-mar/2026))</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Gestora global · sem contacto PT publicado</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
-        </is>
-      </c>
+          <t>Fundo de Gestão de Património Imobiliário do Grupo Novo Banco. Projeto contestado por moradores (petição + queixa à CE)</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -3652,33 +3644,37 @@
       <c r="D55" s="5" t="inlineStr"/>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>imolote.pt</t>
+          <t>hines.com</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
+          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
+          <t>Gestora global · sem contacto PT publicado</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
@@ -3687,7 +3683,7 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3697,7 +3693,11 @@
       </c>
       <c r="C56" s="7" t="inlineStr"/>
       <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
@@ -3711,17 +3711,17 @@
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
+          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr"/>
@@ -3730,7 +3730,7 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>KKR Imo, S.A.</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3743,28 +3743,28 @@
       <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
+          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Neptune Developments</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3783,14 +3783,10 @@
       </c>
       <c r="C58" s="7" t="inlineStr"/>
       <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>neptune-developments.com</t>
-        </is>
-      </c>
+      <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -3801,22 +3797,26 @@
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>BellaMary (Cascais) (Comercialização)</t>
+          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+        </is>
+      </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Onyria Group</t>
+          <t>Neptune Developments</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -3828,7 +3828,7 @@
       <c r="D59" s="5" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>onyriagroup.com</t>
+          <t>neptune-developments.com</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -3844,26 +3844,22 @@
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Onyria Quinta da Marinha Residences (Cascais) (Comercialização)</t>
+          <t>BellaMary (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Grupo hoteleiro+imobiliário fundado 1986 por José Carlos Pinto Coelho</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
-        </is>
-      </c>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Overseas</t>
+          <t>Onyria Group</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3873,10 +3869,14 @@
       </c>
       <c r="C60" s="7" t="inlineStr"/>
       <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>onyriagroup.com</t>
+        </is>
+      </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3884,37 +3884,29 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
-        </is>
-      </c>
+      <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+          <t>Onyria Quinta da Marinha Residences (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
+          <t>Grupo hoteleiro+imobiliário fundado 1986 por José Carlos Pinto Coelho</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>Pedro Vicente (CEO)</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
-        </is>
-      </c>
+          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Overseas</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3927,37 +3919,45 @@
       <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
+          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>Nuno Cunha (Managing Director)</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr"/>
+          <t>Pedro Vicente (CEO)</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
+        </is>
+      </c>
       <c r="M61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3970,32 +3970,28 @@
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/site publicados (APPII)</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>Federico Rosales (cofundador e CEO)</t>
+          <t>Nuno Cunha (Managing Director)</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr"/>
@@ -4004,7 +4000,7 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>RAR Imobiliária</t>
+          <t>Prime Portugal</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4017,28 +4013,32 @@
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
+          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+          <t>Sem telefone/site publicados (APPII)</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>Paula Fernandes (CEO)</t>
+          <t>Federico Rosales (cofundador e CEO)</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr"/>
@@ -4047,7 +4047,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>RAR Imobiliária</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4060,33 +4060,37 @@
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
+          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr"/>
+          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Paula Fernandes (CEO)</t>
+        </is>
+      </c>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -4099,23 +4103,23 @@
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>RM Villas (Início obra 1T2026)</t>
+          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -4125,7 +4129,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -4135,48 +4139,36 @@
       </c>
       <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>roundhillcapital.com</t>
-        </is>
-      </c>
+      <c r="E66" s="5" t="inlineStr"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>Rua da Escola Politécnica 38, 1250-102</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+          <t>RM Villas (Início obra 1T2026)</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone PT publicado</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr"/>
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Screendomus (Grupo Teixeira)</t>
+          <t>Round Hill Capital</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4185,14 +4177,10 @@
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>geral@screendomus.com</t>
-        </is>
-      </c>
+      <c r="D67" s="5" t="inlineStr"/>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>screendomus.com</t>
+          <t>roundhillcapital.com</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4205,20 +4193,24 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Rua da Escola Politécnica 38, 1250-102</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Altus (Alta de Lisboa) (Em construção)</t>
+          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
+          <t>Sem telefone PT publicado</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
@@ -4227,7 +4219,7 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>Screendomus (Grupo Teixeira)</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -4236,36 +4228,40 @@
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>geral@screendomus.com</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>shaluinvest.pt</t>
+          <t>screendomus.com</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
+          <t>Altus (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Fundador e Managing Director: Itai Fridman</t>
+          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr"/>
@@ -4274,7 +4270,7 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4284,10 +4280,14 @@
       </c>
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -4298,22 +4298,26 @@
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr"/>
+          <t>Fundador e Managing Director: Itai Fridman</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>United Investments Portugal (UIP)</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4323,52 +4327,36 @@
       </c>
       <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>uip.pt</t>
-        </is>
-      </c>
+      <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+          <t>Verde Vale (Em construção)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Fundada 1985 · sem telefone publicado</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>Carlos Leal (CEO)</t>
-        </is>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
-        </is>
-      </c>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+          <t>United Investments Portugal (UIP)</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4380,7 +4368,7 @@
       <c r="D71" s="5" t="inlineStr"/>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>grupovisabeira.com</t>
+          <t>uip.pt</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4393,25 +4381,29 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Areeiro Select (Comercialização)</t>
+          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fundada 1985 · sem telefone publicado</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
+          <t>Carlos Leal (CEO)</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
+          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr"/>
@@ -4419,7 +4411,7 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Visabeira Imobiliária (Visabeirahouse)</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -4428,14 +4420,10 @@
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="D72" s="5" t="inlineStr"/>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>grupovisabeira.com</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -4448,29 +4436,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+      <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Areeiro Select (Comercialização)</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>Fernando Vasco Costa (CEO)</t>
+          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr"/>
@@ -4478,7 +4462,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>VIZTA (ex-Nexity Portugal)</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -4489,114 +4473,110 @@
       <c r="C73" s="7" t="inlineStr"/>
       <c r="D73" s="5" t="inlineStr">
         <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
           <t>info@ancora-inv.com</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>ancora-inv.com</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+      <c r="M74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Antrix</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4606,22 +4586,22 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
+          <t>900 264 096 (ES)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>info@antrix.pt</t>
+          <t>info@aedashomes.com</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>antrix.pt</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -4631,27 +4611,27 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
@@ -4659,7 +4639,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Arish Capital Partners</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4669,44 +4649,52 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+          <t>+351 917 498 714</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>info@antrix.pt</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>arishcapitalpartners.com</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Grândola</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Fonte: diarioimobiliario.pt</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
@@ -4714,7 +4702,7 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4724,52 +4712,44 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>info@carvoeirobranco.com</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (CEO)</t>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
@@ -4777,7 +4757,7 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4787,56 +4767,60 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>casais@casais.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
+          <t>Erik de Vlieger (CEO)</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4846,17 +4830,17 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 253 305 490</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4871,35 +4855,31 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
-        </is>
-      </c>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4909,52 +4889,52 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 461 462</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>geral@castro-group.pt</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
+          <t>Paulo Castro (CEO)</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
@@ -4962,7 +4942,7 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4972,48 +4952,60 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>+351 234 480 570</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>info@civilria.pt</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+        </is>
+      </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr"/>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
       <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>DST Real Estate (Grupo dst)</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5023,52 +5015,48 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>+351 253 307 200</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>geral@dstsgps.com</t>
-        </is>
-      </c>
+          <t>+351 253 089 932</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>dstsgps.com</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
+          <t>Guimarães</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
-        </is>
-      </c>
+      <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Museu no centro histórico de Braga (Em construção)</t>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Baptista Antunes (CEO)</t>
+        </is>
+      </c>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>DST Real Estate (Grupo dst)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5078,56 +5066,52 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
+          <t>+351 253 307 200</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>geral@dstsgps.com</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dstsgps.com</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
+          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Museu no centro histórico de Braga (Em construção)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
-        </is>
-      </c>
+          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5137,56 +5121,56 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>geral@garcia.pt</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
+          <t>Reinaldo Teixeira (Administrador)</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5196,60 +5180,56 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>aca@grupo-aca.com</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
-        </is>
-      </c>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5259,56 +5239,60 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+        </is>
+      </c>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5318,17 +5302,17 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 253 685 109</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>acrescentar@grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -5343,35 +5327,31 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
-        </is>
-      </c>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5381,52 +5361,60 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
+          <t>+351 253 105 331</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>geral@arliz.co</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5436,52 +5424,52 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>273 332 784 (confirmar)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5491,56 +5479,52 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5550,43 +5534,47 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr"/>
+          <t>+351 934 175 642</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>geral@jhomea.pt</t>
+        </is>
+      </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>José Miguel Afonso (CEO/fundador)</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
@@ -5595,7 +5583,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5605,56 +5593,52 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>info@pinehill.pt</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+        </is>
+      </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5664,52 +5648,48 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>info@quintadolago.com</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Almancil</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
+          <t>Nuno Pinheiro (fundador)</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
@@ -5717,7 +5697,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5727,52 +5707,60 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 289 390 700</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@quintadolago.com</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+          <t>Almancil</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
+          <t>Resort residencial/golfe</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5782,48 +5770,52 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5833,18 +5825,18 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
+          <t>+351 939 443 765</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -5855,7 +5847,7 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5865,20 +5857,16 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5888,56 +5876,52 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 219 362 960</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -5947,87 +5931,107 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>tps.com.pt</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Fonte: omirante.pt</t>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
-      <c r="D99" s="5" t="inlineStr"/>
-      <c r="E99" s="5" t="inlineStr"/>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr"/>
-      <c r="L99" s="5" t="inlineStr"/>
-      <c r="M99" s="5" t="inlineStr"/>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: omirante.pt</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Amorim Luxury</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6040,37 +6044,33 @@
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Grândola/Lagoa</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="5" t="inlineStr"/>
       <c r="M100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6083,33 +6083,37 @@
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
       <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6122,37 +6126,33 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="5" t="inlineStr"/>
       <c r="M102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6162,35 +6162,31 @@
       </c>
       <c r="C103" s="7" t="inlineStr"/>
       <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+          <t>João Bugalho (CEO)</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr"/>
@@ -6199,7 +6195,7 @@
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6209,36 +6205,44 @@
       </c>
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
-        </is>
-      </c>
-      <c r="K104" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L104" s="5" t="inlineStr"/>
       <c r="M104" s="5" t="inlineStr"/>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6251,23 +6255,23 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr"/>
@@ -6277,7 +6281,7 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6287,14 +6291,10 @@
       </c>
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -6305,12 +6305,12 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr"/>
@@ -6320,7 +6320,7 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6330,10 +6330,14 @@
       </c>
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="5" t="inlineStr"/>
-      <c r="E107" s="5" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -6344,12 +6348,12 @@
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -6359,7 +6363,7 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6372,23 +6376,23 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr"/>
@@ -6398,7 +6402,7 @@
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6408,30 +6412,26 @@
       </c>
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: diariocoimbra.pt</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr"/>
@@ -6441,7 +6441,7 @@
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6451,26 +6451,30 @@
       </c>
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: brainsre.news</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr"/>
@@ -6480,7 +6484,7 @@
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6493,41 +6497,33 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr"/>
+      <c r="L111" s="5" t="inlineStr"/>
       <c r="M111" s="5" t="inlineStr"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6540,37 +6536,41 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
-      <c r="L112" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M112" s="5" t="inlineStr"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6583,28 +6583,28 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr"/>
@@ -6613,7 +6613,7 @@
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6623,14 +6623,10 @@
       </c>
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -6641,17 +6637,17 @@
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr"/>
@@ -6660,7 +6656,7 @@
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6670,31 +6666,35 @@
       </c>
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr"/>
-      <c r="E115" s="5" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr"/>
@@ -6703,7 +6703,7 @@
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6716,7 +6716,7 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -6727,22 +6727,26 @@
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K116" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L116" s="5" t="inlineStr"/>
       <c r="M116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6755,23 +6759,23 @@
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr"/>
@@ -6781,7 +6785,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6794,23 +6798,23 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr"/>
@@ -6820,7 +6824,7 @@
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -6830,14 +6834,10 @@
       </c>
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -6848,12 +6848,12 @@
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr"/>
@@ -6863,7 +6863,7 @@
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -6875,12 +6875,12 @@
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>ferreirabuildpower.com</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
@@ -6891,26 +6891,22 @@
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: genuinoinvestments.com</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr"/>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -6922,38 +6918,42 @@
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -6963,10 +6963,14 @@
       </c>
       <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr"/>
-      <c r="E122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>glowing.pt</t>
+        </is>
+      </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
@@ -6977,12 +6981,12 @@
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr"/>
@@ -6992,7 +6996,7 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -7002,36 +7006,36 @@
       </c>
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F123" s="7" t="inlineStr"/>
-      <c r="G123" s="7" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr"/>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Seixal</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr"/>
       <c r="L123" s="5" t="inlineStr"/>
       <c r="M123" s="5" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7043,33 +7047,25 @@
       <c r="D124" s="5" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>Sintra</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr"/>
+      <c r="G124" s="7" t="inlineStr"/>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr"/>
@@ -7078,7 +7074,7 @@
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7088,31 +7084,35 @@
       </c>
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr"/>
@@ -7121,7 +7121,7 @@
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7134,41 +7134,37 @@
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L126" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7178,25 +7174,21 @@
       </c>
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="5" t="inlineStr"/>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
+      <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
@@ -7204,14 +7196,22 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K127" s="5" t="inlineStr"/>
-      <c r="L127" s="5" t="inlineStr"/>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7223,42 +7223,38 @@
       <c r="D128" s="5" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>gruponbportugal.pt</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr"/>
       <c r="L128" s="5" t="inlineStr"/>
       <c r="M128" s="5" t="inlineStr"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7270,33 +7266,33 @@
       <c r="D129" s="5" t="inlineStr"/>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
+          <t>Fonte: gruponb.pt</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
+          <t>Ioav Blanche (presidente)</t>
         </is>
       </c>
       <c r="L129" s="5" t="inlineStr"/>
@@ -7305,7 +7301,7 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7317,38 +7313,42 @@
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K130" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7360,28 +7360,28 @@
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>hillside.pt</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+          <t>Fonte: remax.pt, hillside.pt</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr"/>
@@ -7391,7 +7391,7 @@
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7401,10 +7401,14 @@
       </c>
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>zenithresidences.pt</t>
+        </is>
+      </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -7415,12 +7419,12 @@
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr"/>
@@ -7430,7 +7434,7 @@
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7440,48 +7444,36 @@
       </c>
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>jpaiva.pt</t>
-        </is>
-      </c>
+      <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K133" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L133" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr"/>
+      <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7493,38 +7485,46 @@
       <c r="D134" s="5" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>leparc.pt</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr"/>
-      <c r="L134" s="5" t="inlineStr"/>
+          <t>Fonte: jpaiva.pt</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7536,42 +7536,38 @@
       <c r="D135" s="5" t="inlineStr"/>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>leparc.pt</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr">
-        <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
+          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr"/>
       <c r="L135" s="5" t="inlineStr"/>
       <c r="M135" s="5" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7581,31 +7577,35 @@
       </c>
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
+          <t>Fonte: luxpremium.net</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+          <t>Claude Berda (fundador)</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr"/>
@@ -7614,7 +7614,7 @@
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7627,33 +7627,37 @@
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr"/>
+          <t>Fonte: oconnormurphy.ie</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+        </is>
+      </c>
       <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7663,44 +7667,36 @@
       </c>
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr">
-        <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr"/>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7712,12 +7708,12 @@
       <c r="D139" s="5" t="inlineStr"/>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>mellordc.pt</t>
+          <t>maveninvest.pt</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -7728,30 +7724,26 @@
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: maveninvest.pt</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7761,36 +7753,48 @@
       </c>
       <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr"/>
-      <c r="L140" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7803,37 +7807,33 @@
       <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr">
-        <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: ireland-portugal.com</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr"/>
       <c r="L141" s="5" t="inlineStr"/>
       <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -7843,40 +7843,40 @@
       </c>
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr"/>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
       <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -7888,12 +7888,12 @@
       <c r="D143" s="5" t="inlineStr"/>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>ombria.com</t>
+          <t>oconnormurphy.ie</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
@@ -7901,37 +7901,25 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+      <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
-        </is>
-      </c>
-      <c r="K143" s="5" t="inlineStr">
-        <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L143" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr"/>
+      <c r="L143" s="5" t="inlineStr"/>
       <c r="M143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -7941,10 +7929,14 @@
       </c>
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -7952,25 +7944,37 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H144" s="5" t="inlineStr"/>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
-        </is>
-      </c>
-      <c r="K144" s="5" t="inlineStr"/>
-      <c r="L144" s="5" t="inlineStr"/>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -7983,37 +7987,33 @@
       <c r="E145" s="5" t="inlineStr"/>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
-        </is>
-      </c>
-      <c r="K145" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr"/>
       <c r="L145" s="5" t="inlineStr"/>
       <c r="M145" s="5" t="inlineStr"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -8026,33 +8026,37 @@
       <c r="E146" s="5" t="inlineStr"/>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K146" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L146" s="5" t="inlineStr"/>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8065,23 +8069,23 @@
       <c r="E147" s="5" t="inlineStr"/>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: idealista.pt, construir.pt</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr"/>
@@ -8091,7 +8095,7 @@
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8104,37 +8108,33 @@
       <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K148" s="5" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr"/>
       <c r="L148" s="5" t="inlineStr"/>
       <c r="M148" s="5" t="inlineStr"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8144,35 +8144,31 @@
       </c>
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E149" s="5" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr">
         <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
         </is>
       </c>
       <c r="L149" s="5" t="inlineStr"/>
@@ -8181,7 +8177,7 @@
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8193,46 +8189,42 @@
       <c r="D150" s="5" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>soccal-vaz.com</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
       <c r="K150" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L150" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8244,12 +8236,12 @@
       <c r="D151" s="5" t="inlineStr"/>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>soccal-vaz.com</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -8260,22 +8252,22 @@
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: eco.sapo.pt</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
+          <t>António Vaz (fundador e CEO)</t>
         </is>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
         </is>
       </c>
       <c r="M151" s="5" t="inlineStr"/>
@@ -8283,7 +8275,7 @@
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8293,36 +8285,48 @@
       </c>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr"/>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>solidsentinel.pt</t>
+        </is>
+      </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K152" s="5" t="inlineStr"/>
-      <c r="L152" s="5" t="inlineStr"/>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8332,44 +8336,36 @@
       </c>
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>sonaesierra.com</t>
-        </is>
-      </c>
+      <c r="E153" s="5" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K153" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr"/>
       <c r="L153" s="5" t="inlineStr"/>
       <c r="M153" s="5" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8381,38 +8377,42 @@
       <c r="D154" s="5" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>southshoreinvest.com</t>
+          <t>sonaesierra.com</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
-        </is>
-      </c>
-      <c r="K154" s="5" t="inlineStr"/>
+          <t>Fonte: rtp.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
       <c r="L154" s="5" t="inlineStr"/>
       <c r="M154" s="5" t="inlineStr"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8424,42 +8424,38 @@
       <c r="D155" s="5" t="inlineStr"/>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>southshoreinvest.com</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
-        </is>
-      </c>
-      <c r="K155" s="5" t="inlineStr">
-        <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: southshoreinvest.com</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr"/>
       <c r="L155" s="5" t="inlineStr"/>
       <c r="M155" s="5" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -8469,36 +8465,44 @@
       </c>
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="5" t="inlineStr"/>
-      <c r="E156" s="5" t="inlineStr"/>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K156" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
       <c r="L156" s="5" t="inlineStr"/>
       <c r="M156" s="5" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -8508,30 +8512,26 @@
       </c>
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="5" t="inlineStr"/>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>valentavillas.com</t>
-        </is>
-      </c>
+      <c r="E157" s="5" t="inlineStr"/>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
+          <t>Fonte: racius.com, idealista.pt</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -8551,26 +8551,30 @@
       </c>
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="5" t="inlineStr"/>
-      <c r="E158" s="5" t="inlineStr"/>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>valentavillas.com</t>
+        </is>
+      </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr"/>
@@ -8580,7 +8584,7 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -8590,44 +8594,36 @@
       </c>
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="5" t="inlineStr"/>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>ugp.ie</t>
-        </is>
-      </c>
+      <c r="E159" s="5" t="inlineStr"/>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K159" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr"/>
       <c r="L159" s="5" t="inlineStr"/>
       <c r="M159" s="5" t="inlineStr"/>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -8639,12 +8635,12 @@
       <c r="D160" s="5" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>valedolobo.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
@@ -8652,29 +8648,29 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H160" s="5" t="inlineStr">
-        <is>
-          <t>Parque do Golfe</t>
-        </is>
-      </c>
+      <c r="H160" s="5" t="inlineStr"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+          <t>The Shipyard (Comercialização)</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
-        </is>
-      </c>
-      <c r="K160" s="5" t="inlineStr"/>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L160" s="5" t="inlineStr"/>
       <c r="M160" s="5" t="inlineStr"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Vale do Lobo Resort</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -8686,33 +8682,80 @@
       <c r="D161" s="5" t="inlineStr"/>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>vilagale.com</t>
+          <t>valedolobo.com</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>Parque do Golfe</t>
+        </is>
+      </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr"/>
       <c r="L161" s="5" t="inlineStr"/>
       <c r="M161" s="5" t="inlineStr"/>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr"/>
+      <c r="D162" s="5" t="inlineStr"/>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr"/>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr"/>
+      <c r="L162" s="5" t="inlineStr"/>
+      <c r="M162" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8754,7 +8797,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
@@ -8774,7 +8817,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -8784,7 +8827,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -644,7 +644,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ALMA Development</t>
+          <t>AFA (Grupo AFA)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -654,17 +654,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>+351 218 019 249</t>
+          <t>+351 218 981 190</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>geral@almadevelopment.pt</t>
+          <t>anaborges@afa.pt</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>almadevelopment.pt</t>
+          <t>afa-realestate.com</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -679,35 +679,31 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Torre Duarte Pacheco, 1070-101</t>
+          <t>Av. D. João II, nº25, 2º, 1990-079</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Caxias Heights (Oeiras) (Comercialização) | 3 projetos Grande Porto/Lisboa (Em construção)</t>
+          <t>Savoy Residence D'Ávila (Em construção)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Fundada 2022, ligada à Panhard. Tel. móvel 914 192 506</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Carlos Morgado (Diretor Executivo)</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/cafmorgado/</t>
-        </is>
-      </c>
+          <t>Victor de Sousa (Diretor-Geral AFA Real Estate)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AM48</t>
+          <t>ALMA Development</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -717,17 +713,17 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>+351 910 713 848</t>
+          <t>+351 218 019 249</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>quintadoalverde@am48.pt</t>
+          <t>geral@almadevelopment.pt</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>am48.pt</t>
+          <t>almadevelopment.pt</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -742,27 +738,27 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Lisboa (sede) · Aveiro</t>
+          <t>Torre Duarte Pacheco, 1070-101</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Alverde (Oeiras) (Comercialização) | Foz de Prata + Ceramium (Aveiro) (Em construção) | Ópera LX / Focus LX / Promenade (Lisboa) (Concluído)</t>
+          <t>Caxias Heights (Oeiras) (Comercialização) | 3 projetos Grande Porto/Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Telefone é da linha comercial Quinta do Alverde</t>
+          <t>Fundada 2022, ligada à Panhard. Tel. móvel 914 192 506</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Alejandro Martins (Founder &amp; CEO)</t>
+          <t>Carlos Morgado (Diretor Executivo)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alejandro-martins-74b18590/</t>
+          <t>https://www.linkedin.com/in/cafmorgado/</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -770,7 +766,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AVENUE</t>
+          <t>AM48</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -780,17 +776,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>+351 215 989 523</t>
+          <t>+351 910 713 848</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>geral@avenue.pt</t>
+          <t>quintadoalverde@am48.pt</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>avenue.pt</t>
+          <t>am48.pt</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -805,27 +801,27 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Rua Serpa Pinto 14A, 3º, 1200-445 (Porto: Av. Boavista 772, +351 220 990 530)</t>
+          <t>Lisboa (sede) · Aveiro</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Nolipa (Campo Grande) (Em construção) | Bonjardim (Porto) (Concluído)</t>
+          <t>Quinta do Alverde (Oeiras) (Comercialização) | Foz de Prata + Ceramium (Aveiro) (Em construção) | Ópera LX / Focus LX / Promenade (Lisboa) (Concluído)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Promotor de referência Lisboa/Porto</t>
+          <t>Telefone é da linha comercial Quinta do Alverde</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Aniceto Viegas (CEO)</t>
+          <t>Alejandro Martins (Founder &amp; CEO)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/aniceto-viegas-02586a1</t>
+          <t>https://www.linkedin.com/in/alejandro-martins-74b18590/</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -833,7 +829,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Benoit Properties International</t>
+          <t>Arts Investments, SA</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -843,13 +839,13 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+44 161 250 5300 (UK)</t>
+          <t>+351 291 281 182</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>benoitproperties.com</t>
+          <t>artsinvestments.com</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -864,31 +860,27 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Rua Tierno Galvan, Amoreiras Torre 3, piso 6, sala 612, 1070-274</t>
+          <t>Av. Eng. Duarte Pacheco, Amoreiras Torre 2, 10º, sala 10, 1070-101</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>114 Avenida Central (Braga) (Comercialização) | Alexandre Braga 10 (Lisboa) (Em construção)</t>
+          <t>3 projetos em curso (nomes não encontrados) (Em construção/desenvolvimento)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Só telefone UK publicado</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Fredrick J. Benoit II (Director/co-fundador, 50% com Matthew Lavin)</t>
-        </is>
-      </c>
+          <t>Fonte: vidaimobiliaria.com. Nota: nº de telefone tem indicativo da Madeira (291) — confirmar antes de ligar</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BESIX RED Portugal</t>
+          <t>AVENUE</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -898,17 +890,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>+351 216 037 894</t>
+          <t>+351 215 989 523</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>info@besixred.com</t>
+          <t>geral@avenue.pt</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>besixred.com</t>
+          <t>avenue.pt</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -923,27 +915,27 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Av. Duque de Loulé 106, 9º, 1050-093</t>
+          <t>Rua Serpa Pinto 14A, 3º, 1200-445 (Porto: Av. Boavista 772, +351 220 990 530)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>DUUO (Praça de Espanha) (Em construção) | Parque Oriente (Parque das Nações) (Em construção) | WellBe (Em construção)</t>
+          <t>Nolipa (Campo Grande) (Em construção) | Bonjardim (Porto) (Concluído)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Promotor pan-europeu (grupo BESIX)</t>
+          <t>Promotor de referência Lisboa/Porto</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Nicolas Goffin (Country Director Portugal· CEO do grupo é Gabriel Uzgen, Bruxelas)</t>
+          <t>Aniceto Viegas (CEO)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nicolas-goffin-32707487/</t>
+          <t>https://pt.linkedin.com/in/aniceto-viegas-02586a1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -951,7 +943,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Blue Buffalo Capital</t>
+          <t>Benoit Properties International</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -961,22 +953,18 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>+351 934 643 306</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>geral@bluebuffalocapital.com</t>
-        </is>
-      </c>
+          <t>+44 161 250 5300 (UK)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>bluebuffalocapital.com</t>
+          <t>benoitproperties.com</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -986,35 +974,31 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Rua de São Tomé e Príncipe 23 B, 2765-282 Estoril</t>
+          <t>Rua Tierno Galvan, Amoreiras Torre 3, piso 6, sala 612, 1070-274</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Residencial de luxo Grande Lisboa (Em construção)</t>
+          <t>114 Avenida Central (Braga) (Comercialização) | Alexandre Braga 10 (Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Desde 2015, sócios com &gt;500M€ promovidos</t>
+          <t>Só telefone UK publicado</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Celma de Almeida Lavradio (Co-Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/celma-de-almeida-lavradio-645baa43</t>
-        </is>
-      </c>
+          <t>Fredrick J. Benoit II (Director/co-fundador, 50% com Matthew Lavin)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Bondstone</t>
+          <t>BESIX RED Portugal</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1024,13 +1008,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>+351 211 349 157</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>+351 216 037 894</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>info@besixred.com</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>bondstone.com</t>
+          <t>besixred.com</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1045,27 +1033,27 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Rua Castilho 39, 10º C, 1250-068</t>
+          <t>Av. Duque de Loulé 106, 9º, 1050-093</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>The Coral (Cascais) (Em construção)</t>
+          <t>DUUO (Praça de Espanha) (Em construção) | Parque Oriente (Parque das Nações) (Em construção) | WellBe (Em construção)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Gestora regulada CMVM, capital internacional</t>
+          <t>Promotor pan-europeu (grupo BESIX)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Paulo Loureiro (fundador e CEO)</t>
+          <t>Nicolas Goffin (Country Director Portugal· CEO do grupo é Gabriel Uzgen, Bruxelas)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paulo-loureiro-8a46016/</t>
+          <t>https://www.linkedin.com/in/nicolas-goffin-32707487/</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
@@ -1073,7 +1061,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Coporgest</t>
+          <t>Blue Buffalo Capital</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1083,22 +1071,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>+351 213 108 900</t>
+          <t>+351 934 643 306</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>geral@coporgest.com</t>
+          <t>geral@bluebuffalocapital.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>coporgest.com</t>
+          <t>bluebuffalocapital.com</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1108,31 +1096,35 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 245, 9º C, 1250-143</t>
+          <t>Rua de São Tomé e Príncipe 23 B, 2765-282 Estoril</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Comporta Beach Resort (Em construção)</t>
+          <t>Residencial de luxo Grande Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Promotor de Lisboa desde 2004</t>
+          <t>Desde 2015, sócios com &gt;500M€ promovidos</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Ferreira (fundador e CEO, homónimos sem confirmação total)</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>Celma de Almeida Lavradio (Co-Founder &amp; CEO)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/celma-de-almeida-lavradio-645baa43</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EastBanc Portugal</t>
+          <t>Bondstone</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1142,17 +1134,13 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>+351 213 404 150</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>geral@eastbanc.com</t>
-        </is>
-      </c>
+          <t>+351 211 349 157</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>eastbanc.pt</t>
+          <t>bondstone.com</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1167,31 +1155,35 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Rua da Escola Politécnica 38, 2º, 1250-102</t>
+          <t>Rua Castilho 39, 10º C, 1250-068</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8 projetos Príncipe Real (Em construção) | DPV Block (Comercialização) | EmbaiXada (Concluído)</t>
+          <t>The Coral (Cascais) (Em construção)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20 anos em Príncipe Real, &gt;20 edifícios</t>
+          <t>Gestora regulada CMVM, capital internacional</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Tiago Eiró (CEO)</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>Paulo Loureiro (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulo-loureiro-8a46016/</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Easyliving</t>
+          <t>Ceetrus / Nhood Portugal</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1201,38 +1193,42 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>+351 961 866 297</t>
+          <t>+351 210 537 815</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>info@easyliving.pt</t>
+          <t>news@nhood.pt</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>easyliving.pt</t>
+          <t>nhood.pt</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Rua Artilharia 1, nº51, Páteo Bagatela, Ed. 3, 1250-038</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Boavista Garden (Av. da Boavista) (Em construção) | Aspreladas Easy (Comercialização)</t>
+          <t>Pipeline nacional 15 cidades (nomes não encontrados) (Planeamento)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Compra, reabilitação e construção. Comercialização via RE/MAX Collection</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -1242,7 +1238,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EMERGE – Mota-Engil Real Estate</t>
+          <t>Coporgest</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1252,60 +1248,56 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>+351 225 190 362</t>
+          <t>+351 213 108 900</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>emerge@mota-engil.pt</t>
+          <t>geral@coporgest.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>emerge-realestate.pt</t>
+          <t>coporgest.com</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Calçada do Rêgo Lameiro 38, 4300-454</t>
+          <t>Av. da Liberdade 245, 9º C, 1250-143</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>OPO-City (Porto/Matosinhos) (Comercialização) | AURIOS (Comercialização)</t>
+          <t>Comporta Beach Resort (Em construção)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Promotora do grupo Mota-Engil</t>
+          <t>Promotor de Lisboa desde 2004</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Vitor Paulo Pinho (CEO)</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/vitor-paulo-pinho-0a7952173/</t>
-        </is>
-      </c>
+          <t>Sérgio Ferreira (fundador e CEO, homónimos sem confirmação total)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Fercopor</t>
+          <t>EastBanc Portugal</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1315,43 +1307,47 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>+351 226 091 113</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>+351 213 404 150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>geral@eastbanc.com</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>fercopor.pt</t>
+          <t>eastbanc.pt</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Av. da França 20, Sala 509, 4050-275</t>
+          <t>Rua da Escola Politécnica 38, 2º, 1250-102</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Boavista (2 projetos) (Planeamento) | Vila do Conde (Planeamento)</t>
+          <t>8 projetos Príncipe Real (Em construção) | DPV Block (Comercialização) | EmbaiXada (Concluído)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Luxo desde 1981. Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>20 anos em Príncipe Real, &gt;20 edifícios</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Mário Almeida (Administrador)</t>
+          <t>Tiago Eiró (CEO)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1360,7 +1356,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Fidelidade Property</t>
+          <t>Easyliving</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1370,42 +1366,38 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>+351 217 807 772</t>
+          <t>+351 961 866 297</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>geral@fidelidadeproperty.pt</t>
+          <t>info@easyliving.pt</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>fidelidadeproperty.pt</t>
+          <t>easyliving.pt</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Largo do Calhariz 30, 1249-001</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>EntreCampos (antiga Feira Popular) (Em construção)</t>
+          <t>Boavista Garden (Av. da Boavista) (Em construção) | Aspreladas Easy (Comercialização)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário da Fidelidade. Projeto: info@entrecampos.pt</t>
+          <t>Compra, reabilitação e construção. Comercialização via RE/MAX Collection</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1415,7 +1407,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FIDES – Investimentos e Gestão Imobiliária</t>
+          <t>EMERGE – Mota-Engil Real Estate</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1425,48 +1417,60 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>+351 213 877 749</t>
+          <t>+351 225 190 362</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>diogopintogoncalves@imofides.com</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>emerge@mota-engil.pt</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>emerge-realestate.pt</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Rua Tierno Galvan, Amoreiras Torre 3, 6º, sala 607, 1070-274</t>
+          <t>Calçada do Rêgo Lameiro 38, 4300-454</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Promoção residencial (Em construção)</t>
+          <t>OPO-City (Porto/Matosinhos) (Comercialização) | AURIOS (Comercialização)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Projeto concreto não nomeado nas fontes</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>Promotora do grupo Mota-Engil</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Vitor Paulo Pinho (CEO)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vitor-paulo-pinho-0a7952173/</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Grupo Madre / Madre Imobiliário</t>
+          <t>Fercopor</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1476,47 +1480,43 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>+351 213 243 220</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>geral@madreimobiliario.com</t>
-        </is>
-      </c>
+          <t>+351 226 091 113</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>madreimobiliario.com</t>
+          <t>fercopor.pt</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Campo Grande 28, 11º, 1700-093</t>
+          <t>Av. da França 20, Sala 509, 4050-275</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>A-Living (Areeiro) (Planeamento) | Parque da Cidade (Setúbal) (Em construção)</t>
+          <t>Boavista (2 projetos) (Planeamento) | Vila do Conde (Planeamento)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Presidente António Parente. Tel. móvel 914 070 350</t>
+          <t>Luxo desde 1981. Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Nuno Dias (Diretor Geral da Madre Imobiliário· presidente do grupo é António Parente)</t>
+          <t>Mário Almeida (Administrador)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1525,7 +1525,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Habitat Invest</t>
+          <t>Fidelidade Property</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>+351 213 461 024</t>
+          <t>+351 217 807 772</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>info@habitatinvest.pt</t>
+          <t>geral@fidelidadeproperty.pt</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>habitatinvest.pt</t>
+          <t>fidelidadeproperty.pt</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1560,31 +1560,27 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Rua da Moeda 4, 1200-275</t>
+          <t>Largo do Calhariz 30, 1249-001</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15 projetos em desenvolvimento (Em construção) | ALMAR SOUTH LIVING (Almada) (Em construção/comercialização) | AURYA (Santo António dos Cavaleiros, Loures) (Em construção)</t>
+          <t>EntreCampos (antiga Feira Popular) (Em construção)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Fundada 2001 · inclui Habitat Ventures/Project/Property/Broker</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Luís Corrêa de Barros (fundador e CEO)</t>
-        </is>
-      </c>
+          <t>Braço imobiliário da Fidelidade. Projeto: info@entrecampos.pt</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>J. Dias &amp; Dias</t>
+          <t>FIDES – Investimentos e Gestão Imobiliária</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1594,22 +1590,18 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>+351 214 422 593</t>
+          <t>+351 213 877 749</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>geral@jdiasdias.pt</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>jdiasdias.pt</t>
-        </is>
-      </c>
+          <t>diogopintogoncalves@imofides.com</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1619,17 +1611,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Av. Venceslau Balseiro da Grande Guerra, Quinta das Marianas, Parede</t>
+          <t>Rua Tierno Galvan, Amoreiras Torre 3, 6º, sala 607, 1070-274</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Urban Living (Carcavelos/Parede) (Comercialização)</t>
+          <t>Promoção residencial (Em construção)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Fundada 1960, alvará ICC 12463. Tel. móvel 961 682 789</t>
+          <t>Projeto concreto não nomeado nas fontes</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -1639,7 +1631,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>JPS Group</t>
+          <t>Fortera</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1649,60 +1641,56 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>+351 218 371 025</t>
+          <t>+351 220 110 929</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>secretariado@jpsgroup.pt</t>
+          <t>info@fortera.pt</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>jpsgroup.pt</t>
+          <t>fortera.pt</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Av. Almirante Gago Coutinho 126</t>
+          <t>Rua de Rei Ramiro 870, 5º A, 4400-281</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>SkyCity (Carnaxide) (Em construção) | Herdade Real de Santiago (Comercialização) | Terraços de São Francisco (Comercialização)</t>
+          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Promotora com construtora e imobiliária próprias</t>
+          <t>Fundadores Elad Dror e Nir Shalom. Nota: Elad Dror foi detido na Operação Babel (2023, corrupção) — confirmar situação atual antes de contacto</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>João Sousa (CEO)</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/joao-sousa-7802352a</t>
-        </is>
-      </c>
+          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Krest Investments</t>
+          <t>Grupo Madre / Madre Imobiliário</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1712,17 +1700,17 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>+351 215 873 920</t>
+          <t>+351 213 243 220</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>info@krestinvestments.com</t>
+          <t>geral@madreimobiliario.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>krestinvestments.com</t>
+          <t>madreimobiliario.com</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1737,35 +1725,31 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Av. Eng.º Duarte Pacheco, Amoreiras Torre 1, piso 14, sala 2, 1070-101</t>
+          <t>Campo Grande 28, 11º, 1700-093</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Lisboa / Porto / Algarve (Comercialização)</t>
+          <t>A-Living (Areeiro) (Planeamento) | Parque da Cidade (Setúbal) (Em construção)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Belga, em Portugal desde 2014</t>
+          <t>Presidente António Parente. Tel. móvel 914 070 350</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Claude Kandiyoti (CEO)</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/claude-kandiyoti-287b9298/</t>
-        </is>
-      </c>
+          <t>Nuno Dias (Diretor Geral da Madre Imobiliário· presidente do grupo é António Parente)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Kronos Homes Portugal</t>
+          <t>Habitat Invest</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1775,13 +1759,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>+351 211 227 710</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>+351 213 461 024</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>info@habitatinvest.pt</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>kronoshomes.com</t>
+          <t>habitatinvest.pt</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1796,35 +1784,31 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 245, 1250-143</t>
+          <t>Rua da Moeda 4, 1200-275</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>The One (Lisboa) (Comercialização) | Lagos e Alcantarilha (Comercialização) | Flamingos Salgados (Comercialização) | Monte Santo (Carvoeiro) (Comercialização)</t>
+          <t>15 projetos em desenvolvimento (Em construção) | ALMAR SOUTH LIVING (Almada) (Em construção/comercialização) | AURYA (Santo António dos Cavaleiros, Loures) (Em construção)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Entidade KIG Portugal (NIF 514667265)</t>
+          <t>Fundada 2001 · inclui Habitat Ventures/Project/Property/Broker</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Rui Meneses Ferreira (CEO)</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/rui-meneses-ferreira-97057825/</t>
-        </is>
-      </c>
+          <t>Luís Corrêa de Barros (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Lantia</t>
+          <t>J. Dias &amp; Dias</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1834,22 +1818,22 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>+351 211 165 360</t>
+          <t>+351 214 422 593</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>geral@lantia.pt</t>
+          <t>geral@jdiasdias.pt</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>lantia.pt</t>
+          <t>jdiasdias.pt</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1859,31 +1843,27 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Praça Duque de Saldanha 1, 4F, 1050-054</t>
+          <t>Av. Venceslau Balseiro da Grande Guerra, Quinta das Marianas, Parede</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Residencial e turístico Grande Lisboa (Em construção)</t>
+          <t>Urban Living (Carcavelos/Parede) (Comercialização)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Constituída em Macau 2015</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Eduardo Kol Netto de Almeida (CEO)</t>
-        </is>
-      </c>
+          <t>Fundada 1960, alvará ICC 12463. Tel. móvel 961 682 789</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Libertas – Investimentos Imobiliários</t>
+          <t>JPS Group</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1893,17 +1873,17 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>+351 213 243 050</t>
+          <t>+351 218 371 025</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>libertas@libertas.pt</t>
+          <t>secretariado@jpsgroup.pt</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>libertas.pt</t>
+          <t>jpsgroup.pt</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1918,31 +1898,35 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 129, 8º A, 1250-140</t>
+          <t>Av. Almirante Gago Coutinho 126</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Lux Garden EVO (Faro) (Em construção) | Novos projetos Algarve (Planeamento)</t>
+          <t>SkyCity (Carnaxide) (Em construção) | Herdade Real de Santiago (Comercialização) | Terraços de São Francisco (Comercialização)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18 projetos no Algarve, &gt;800 unidades entregues · ISO 14001</t>
+          <t>Promotora com construtora e imobiliária próprias</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>António Gonçalves (Fundador)</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>João Sousa (CEO)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/joao-sousa-7802352a</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Major Development</t>
+          <t>Krest Investments</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1952,17 +1936,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>+351 210 912 130</t>
+          <t>+351 215 873 920</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>contacto@majordevelop.com</t>
+          <t>info@krestinvestments.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>majordevelop.com</t>
+          <t>krestinvestments.com</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1977,27 +1961,27 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Cais do Gás, Armazém H, 1200-109</t>
+          <t>Av. Eng.º Duarte Pacheco, Amoreiras Torre 1, piso 14, sala 2, 1070-101</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Garden Cascais (Planeamento) | Solo Oeiras (Planeamento) | Vistabella (Oeiras) (Planeamento) | Santa Apolónia (Planeamento) | Nouveau Lisboa (Av. Berna) (Concluído)</t>
+          <t>Lisboa / Porto / Algarve (Comercialização)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>&gt;100M€ anunciados 2026. Fonte: diarioimobiliario.pt</t>
+          <t>Belga, em Portugal desde 2014</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Costa (CEO, confiança baixa — só rocketreach)</t>
+          <t>Claude Kandiyoti (CEO)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/gabriel-costa-7436b5158</t>
+          <t>https://www.linkedin.com/in/claude-kandiyoti-287b9298/</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
@@ -2005,7 +1989,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Mesmo Valor (Mesmovalor, S.A.)</t>
+          <t>Kronos Homes Portugal</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2015,56 +1999,56 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>+351 223 274 626</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>geral@mesmovalor.pt</t>
-        </is>
-      </c>
+          <t>+351 211 227 710</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>mesmovalor.pt</t>
+          <t>kronoshomes.com</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Rua do Pinheiro Manso 147, 4100-412</t>
+          <t>Av. da Liberdade 245, 1250-143</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Boavista Tower (Comercialização)</t>
+          <t>The One (Lisboa) (Comercialização) | Lagos e Alcantarilha (Comercialização) | Flamingos Salgados (Comercialização) | Monte Santo (Carvoeiro) (Comercialização)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€. Fonte: idealista/news ago/2026</t>
+          <t>Entidade KIG Portugal (NIF 514667265)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Pedro Teixeira Paredes (CEO)</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>Rui Meneses Ferreira (CEO)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rui-meneses-ferreira-97057825/</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MEXTO Property Investment</t>
+          <t>Lantia</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2074,17 +2058,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>+351 213 461 050</t>
+          <t>+351 211 165 360</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>info@mexto.pt</t>
+          <t>geral@lantia.pt</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>mexto.pt</t>
+          <t>lantia.pt</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2099,35 +2083,31 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Rua Nova do Almada 81, 4º Dto</t>
+          <t>Praça Duque de Saldanha 1, 4F, 1050-054</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Castilho 3 (Em construção) | São Gens (Graça) (Em construção)</t>
+          <t>Residencial e turístico Grande Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Grupo suíço, 250M€ em Portugal, 71.000 m²</t>
+          <t>Constituída em Macau 2015</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Tomas Suter (Founding Member/Partner, Suíça)</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/tomas-suter-78564b9/</t>
-        </is>
-      </c>
+          <t>Eduardo Kol Netto de Almeida (CEO)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Norfin</t>
+          <t>Libertas – Investimentos Imobiliários</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2137,13 +2117,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>+351 213 182 520</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>+351 213 243 050</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>libertas@libertas.pt</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>norfin.pt</t>
+          <t>libertas.pt</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2158,35 +2142,31 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Av. Almirante Gago Coutinho 30, piso 0, 1000-017</t>
+          <t>Av. da Liberdade 129, 8º A, 1250-140</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Lisbon Heights (Alta de Lisboa) (Comercialização) | Lote Alta de Lisboa (Planeamento) | Oriente Green Campus / Campo Novo (Em construção)</t>
+          <t>Lux Garden EVO (Faro) (Em construção) | Novos projetos Algarve (Planeamento)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Gestora de investimento (2,1B€) que também promove</t>
+          <t>18 projetos no Algarve, &gt;800 unidades entregues · ISO 14001</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Miguel Mateus (CEO, recém-nomeado)</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-mateus-608b616/</t>
-        </is>
-      </c>
+          <t>António Gonçalves (Fundador)</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Noronha Sanches</t>
+          <t>Major Development</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2196,17 +2176,17 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>+351 217 220 620</t>
+          <t>+351 210 912 130</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>sales@noronhasanches.com</t>
+          <t>contacto@majordevelop.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>noronhasanches.com</t>
+          <t>majordevelop.com</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2221,27 +2201,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Campo Grande 28, 3º G, 1700-093</t>
+          <t>Cais do Gás, Armazém H, 1200-109</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>One Lush (Caxias) (Em construção) | Vila Praia (Comercialização) | Marinha Prime (Comercialização)</t>
+          <t>Garden Cascais (Planeamento) | Solo Oeiras (Planeamento) | Vistabella (Oeiras) (Planeamento) | Santa Apolónia (Planeamento) | Nouveau Lisboa (Av. Berna) (Concluído)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Promotor desde 1986</t>
+          <t>&gt;100M€ anunciados 2026. Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Pedro Sanches (CEO/fundador)</t>
+          <t>Gabriel Costa (CEO, confiança baixa — só rocketreach)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/pedro-sanches-77205825</t>
+          <t>https://pt.linkedin.com/in/gabriel-costa-7436b5158</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
@@ -2249,7 +2229,7 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Névoa, S.A.</t>
+          <t>Mesmo Valor (Mesmovalor, S.A.)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2259,44 +2239,56 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>+351 253 240 010</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>+351 223 274 626</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>geral@mesmovalor.pt</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>nevoa.pt</t>
+          <t>mesmovalor.pt</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Pinheiro Manso 147, 4100-412</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Portfólio nacional de empreendimentos (Comercialização)</t>
+          <t>Boavista Tower (Comercialização)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com, racius.com</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Capital social 5M€. Fonte: idealista/news ago/2026</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Teixeira Paredes (CEO)</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Optylon Krea</t>
+          <t>MEXTO Property Investment</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2306,17 +2298,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>+351 212 400 124</t>
+          <t>+351 213 461 050</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>sales@optylonkrea.com</t>
+          <t>info@mexto.pt</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>optylonkrea.com</t>
+          <t>mexto.pt</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2331,27 +2323,27 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Rua Alexandre Herculano 50, 10º/11º, 1250-096</t>
+          <t>Rua Nova do Almada 81, 4º Dto</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Ando Living – Alfama Club e Liberdade Club (Em construção) | Augusta Townhouse + Santos Townhouse (Comercialização)</t>
+          <t>Castilho 3 (Em construção) | São Gens (Graça) (Em construção)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,7B€ investidos · PT e Turquia</t>
+          <t>Grupo suíço, 250M€ em Portugal, 71.000 m²</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>William Tonnard (President &amp; COO· Chairman é Hakan Kodal)</t>
+          <t>Tomas Suter (Founding Member/Partner, Suíça)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/william-tonnard/</t>
+          <t>https://www.linkedin.com/in/tomas-suter-78564b9/</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
@@ -2359,7 +2351,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Qualive</t>
+          <t>Norfin</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2369,44 +2361,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>+351 226 090 545</t>
+          <t>+351 213 182 520</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>norfin.pt</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Rua D. Pedro V 410, 2º, 4150-601</t>
+          <t>Av. Almirante Gago Coutinho 30, piso 0, 1000-017</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Fábrica do Prado (Matosinhos) (Em construção)</t>
+          <t>Lisbon Heights (Alta de Lisboa) (Comercialização) | Lote Alta de Lisboa (Planeamento) | Oriente Green Campus / Campo Novo (Em construção)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Telefone do registo comercial (einforma). Comercialização JLL/Predibisa</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>Gestora de investimento (2,1B€) que também promove</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Mateus (CEO, recém-nomeado)</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-mateus-608b616/</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Quest Capital</t>
+          <t>Noronha Sanches</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2416,17 +2420,17 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>+351 213 472 435</t>
+          <t>+351 217 220 620</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>info@questcapital.eu</t>
+          <t>sales@noronhasanches.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>questcapital.eu</t>
+          <t>noronhasanches.com</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2441,27 +2445,27 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Rua António Maria Cardoso 2, 1200-027 (escritório Porto: Rua Fernandes Tomás 546)</t>
+          <t>Campo Grande 28, 3º G, 1700-093</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Antas Atrium (Porto, antigo estádio) (Em construção)</t>
+          <t>One Lush (Caxias) (Em construção) | Vila Praia (Comercialização) | Marinha Prime (Comercialização)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Com Tikehau Capital. &gt;1B€ sob gestão</t>
+          <t>Promotor desde 1986</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Carlos Vasconcellos (Founding Partner, CEO exato não confirmado)</t>
+          <t>Pedro Sanches (CEO/fundador)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/vasconcelloscarlos/</t>
+          <t>https://pt.linkedin.com/in/pedro-sanches-77205825</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
@@ -2469,7 +2473,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ReVentures – Property Developers</t>
+          <t>Névoa, S.A.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2479,17 +2483,13 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>+351 212 402 489</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>info@reventures.pt</t>
-        </is>
-      </c>
+          <t>+351 253 240 010</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>reventures.pt</t>
+          <t>nevoa.pt</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2502,37 +2502,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Campo Grande 28, 3º A, 1700-093</t>
-        </is>
-      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7 residências de estudantes (rede nacional) (Em construção) | Senior Living (Planeamento)</t>
+          <t>Portfólio nacional de empreendimentos (Comercialização)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>NIF 516390350, capital 800k€. Fonte: construir.pt abr/2026</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Hugo Gonçalves Pereira (CEO)</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/hugogpereira/</t>
-        </is>
-      </c>
+          <t>Fonte: vidaimobiliaria.com, racius.com</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Rio Capital / Grupo Rio</t>
+          <t>Optylon Krea</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2542,17 +2530,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>+351 213 861 065</t>
+          <t>+351 212 400 124</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>geral@riocapital.pt</t>
+          <t>sales@optylonkrea.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>riocapital.pt</t>
+          <t>optylonkrea.com</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2567,27 +2555,35 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Av. Duarte Pacheco, Amoreiras Torre 2, 14º D</t>
+          <t>Rua Alexandre Herculano 50, 10º/11º, 1250-096</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21 projetos residenciais Grande Porto (Em construção) | Velaris (Porto) (Planeamento) | São Vicente (Maia) (Planeamento) | Metropólis Estúdio Residence (Matosinhos) (Planeamento)</t>
+          <t>Ando Living – Alfama Club e Liberdade Club (Em construção) | Augusta Townhouse + Santos Townhouse (Comercialização)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Grupo nascido em Monção, liderado por Nuno Afonso. Fonte: idealista/news jun/2026, Público</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>1,7B€ investidos · PT e Turquia</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>William Tonnard (President &amp; COO· Chairman é Hakan Kodal)</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-tonnard/</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Rockbuilding – Soluções Imobiliárias</t>
+          <t>Overseas</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2597,13 +2593,17 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>+351 217 996 700</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>+351 911 741 900</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>info@overseasglobal.com</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>rockbuilding.com</t>
+          <t>overseasglobal.com</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2618,27 +2618,27 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, 7º A, 1070-374</t>
+          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Serviços de desenvolvimento para promotores (Em construção)</t>
+          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>ATENÇÃO: é gestor de projeto/serviços, não promotor puro</t>
+          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>José Pedro Almeida Guerra (Diretor Geral)</t>
+          <t>Pedro Vicente (CEO)</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/josé-pedro-almeida-guerra-20723679</t>
+          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
@@ -2646,7 +2646,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Royal Ventures</t>
+          <t>Prime Portugal</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2656,60 +2656,56 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>+351 916 770 322</t>
+          <t>+351 915 896 265</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>alex@royal-ventures.com</t>
+          <t>info@primelisbon.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>royal-ventures.com</t>
+          <t>primelisbon.com</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Edifício Oceanus, Av. da Boavista 3227, 4100-137</t>
+          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação centro histórico do Porto (Em construção)</t>
+          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
+          <t>Telefone/site é da 'Prime Lisbon', mesma morada — confirmar que é a mesma entidade antes de contactar</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Udi Yadin (fundador/General Partner)</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/udiyadin/</t>
-        </is>
-      </c>
+          <t>Federico Rosales (cofundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Sharp Developers</t>
+          <t>Qualive</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2719,19 +2715,11 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>+351 933 078 094</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>info@sharpdevelopers.pt</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>sharpdevelopers.pt</t>
-        </is>
-      </c>
+          <t>+351 226 090 545</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Porto</t>
@@ -2744,35 +2732,27 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
+          <t>Rua D. Pedro V 410, 2º, 4150-601</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Residencial de luxo Porto (Em construção)</t>
+          <t>Fábrica do Prado (Matosinhos) (Em construção)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>CEO Carla Luís</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Carla Luís (CEO/cofundadora)</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carla-luís-b14a7616/</t>
-        </is>
-      </c>
+          <t>Telefone do registo comercial (einforma). Comercialização JLL/Predibisa</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SILCOGE / Grupo SIL</t>
+          <t>Quest Capital</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2782,17 +2762,17 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>+351 210 124 500</t>
+          <t>+351 213 472 435</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>info@sil.pt</t>
+          <t>info@questcapital.eu</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sil.pt</t>
+          <t>questcapital.eu</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2807,27 +2787,27 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
+          <t>Rua António Maria Cardoso 2, 1200-027 (escritório Porto: Rua Fernandes Tomás 546)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Grande Lisboa (Em construção)</t>
+          <t>Antas Atrium (Porto, antigo estádio) (Em construção)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Promoção imobiliária desde 1949</t>
+          <t>Com Tikehau Capital. &gt;1B€ sob gestão</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Pedro Silveira (acionista maioritário/ex-Chairman, destituído judicialmente mai/2025, em recurso)</t>
+          <t>Carlos Vasconcellos (Founding Partner, CEO exato não confirmado)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pedro-silveira-88822a20/</t>
+          <t>https://www.linkedin.com/in/vasconcelloscarlos/</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
@@ -2835,7 +2815,7 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SOLYD Property Developers</t>
+          <t>RAR Imobiliária</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2845,52 +2825,52 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>+351 211 214 926</t>
+          <t>+351 226 190 530</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>info@elou-solyd.pt</t>
+          <t>geral@rarimobiliaria.pt</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>solyd.pt</t>
+          <t>rarimobiliaria.pt</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
+          <t>Rua do Passeio Alegre 600-624, 4169-002</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Luz Altear (Alta de Lisboa) (Em construção) | ÉLOU (Santo António dos Cavaleiros, Loures) (Em construção/Comercialização)</t>
+          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
+          <t>Fonte: dinheirovivo.pt, construir.pt</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Gonçalo Cadete (CEO)</t>
+          <t>Paula Cristina Fernandes (CEO)</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gon%C3%A7alo-cadete-260692/</t>
+          <t>https://pt.linkedin.com/in/paula-fernandes-349a726</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
@@ -2898,7 +2878,7 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Stone Capital</t>
+          <t>ReVentures – Property Developers</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2908,17 +2888,17 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>+351 210 416 350</t>
+          <t>+351 212 402 489</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>info@stonecapital.pt</t>
+          <t>info@reventures.pt</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>stonecapital.pt</t>
+          <t>reventures.pt</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2933,31 +2913,35 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Av. da Liberdade 240, 1250-096</t>
+          <t>Campo Grande 28, 3º A, 1700-093</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
+          <t>7 residências de estudantes (rede nacional) (Em construção) | Senior Living (Planeamento)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Tel. móvel 965 915 993</t>
+          <t>NIF 516390350, capital 800k€. Fonte: construir.pt abr/2026</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Geoffroy Moreno (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>Hugo Gonçalves Pereira (CEO)</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hugogpereira/</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Teixeira Duarte Real Estate</t>
+          <t>Rio Capital / Grupo Rio</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2967,22 +2951,22 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>+351 217 912 300</t>
+          <t>+351 213 861 065</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>info@tdimobiliaria.pt</t>
+          <t>geral@riocapital.pt</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>tdimobiliaria.pt</t>
+          <t>riocapital.pt</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2992,17 +2976,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
+          <t>Av. Duarte Pacheco, Amoreiras Torre 2, 14º D</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
+          <t>21 projetos residenciais Grande Porto (Em construção) | Velaris (Porto) (Planeamento) | São Vicente (Maia) (Planeamento) | Metropólis Estúdio Residence (Matosinhos) (Planeamento)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do grupo Teixeira Duarte</t>
+          <t>Grupo nascido em Monção, liderado por Nuno Afonso. Fonte: idealista/news jun/2026, Público</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
@@ -3012,7 +2996,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Thomas &amp; Piron Portugal</t>
+          <t>Rockbuilding – Soluções Imobiliárias</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3022,52 +3006,48 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>+351 214 422 464</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>infopt@thomas-piron.eu</t>
-        </is>
-      </c>
+          <t>+351 217 996 700</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>thomas-piron.pt</t>
+          <t>rockbuilding.com</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Escritórios em Matosinhos e Sacavém</t>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, 7º A, 1070-374</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
+          <t>Serviços de desenvolvimento para promotores (Em construção)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
+          <t>ATENÇÃO: é gestor de projeto/serviços, não promotor puro</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>David Carreira (Diretor Geral/Country Manager)</t>
+          <t>José Pedro Almeida Guerra (Diretor Geral)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://lu.linkedin.com/in/david-carreira-a4082050</t>
+          <t>https://pt.linkedin.com/in/josé-pedro-almeida-guerra-20723679</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -3075,7 +3055,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Properties</t>
+          <t>Round Hill Capital</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3085,17 +3065,13 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>+351 215 814 094</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>info@vangproperties.com</t>
-        </is>
-      </c>
+          <t>+351 213 303 727</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>vangproperties.com</t>
+          <t>roundhillcapital.com</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -3110,35 +3086,31 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
+          <t>Av. D. João II, nº46, 1º B, 1990-095</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
+          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
+          <t>Sem telefone PT publicado</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Henrique Rodrigues da Silva (CEO desde fev/2026)</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/henrique-rodrigues-da-silva-b396643/</t>
-        </is>
-      </c>
+          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>VIC Properties</t>
+          <t>Royal Ventures</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3148,52 +3120,52 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>+351 219 347 112</t>
+          <t>+351 916 770 322</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>info@vic-properties.com</t>
+          <t>alex@royal-ventures.com</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>vic-properties.com</t>
+          <t>royal-ventures.com</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+          <t>Edifício Oceanus, Av. da Boavista 3227, 4100-137</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+          <t>Reabilitação centro histórico do Porto (Em construção)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Portefólio &gt;3B€. Fundada 2018</t>
+          <t>Sócios israelitas (Udi, Liad) + contacto PT Alexandre. Fonte: royal-ventures.com/contact-us</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>João Cabaça (Co-fundador e CEO)</t>
+          <t>Udi Yadin (fundador/General Partner)</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/jo%C3%A3o-caba%C3%A7a-6b293614b</t>
+          <t>https://www.linkedin.com/in/udiyadin/</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
@@ -3201,7 +3173,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Vogue Homes</t>
+          <t>Screendomus (Grupo Teixeira)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3211,17 +3183,17 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>+351 213 461 246</t>
+          <t>+351 928 110 064</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>comercial@vogue-homes.com</t>
+          <t>geral@screendomus.com</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>vogue-homes.com</t>
+          <t>screendomus.com</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3234,589 +3206,761 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Rua Luz Soriano 15, 1200-246</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Dafundo 24 (Comercialização) | Bom Sucesso (Comercialização) | Westhouse (Cascais) (Comercialização)</t>
+          <t>Altus (Alta de Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>NIF 510933084. Tel. móvel 913 385 846</t>
+          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Joaquim Lico (CEO)</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/joaquim-lico-4383239/</t>
-        </is>
-      </c>
+          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>Sharp Developers</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>+351 933 078 094</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>info@sharpdevelopers.pt</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sharpdevelopers.pt</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Av. Boavista 1681, Ed. Bristol, Esc. 5.4</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Residencial de luxo Porto (Em construção)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>CEO Carla Luís</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Carla Luís (CEO/cofundadora)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carla-luís-b14a7616/</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SILCOGE / Grupo SIL</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>+351 210 124 500</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>info@sil.pt</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sil.pt</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Av. Fontes Pereira de Melo 6, 5º, 1050-121</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Grande Lisboa (Em construção)</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Promoção imobiliária desde 1949</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Silveira (acionista maioritário/ex-Chairman, destituído judicialmente mai/2025, em recurso)</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-silveira-88822a20/</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SOLYD Property Developers</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>+351 211 214 926</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>info@elou-solyd.pt</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>solyd.pt</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Oeiras</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Torre de Monsanto, Rua Afonso Praça 30, 7º, 1495-061 Algés</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Luz Altear (Alta de Lisboa) (Em construção) | ÉLOU (Santo António dos Cavaleiros, Loures) (Em construção/Comercialização)</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Estoril Capital Partners + Oaktree. Tel. alternativo 210 966 905</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Gonçalo Cadete (CEO)</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gon%C3%A7alo-cadete-260692/</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Stone Capital</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>+351 210 416 350</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>info@stonecapital.pt</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>stonecapital.pt</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Av. da Liberdade 240, 1250-096</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Santa Isabel (Em construção) | Portefólio em desenvolvimento (Em construção)</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Tel. móvel 965 915 993</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Geoffroy Moreno (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Teixeira Duarte Real Estate</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>+351 217 912 300</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>info@tdimobiliaria.pt</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>tdimobiliaria.pt</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Oeiras</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Lagoas Park, Edifício 2, 2740-265 Porto Salvo</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Braço imobiliário do grupo Teixeira Duarte</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Thomas &amp; Piron Portugal</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>+351 214 422 464</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>infopt@thomas-piron.eu</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>thomas-piron.pt</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Matosinhos</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Escritórios em Matosinhos e Sacavém</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Docks Matosinhos (Em construção) | Gaia Hills (V.N. Gaia) (Em construção) | Conde de Lima (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Promotor belga em Portugal desde 2018. Fonte: diarioimobiliario.pt</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>David Carreira (Diretor Geral/Country Manager)</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>https://lu.linkedin.com/in/david-carreira-a4082050</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>United Investments Portugal (UIP)</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>+351 215 834 534</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>reception.lisboa@uip.pt</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>uip.pt</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Mar da China, Ed. Mar do Oriente nº1, Fração 3.2, Parque das Nações, 1990-137</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Fundada 1985</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Leal (CEO)</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard Properties</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>+351 215 814 094</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>info@vangproperties.com</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>vangproperties.com</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Ed. Tivoli Fórum, Av. da Liberdade 180A, 7º, 1250-146</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>22 projetos (Lisboa, Oeiras, Algarve, Comporta) (Em construção) | Infinity (Lisboa) (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Entidade legal Vanguardeagle Asset Management (NIF 514114215). Tel. móvel 915 292 222</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Henrique Rodrigues da Silva (CEO desde fev/2026)</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henrique-rodrigues-da-silva-b396643/</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>VIC Properties</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>+351 219 347 112</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>info@vic-properties.com</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>vic-properties.com</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Av. D. João II, Ed. Mythos 42, 4.03, Parque das Nações, 1990-095</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Prata Riverside Village (Marvila) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Portefólio &gt;3B€. Fundada 2018</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>João Cabaça (Co-fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/jo%C3%A3o-caba%C3%A7a-6b293614b</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>+351 218 429 970</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>grupovisabeira.com</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Av. Almirante Gago Coutinho 78, 1700-031</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Areeiro Select (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Vogue Homes</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>+351 213 461 246</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>comercial@vogue-homes.com</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>vogue-homes.com</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Rua Luz Soriano 15, 1200-246</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Dafundo 24 (Comercialização) | Bom Sucesso (Comercialização) | Westhouse (Cascais) (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>NIF 510933084. Tel. móvel 913 385 846</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Joaquim Lico (CEO)</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joaquim-lico-4383239/</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>YARD Properties</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>+351 918 888 353</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>sales@355outubro.com</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>yardproperties.pt</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>355 Outubro (Av. 5 de Outubro, Lisboa) (Em construção)</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Grupo israelita liderado por David Rabbi. Telefone é da linha comercial do projeto 355 Outubro</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>David Rabbi (fundador)</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>AFA (Grupo AFA)</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Savoy Residence D'Ávila (Em construção)</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: diarioimobiliario.pt</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Victor de Sousa (Diretor-Geral AFA Real Estate)</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Alecrim Real Estate (Lince Capital)</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>lince-capital.com</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Arts Investments, SA</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>artsinvestments.com</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>3 projetos em curso (nomes não encontrados) (Em construção/desenvolvimento)</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Ceetrus / Nhood Portugal</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>nacional</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>Pipeline nacional 15 cidades (nomes não encontrados) (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Fábrica Vilar (Em desenvolvimento)</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: viva-porto.pt</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Fortera</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Vila Nova de Gaia</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Porto / Gaia</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Skyline (V.N. Gaia) (Em construção) | 20 projetos (Porto, Gaia, Espinho, Braga) (Em construção) | Convento do Carmo (Braga) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>Israelita (Elad Dror). Sem telefone publicado nas fontes</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>Pedro Ferreira (CEO desde jun/2023· fundador anterior Elad Dror saiu em 2023)</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Fungepi (Grupo Novo Banco)</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>Rua de Artilharia 1, Campolide</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Urbanização Artilharia Um / Amoreiras (Campolide) (Planeamento (consulta pública fev-mar/2026))</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>Fundo de Gestão de Património Imobiliário do Grupo Novo Banco. Projeto contestado por moradores (petição + queixa à CE)</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Hines Portugal</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>hines.com</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>Gestora global · sem contacto PT publicado</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Imolote</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>imolote.pt</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr"/>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>KKR Imo, S.A.</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Neptune Developments</t>
+          <t>Alecrim Real Estate (Lince Capital)</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -3828,12 +3972,12 @@
       <c r="D59" s="5" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>neptune-developments.com</t>
+          <t>lince-capital.com</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3841,25 +3985,37 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Av. Eng.º Duarte Pacheco, Torre 2, piso 17, 1070-102</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>BellaMary (Cascais) (Comercialização)</t>
+          <t>Metrass (Campo de Ourique) (Em construção) | 8 projetos em pipeline (Planeamento)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr"/>
+          <t>Nova promotora (jan/2026), CEO António Velho da Palma</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>António Velho da Palma (CEO Alecrim RE)· CEO da holding Lince Capital é Vasco Pereira Coutinho</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-velho-da-palma-82112282/</t>
+        </is>
+      </c>
       <c r="M59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Onyria Group</t>
+          <t>Década Paralela (Grupo Latitude, com a TPS)</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3869,35 +4025,31 @@
       </c>
       <c r="C60" s="7" t="inlineStr"/>
       <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>onyriagroup.com</t>
-        </is>
-      </c>
+      <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Onyria Quinta da Marinha Residences (Cascais) (Comercialização)</t>
+          <t>Fábrica Vilar (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Grupo hoteleiro+imobiliário fundado 1986 por José Carlos Pinto Coelho</t>
+          <t>Fonte: viva-porto.pt</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+          <t>Bruno Soares (CEO, família Soares/Latitude Capital)</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr"/>
@@ -3906,7 +4058,7 @@
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Overseas</t>
+          <t>Fungepi (Grupo Novo Banco)</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3929,35 +4081,27 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Rua Alexandre Herculano 25, 1º, 1250-008</t>
+          <t>Rua de Artilharia 1, Campolide</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>5 projetos premium (4 Lisboa + Comporta) (Em construção) | JV com Grupo André Guimarães (Lisboa) (Planeamento) | Karl Lagerfeld branded residences (Planeamento) | Telhal 72 Liberdade (Comercialização)</t>
+          <t>Urbanização Artilharia Um / Amoreiras (Campolide) (Planeamento (consulta pública fev-mar/2026))</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>CEO Pedro Vicente (vice-presidente APPII). Sem telefone publicado</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>Pedro Vicente (CEO)</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/pedro-vicente-9aa0b424/</t>
-        </is>
-      </c>
+          <t>Fundo de Gestão de Património Imobiliário do Grupo Novo Banco. Projeto contestado por moradores (petição + queixa à CE)</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3967,31 +4111,39 @@
       </c>
       <c r="C62" s="7" t="inlineStr"/>
       <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>hines.com</t>
+        </is>
+      </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
+          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Gestora global · sem contacto PT publicado</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>Nuno Cunha (Managing Director)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr"/>
@@ -4000,7 +4152,7 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Prime Portugal</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4010,35 +4162,35 @@
       </c>
       <c r="C63" s="7" t="inlineStr"/>
       <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Av. Fontes Pereira de Melo 6, 1600-001</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Projetos residenciais Lisboa, Cascais e Melides (Em construção)</t>
+          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/site publicados (APPII)</t>
+          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>Federico Rosales (cofundador e CEO)</t>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr"/>
@@ -4047,7 +4199,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>RAR Imobiliária</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4071,17 +4223,17 @@
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Montebelo Villas (Foz Velha) (Em construção)</t>
+          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Fonte: dinheirovivo.pt, construir.pt</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>Paula Fernandes (CEO)</t>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr"/>
@@ -4090,7 +4242,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -4103,7 +4255,7 @@
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -4114,22 +4266,26 @@
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
+          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
+        </is>
+      </c>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>Neptune Developments</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -4139,26 +4295,30 @@
       </c>
       <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>neptune-developments.com</t>
+        </is>
+      </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>RM Villas (Início obra 1T2026)</t>
+          <t>BellaMary (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr"/>
@@ -4168,7 +4328,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Round Hill Capital</t>
+          <t>Onyria Group</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4180,12 +4340,12 @@
       <c r="D67" s="5" t="inlineStr"/>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>roundhillcapital.com</t>
+          <t>onyriagroup.com</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -4193,24 +4353,20 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>Rua da Escola Politécnica 38, 1250-102</t>
-        </is>
-      </c>
+      <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Student + residential Lisboa (com TPG) (Planeamento) | Tannery Amial (Porto) (Em construção)</t>
+          <t>Onyria Quinta da Marinha Residences (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone PT publicado</t>
+          <t>Grupo hoteleiro+imobiliário fundado 1986 por José Carlos Pinto Coelho</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>Michael Bickford (Founder &amp; CEO global· sem responsável PT confirmado)</t>
+          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
@@ -4219,7 +4375,7 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Screendomus (Grupo Teixeira)</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -4228,40 +4384,32 @@
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>geral@screendomus.com</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>screendomus.com</t>
-        </is>
-      </c>
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Altus (Alta de Lisboa) (Em construção)</t>
+          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Integra o Grupo Teixeira. Sem telefone confirmado — contacto via screendomus.com</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>Nuno Teixeira (Administrador, perfil LinkedIn não confirmado)</t>
+          <t>Nuno Cunha (Managing Director)</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr"/>
@@ -4270,7 +4418,7 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4280,44 +4428,36 @@
       </c>
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>shaluinvest.pt</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
+          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Fundador e Managing Director: Itai Fridman</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
-        </is>
-      </c>
+          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr"/>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4330,7 +4470,7 @@
       <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -4341,12 +4481,12 @@
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>RM Villas (Início obra 1T2026)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr"/>
@@ -4356,7 +4496,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>United Investments Portugal (UIP)</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4368,50 +4508,42 @@
       <c r="D71" s="5" t="inlineStr"/>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>uip.pt</t>
+          <t>shaluinvest.pt</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Pine Cliffs (Algarve), Sheraton Cascais, YOTEL Porto, Hyatt Regency Lisboa (Em construção)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Fundada 1985 · sem telefone publicado</t>
+          <t>Fundador e Managing Director: Itai Fridman</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>Carlos Leal (CEO)</t>
-        </is>
-      </c>
-      <c r="L71" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carlos-leal-62797227/</t>
-        </is>
-      </c>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Visabeira Imobiliária (Visabeirahouse)</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -4421,42 +4553,30 @@
       </c>
       <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>grupovisabeira.com</t>
-        </is>
-      </c>
+      <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Areeiro Select (Comercialização)</t>
+          <t>Verde Vale (Em construção)</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>Paula Santos (Diretora Geral Visabeirahouse)</t>
-        </is>
-      </c>
-      <c r="L72" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/paula-santos-71083337/</t>
-        </is>
-      </c>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
       <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
@@ -8807,7 +8927,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -8817,7 +8937,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -8847,7 +8967,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -4521,7 +4521,11 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Rua Marechal Saldanha 697</t>
+        </is>
+      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
@@ -5170,7 +5174,11 @@
           <t>Diogo Baptista Antunes (CEO)</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
+        </is>
+      </c>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
@@ -8967,7 +8975,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M162" headerRowCount="1">
-  <autoFilter ref="A1:M162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M165" headerRowCount="1">
+  <autoFilter ref="A1:M165"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1516,11 +1516,15 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Mário Almeida (Administrador)</t>
+          <t>Mário Sutil Almeida (Administrador)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mariosutilalmeida/</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -5597,7 +5601,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Hievila – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5607,52 +5611,52 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
+          <t>+351 239 091 692</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>hievila@hievila.com</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>hievila.com</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Rua da Casa Branca 13</t>
+        </is>
+      </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Portela Flats (Quinta da Portela, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Fundada 2008</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5662,56 +5666,52 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>iLanga Capital (Ohai Resorts)</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5721,43 +5721,47 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
+          <t>+351 262 561 800</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>info.nazare@ohairesorts.com</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>ohairesorts.com</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Nazaré</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Entrada Nacional 242 Km 31.5, 2450-138</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Ohai Peniche (Em construção) | Ohai Nazaré (Concluído/Operação)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>Grupo espanhol de Pelayo Cortina Koplowitz (conde de San Fernando de Peñalver). Tel. alt. 933 089 416</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>Pelayo Cortina Koplowitz (fundador)</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
@@ -5766,7 +5770,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5776,56 +5780,56 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 934 175 642</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>info@pinehill.pt</t>
+          <t>geral@jhomea.pt</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+        </is>
+      </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>José Miguel Afonso (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5835,60 +5839,52 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>info@quintadolago.com</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Almancil</t>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5898,52 +5894,56 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Pinheiro (fundador)</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+        </is>
+      </c>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5953,48 +5953,60 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>+351 289 390 700</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Resort residencial/golfe</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -6004,52 +6016,52 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -6059,47 +6071,39 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 939 443 765</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr"/>
@@ -6108,7 +6112,7 @@
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -6118,130 +6122,162 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
+          <t>+351 219 362 960</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>tps.com.pt</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
           <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>Fonte: omirante.pt</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr"/>
-      <c r="D100" s="5" t="inlineStr"/>
-      <c r="E100" s="5" t="inlineStr"/>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr"/>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr"/>
-      <c r="L100" s="5" t="inlineStr"/>
-      <c r="M100" s="5" t="inlineStr"/>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr"/>
-      <c r="D101" s="5" t="inlineStr"/>
-      <c r="E101" s="5" t="inlineStr"/>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa/Grândola/Lagoa</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="L101" s="5" t="inlineStr"/>
-      <c r="M101" s="5" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6254,23 +6290,23 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr"/>
@@ -6280,7 +6316,7 @@
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6293,28 +6329,28 @@
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>João Bugalho (CEO)</t>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr"/>
@@ -6323,7 +6359,7 @@
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6333,14 +6369,10 @@
       </c>
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -6351,26 +6383,22 @@
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
-        </is>
-      </c>
-      <c r="K104" s="5" t="inlineStr">
-        <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr"/>
       <c r="L104" s="5" t="inlineStr"/>
       <c r="M104" s="5" t="inlineStr"/>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6383,33 +6411,37 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6419,36 +6451,44 @@
       </c>
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L106" s="5" t="inlineStr"/>
       <c r="M106" s="5" t="inlineStr"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6458,30 +6498,26 @@
       </c>
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="5" t="inlineStr"/>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -6491,7 +6527,7 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6504,7 +6540,7 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -6515,12 +6551,12 @@
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr"/>
@@ -6530,7 +6566,7 @@
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6540,26 +6576,30 @@
       </c>
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="5" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr"/>
@@ -6569,7 +6609,7 @@
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6579,30 +6619,26 @@
       </c>
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr"/>
@@ -6612,7 +6648,7 @@
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6625,23 +6661,23 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: diariocoimbra.pt</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -6651,7 +6687,7 @@
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6661,44 +6697,40 @@
       </c>
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr"/>
-      <c r="E112" s="5" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K112" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L112" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: brainsre.news</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr"/>
+      <c r="L112" s="5" t="inlineStr"/>
       <c r="M112" s="5" t="inlineStr"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6711,37 +6743,33 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="inlineStr"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6754,37 +6782,41 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
-      <c r="L114" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M114" s="5" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6794,35 +6826,31 @@
       </c>
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr"/>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr"/>
@@ -6831,7 +6859,7 @@
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6844,28 +6872,28 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr"/>
@@ -6874,7 +6902,7 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6884,36 +6912,44 @@
       </c>
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr"/>
-      <c r="E117" s="5" t="inlineStr"/>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="L117" s="5" t="inlineStr"/>
       <c r="M117" s="5" t="inlineStr"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6926,33 +6962,37 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -6965,7 +7005,7 @@
       <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -6976,12 +7016,12 @@
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr"/>
@@ -6991,7 +7031,7 @@
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -7001,30 +7041,26 @@
       </c>
       <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="5" t="inlineStr"/>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr"/>
@@ -7034,7 +7070,7 @@
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -7044,14 +7080,10 @@
       </c>
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="5" t="inlineStr"/>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -7062,26 +7094,22 @@
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr"/>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -7093,28 +7121,28 @@
       <c r="D122" s="5" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: genuinoinvestments.com</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr"/>
@@ -7124,7 +7152,7 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -7134,36 +7162,44 @@
       </c>
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L123" s="5" t="inlineStr"/>
       <c r="M123" s="5" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7175,34 +7211,38 @@
       <c r="D124" s="5" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr"/>
-      <c r="G124" s="7" t="inlineStr"/>
+          <t>glowing.pt</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr"/>
       <c r="L124" s="5" t="inlineStr"/>
       <c r="M124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7212,44 +7252,36 @@
       </c>
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
+      <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr"/>
       <c r="L125" s="5" t="inlineStr"/>
       <c r="M125" s="5" t="inlineStr"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7259,31 +7291,27 @@
       </c>
       <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr"/>
@@ -7292,7 +7320,7 @@
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7302,10 +7330,14 @@
       </c>
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="5" t="inlineStr"/>
-      <c r="E127" s="5" t="inlineStr"/>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -7316,7 +7348,7 @@
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
@@ -7326,20 +7358,16 @@
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L127" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7349,40 +7377,40 @@
       </c>
       <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="5" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
+      <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr"/>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
       <c r="L128" s="5" t="inlineStr"/>
       <c r="M128" s="5" t="inlineStr"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7392,44 +7420,44 @@
       </c>
       <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>gruponbportugal.pt</t>
-        </is>
-      </c>
+      <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
-      <c r="L129" s="5" t="inlineStr"/>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M129" s="5" t="inlineStr"/>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7441,42 +7469,38 @@
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K130" s="5" t="inlineStr">
-        <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr"/>
       <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7488,12 +7512,12 @@
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -7504,22 +7528,26 @@
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K131" s="5" t="inlineStr"/>
+          <t>Fonte: gruponb.pt</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="L131" s="5" t="inlineStr"/>
       <c r="M131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7531,38 +7559,42 @@
       <c r="D132" s="5" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7572,26 +7604,30 @@
       </c>
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr"/>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>hillside.pt</t>
+        </is>
+      </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
+          <t>Fonte: remax.pt, hillside.pt</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr"/>
@@ -7601,7 +7637,7 @@
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7613,46 +7649,38 @@
       <c r="D134" s="5" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>jpaiva.pt</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr"/>
+      <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7662,14 +7690,10 @@
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>leparc.pt</t>
-        </is>
-      </c>
+      <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -7680,12 +7704,12 @@
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr"/>
@@ -7695,7 +7719,7 @@
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7707,7 +7731,7 @@
       <c r="D136" s="5" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -7723,26 +7747,30 @@
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M136" s="5" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7752,10 +7780,14 @@
       </c>
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr"/>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -7766,26 +7798,22 @@
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr">
-        <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
+          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr"/>
       <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7795,36 +7823,44 @@
       </c>
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr"/>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr"/>
+          <t>Fonte: luxpremium.net</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7834,35 +7870,31 @@
       </c>
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="E139" s="5" t="inlineStr"/>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
+          <t>Fonte: oconnormurphy.ie</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
         </is>
       </c>
       <c r="L139" s="5" t="inlineStr"/>
@@ -7871,7 +7903,7 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7881,48 +7913,36 @@
       </c>
       <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7932,36 +7952,44 @@
       </c>
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr"/>
+          <t>Fonte: maveninvest.pt</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
       <c r="L141" s="5" t="inlineStr"/>
       <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -7971,40 +7999,48 @@
       </c>
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
-      <c r="L142" s="5" t="inlineStr"/>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -8014,14 +8050,10 @@
       </c>
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
@@ -8032,12 +8064,12 @@
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
+          <t>Fonte: ireland-portugal.com</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr"/>
@@ -8047,7 +8079,7 @@
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -8057,52 +8089,40 @@
       </c>
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>ombria.com</t>
-        </is>
-      </c>
+      <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L144" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="inlineStr"/>
       <c r="M144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -8112,10 +8132,14 @@
       </c>
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr"/>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -8126,12 +8150,12 @@
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr"/>
@@ -8141,7 +8165,7 @@
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -8151,40 +8175,52 @@
       </c>
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr"/>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
-      <c r="L146" s="5" t="inlineStr"/>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8197,23 +8233,23 @@
       <c r="E147" s="5" t="inlineStr"/>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
+          <t>Fonte: ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr"/>
@@ -8223,7 +8259,7 @@
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8236,7 +8272,7 @@
       <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -8247,22 +8283,26 @@
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K148" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L148" s="5" t="inlineStr"/>
       <c r="M148" s="5" t="inlineStr"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8275,37 +8315,33 @@
       <c r="E149" s="5" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K149" s="5" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr"/>
       <c r="L149" s="5" t="inlineStr"/>
       <c r="M149" s="5" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8315,44 +8351,36 @@
       </c>
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="5" t="inlineStr"/>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E150" s="5" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr"/>
       <c r="L150" s="5" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8362,48 +8390,40 @@
       </c>
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="5" t="inlineStr"/>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>soccal-vaz.com</t>
-        </is>
-      </c>
+      <c r="E151" s="5" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L151" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr"/>
       <c r="M151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8415,46 +8435,42 @@
       <c r="D152" s="5" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
-        </is>
-      </c>
-      <c r="L152" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
-        </is>
-      </c>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr"/>
       <c r="M152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8464,36 +8480,48 @@
       </c>
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr"/>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>soccal-vaz.com</t>
+        </is>
+      </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K153" s="5" t="inlineStr"/>
-      <c r="L153" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>António Vaz (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+        </is>
+      </c>
       <c r="M153" s="5" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8505,42 +8533,46 @@
       <c r="D154" s="5" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
-        </is>
-      </c>
-      <c r="L154" s="5" t="inlineStr"/>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M154" s="5" t="inlineStr"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8550,30 +8582,26 @@
       </c>
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="5" t="inlineStr"/>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>southshoreinvest.com</t>
-        </is>
-      </c>
+      <c r="E155" s="5" t="inlineStr"/>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr"/>
@@ -8583,7 +8611,7 @@
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -8595,33 +8623,33 @@
       <c r="D156" s="5" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>sonaesierra.com</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
+          <t>Fonte: rtp.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr"/>
@@ -8630,7 +8658,7 @@
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -8640,26 +8668,30 @@
       </c>
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="5" t="inlineStr"/>
-      <c r="E157" s="5" t="inlineStr"/>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>southshoreinvest.com</t>
+        </is>
+      </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
+          <t>Fonte: southshoreinvest.com</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr"/>
@@ -8669,7 +8701,7 @@
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -8681,38 +8713,42 @@
       <c r="D158" s="5" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>valentavillas.com</t>
+          <t>squareview.pt</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
-        </is>
-      </c>
-      <c r="K158" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
       <c r="L158" s="5" t="inlineStr"/>
       <c r="M158" s="5" t="inlineStr"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -8725,23 +8761,23 @@
       <c r="E159" s="5" t="inlineStr"/>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: racius.com, idealista.pt</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr"/>
@@ -8751,7 +8787,7 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -8763,42 +8799,38 @@
       <c r="D160" s="5" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>ugp.ie</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K160" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr"/>
       <c r="L160" s="5" t="inlineStr"/>
       <c r="M160" s="5" t="inlineStr"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -8808,34 +8840,26 @@
       </c>
       <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="5" t="inlineStr"/>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>valedolobo.com</t>
-        </is>
-      </c>
+      <c r="E161" s="5" t="inlineStr"/>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr">
-        <is>
-          <t>Parque do Golfe</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr"/>
@@ -8845,7 +8869,7 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -8857,33 +8881,174 @@
       <c r="D162" s="5" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>vilagale.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>The Shipyard (Comercialização)</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K162" s="5" t="inlineStr"/>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L162" s="5" t="inlineStr"/>
       <c r="M162" s="5" t="inlineStr"/>
+    </row>
+    <row r="163" ht="30" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Urban Office</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr"/>
+      <c r="D163" s="5" t="inlineStr"/>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>urbanoffice.pt</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>Torres Vedras</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>Rua Paiva de Andrade 6A, 2560-357</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Torres Prime (Torres Vedras) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>Do Grupo Riberalves (&gt;30 anos de história). Nota: site autodenomina-se promotora, mas core histórico é mediação imobiliária</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="inlineStr"/>
+      <c r="L163" s="5" t="inlineStr"/>
+      <c r="M163" s="5" t="inlineStr"/>
+    </row>
+    <row r="164" ht="30" customHeight="1">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr"/>
+      <c r="D164" s="5" t="inlineStr"/>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>Parque do Golfe</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr"/>
+      <c r="L164" s="5" t="inlineStr"/>
+      <c r="M164" s="5" t="inlineStr"/>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr"/>
+      <c r="D165" s="5" t="inlineStr"/>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr"/>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="inlineStr"/>
+      <c r="L165" s="5" t="inlineStr"/>
+      <c r="M165" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8925,7 +9090,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -8935,7 +9100,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -8945,7 +9110,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -8965,7 +9130,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M165" headerRowCount="1">
-  <autoFilter ref="A1:M165"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M167" headerRowCount="1">
+  <autoFilter ref="A1:M167"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1350,7 +1350,11 @@
           <t>Tiago Eiró (CEO)</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/tiago-eir%C3%B3-3811093</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -4422,7 +4426,7 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>REABILITA</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4432,10 +4436,14 @@
       </c>
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>reabilita.pt</t>
+        </is>
+      </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -4443,15 +4451,19 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Rua do Instituto Industrial nº18, 2º Esq, 1200-225</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
+          <t>Mouzinho da Silveira 21 (Av. Liberdade) (Comercialização) | São Vicente 68 (Alfama) (Comercialização) | Almirante Reis 246 (Areeiro) (Comercialização)</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
+          <t>Promoção imobiliária em Lisboa e Cascais desde 2007 (reabilitação urbana + obra nova)</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr"/>
@@ -4461,7 +4473,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4474,23 +4486,23 @@
       <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>RM Villas (Início obra 1T2026)</t>
+          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr"/>
@@ -4500,7 +4512,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4510,48 +4522,36 @@
       </c>
       <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="5" t="inlineStr"/>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>shaluinvest.pt</t>
-        </is>
-      </c>
+      <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
+          <t>Matosinhos</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Rua Marechal Saldanha 697</t>
-        </is>
-      </c>
+      <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
+          <t>RM Villas (Início obra 1T2026)</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Fundador e Managing Director: Itai Fridman</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="inlineStr">
-        <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr"/>
       <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -4561,26 +4561,34 @@
       </c>
       <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>altadelisboa.com</t>
+        </is>
+      </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Rua Manuel Marques 10D, 1º, 1750-171</t>
+        </is>
+      </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>Alta de Lisboa (Lumiar) (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
+          <t>NIF 501450831. Capital social €0 (SPV de parceria público-privada, sem capital de risco próprio)</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr"/>
@@ -4590,7 +4598,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -4599,57 +4607,49 @@
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr"/>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="D73" s="5" t="inlineStr"/>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>shaluinvest.pt</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+          <t>Rua Marechal Saldanha 697</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+          <t>Fundador e Managing Director: Itai Fridman</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>Fernando Vasco Costa (CEO)</t>
-        </is>
-      </c>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
-        </is>
-      </c>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr"/>
       <c r="M73" s="5" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -4658,19 +4658,11 @@
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>info@ancora-inv.com</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>ancora-inv.com</t>
-        </is>
-      </c>
+      <c r="D74" s="5" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -4681,156 +4673,136 @@
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
+          <t>Verde Vale (Em construção)</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="inlineStr"/>
+      <c r="M74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>VIZTA (ex-Nexity Portugal)</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr"/>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>info@ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Antrix</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>info@antrix.pt</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>antrix.pt</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="M76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Arish Capital Partners</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4840,44 +4812,52 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>900 264 096 (ES)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>info@aedashomes.com</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>arishcapitalpartners.com</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Grândola</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
+        </is>
+      </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Fonte: diarioimobiliario.pt</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
@@ -4885,7 +4865,7 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4900,12 +4880,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>info@carvoeirobranco.com</t>
+          <t>info@antrix.pt</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -4925,22 +4905,22 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (CEO)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
@@ -4948,7 +4928,7 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4958,56 +4938,52 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>casais@casais.pt</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr"/>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+        </is>
+      </c>
       <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -5017,52 +4993,52 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
+          <t>Erik de Vlieger (CEO)</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
@@ -5070,7 +5046,7 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -5080,60 +5056,56 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 305 490</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
-        </is>
-      </c>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5143,18 +5115,22 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>+351 253 461 462</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>geral@castro-group.pt</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -5162,25 +5138,29 @@
           <t>Braga</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
+          <t>Paulo Castro (CEO)</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
@@ -5188,7 +5168,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>DST Real Estate (Grupo dst)</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5198,52 +5178,60 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 253 307 200</t>
+          <t>+351 234 480 570</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>geral@dstsgps.com</t>
+          <t>info@civilria.pt</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>dstsgps.com</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Museu no centro histórico de Braga (Em construção)</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5253,48 +5241,44 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
+          <t>+351 253 089 932</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
+          <t>Diogo Baptista Antunes (CEO)</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -5302,7 +5286,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>DST Real Estate (Grupo dst)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5312,56 +5296,52 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
+          <t>+351 253 307 200</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>geral@garcia.pt</t>
+          <t>geral@dstsgps.com</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>dstsgps.com</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Museu no centro histórico de Braga (Em construção)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
+          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5371,52 +5351,48 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>aca@grupo-aca.com</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
+          <t>Reinaldo Teixeira (Administrador)</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
@@ -5424,7 +5400,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5434,47 +5410,47 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr"/>
@@ -5483,7 +5459,7 @@
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5493,52 +5469,52 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
@@ -5546,7 +5522,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5556,43 +5532,47 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
+          <t>+351 253 685 109</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>acrescentar@grupoacrescentar.pt</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr"/>
@@ -5601,7 +5581,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Hievila – Empreendimentos Imobiliários</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5611,52 +5591,60 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 239 091 692</t>
+          <t>+351 253 105 331</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>hievila@hievila.com</t>
+          <t>geral@arliz.co</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>hievila.com</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Rua da Casa Branca 13</t>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Portela Flats (Quinta da Portela, Coimbra) (Em construção)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Fundada 2008</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
       <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5666,52 +5654,52 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>273 332 784 (confirmar)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>iLanga Capital (Ohai Resorts)</t>
+          <t>Hievila – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5721,56 +5709,52 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 262 561 800</t>
+          <t>+351 239 091 692</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>info.nazare@ohairesorts.com</t>
+          <t>hievila@hievila.com</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>ohairesorts.com</t>
+          <t>hievila.com</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Nazaré</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Entrada Nacional 242 Km 31.5, 2450-138</t>
+          <t>Rua da Casa Branca 13</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Ohai Peniche (Em construção) | Ohai Nazaré (Concluído/Operação)</t>
+          <t>Portela Flats (Quinta da Portela, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Grupo espanhol de Pelayo Cortina Koplowitz (conde de San Fernando de Peñalver). Tel. alt. 933 089 416</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Pelayo Cortina Koplowitz (fundador)</t>
-        </is>
-      </c>
+          <t>Fundada 2008</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5780,56 +5764,52 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>iLanga Capital (Ohai Resorts)</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5839,43 +5819,47 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
+          <t>+351 262 561 800</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>info.nazare@ohairesorts.com</t>
+        </is>
+      </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>ohairesorts.com</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Nazaré</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Entrada Nacional 242 Km 31.5, 2450-138</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Ohai Peniche (Em construção) | Ohai Nazaré (Concluído/Operação)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>Grupo espanhol de Pelayo Cortina Koplowitz (conde de San Fernando de Peñalver). Tel. alt. 933 089 416</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>Pelayo Cortina Koplowitz (fundador)</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr"/>
@@ -5884,7 +5868,7 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5894,56 +5878,56 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 934 175 642</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>info@pinehill.pt</t>
+          <t>geral@jhomea.pt</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+        </is>
+      </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>José Miguel Afonso (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5953,60 +5937,52 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>info@quintadolago.com</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Almancil</t>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -6016,52 +5992,56 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Pinheiro (fundador)</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+        </is>
+      </c>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -6071,48 +6051,60 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>+351 289 390 700</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Resort residencial/golfe</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -6122,52 +6114,52 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -6177,47 +6169,39 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 939 443 765</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr"/>
@@ -6226,7 +6210,7 @@
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -6236,130 +6220,162 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
+          <t>+351 219 362 960</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>tps.com.pt</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
           <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>Fonte: omirante.pt</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr"/>
-      <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr"/>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr"/>
-      <c r="L102" s="5" t="inlineStr"/>
-      <c r="M102" s="5" t="inlineStr"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr"/>
-      <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr"/>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa/Grândola/Lagoa</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr"/>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J103" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="L103" s="5" t="inlineStr"/>
-      <c r="M103" s="5" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6372,23 +6388,23 @@
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr"/>
@@ -6398,7 +6414,7 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6411,37 +6427,41 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
-      <c r="L105" s="5" t="inlineStr"/>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
+        </is>
+      </c>
       <c r="M105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6451,14 +6471,10 @@
       </c>
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -6469,26 +6485,22 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="inlineStr">
-        <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr"/>
       <c r="L106" s="5" t="inlineStr"/>
       <c r="M106" s="5" t="inlineStr"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6501,33 +6513,37 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="L107" s="5" t="inlineStr"/>
       <c r="M107" s="5" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6537,36 +6553,44 @@
       </c>
       <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
-        </is>
-      </c>
-      <c r="K108" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L108" s="5" t="inlineStr"/>
       <c r="M108" s="5" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6576,30 +6600,26 @@
       </c>
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr"/>
@@ -6609,7 +6629,7 @@
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6622,7 +6642,7 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -6633,12 +6653,12 @@
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr"/>
@@ -6648,7 +6668,7 @@
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6658,26 +6678,30 @@
       </c>
       <c r="C111" s="7" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr"/>
-      <c r="E111" s="5" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -6687,7 +6711,7 @@
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6697,30 +6721,26 @@
       </c>
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr"/>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr"/>
@@ -6730,7 +6750,7 @@
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6743,23 +6763,23 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: diariocoimbra.pt</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr"/>
@@ -6769,7 +6789,7 @@
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6779,44 +6799,40 @@
       </c>
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: brainsre.news</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr"/>
+      <c r="L114" s="5" t="inlineStr"/>
       <c r="M114" s="5" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6829,37 +6845,33 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr"/>
       <c r="L115" s="5" t="inlineStr"/>
       <c r="M115" s="5" t="inlineStr"/>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6872,37 +6884,41 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
-      <c r="L116" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6912,35 +6928,31 @@
       </c>
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr"/>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr"/>
@@ -6949,7 +6961,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6962,28 +6974,28 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr"/>
@@ -6992,7 +7004,7 @@
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -7002,36 +7014,44 @@
       </c>
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="L119" s="5" t="inlineStr"/>
       <c r="M119" s="5" t="inlineStr"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -7044,33 +7064,37 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -7083,7 +7107,7 @@
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -7094,12 +7118,12 @@
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr"/>
@@ -7109,7 +7133,7 @@
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -7119,30 +7143,26 @@
       </c>
       <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr"/>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr"/>
@@ -7152,7 +7172,7 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -7162,14 +7182,10 @@
       </c>
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -7180,26 +7196,22 @@
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr"/>
       <c r="L123" s="5" t="inlineStr"/>
       <c r="M123" s="5" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7211,28 +7223,28 @@
       <c r="D124" s="5" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: genuinoinvestments.com</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr"/>
@@ -7242,7 +7254,7 @@
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7252,36 +7264,44 @@
       </c>
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L125" s="5" t="inlineStr"/>
       <c r="M125" s="5" t="inlineStr"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7293,34 +7313,38 @@
       <c r="D126" s="5" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr"/>
-      <c r="G126" s="7" t="inlineStr"/>
+          <t>glowing.pt</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K126" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr"/>
       <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7330,44 +7354,36 @@
       </c>
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="5" t="inlineStr"/>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
+      <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr"/>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7377,31 +7393,27 @@
       </c>
       <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="5" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr"/>
+      <c r="G128" s="7" t="inlineStr"/>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr"/>
@@ -7410,7 +7422,7 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7420,10 +7432,14 @@
       </c>
       <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="5" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -7434,7 +7450,7 @@
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -7444,20 +7460,16 @@
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L129" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr"/>
       <c r="M129" s="5" t="inlineStr"/>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7467,40 +7479,40 @@
       </c>
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
+      <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K130" s="5" t="inlineStr"/>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
       <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7510,44 +7522,44 @@
       </c>
       <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="5" t="inlineStr"/>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>gruponbportugal.pt</t>
-        </is>
-      </c>
+      <c r="E131" s="5" t="inlineStr"/>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
-      <c r="L131" s="5" t="inlineStr"/>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7559,42 +7571,38 @@
       <c r="D132" s="5" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr"/>
       <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7606,12 +7614,12 @@
       <c r="D133" s="5" t="inlineStr"/>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -7622,22 +7630,26 @@
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K133" s="5" t="inlineStr"/>
+          <t>Fonte: gruponb.pt</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7649,38 +7661,42 @@
       <c r="D134" s="5" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7690,26 +7706,30 @@
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>hillside.pt</t>
+        </is>
+      </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
+          <t>Fonte: remax.pt, hillside.pt</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr"/>
@@ -7719,7 +7739,7 @@
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7731,46 +7751,38 @@
       <c r="D136" s="5" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>jpaiva.pt</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K136" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr"/>
+      <c r="L136" s="5" t="inlineStr"/>
       <c r="M136" s="5" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7780,14 +7792,10 @@
       </c>
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>leparc.pt</t>
-        </is>
-      </c>
+      <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -7798,12 +7806,12 @@
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr"/>
@@ -7813,7 +7821,7 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7825,7 +7833,7 @@
       <c r="D138" s="5" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
@@ -7841,26 +7849,30 @@
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
         <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
-      <c r="L138" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7870,10 +7882,14 @@
       </c>
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr"/>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -7884,26 +7900,22 @@
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
+          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr"/>
       <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7913,36 +7925,44 @@
       </c>
       <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr"/>
+          <t>Fonte: luxpremium.net</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7952,35 +7972,31 @@
       </c>
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="5" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
+          <t>Fonte: oconnormurphy.ie</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
         </is>
       </c>
       <c r="L141" s="5" t="inlineStr"/>
@@ -7989,7 +8005,7 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -7999,48 +8015,36 @@
       </c>
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr">
-        <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L142" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr"/>
+      <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -8050,36 +8054,44 @@
       </c>
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr"/>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
-        </is>
-      </c>
-      <c r="K143" s="5" t="inlineStr"/>
+          <t>Fonte: maveninvest.pt</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr">
+        <is>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
       <c r="L143" s="5" t="inlineStr"/>
       <c r="M143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -8089,40 +8101,48 @@
       </c>
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
-      <c r="L144" s="5" t="inlineStr"/>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -8132,14 +8152,10 @@
       </c>
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="E145" s="5" t="inlineStr"/>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -8150,12 +8166,12 @@
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
+          <t>Fonte: ireland-portugal.com</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr"/>
@@ -8165,7 +8181,7 @@
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -8175,52 +8191,40 @@
       </c>
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>ombria.com</t>
-        </is>
-      </c>
+      <c r="E146" s="5" t="inlineStr"/>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr"/>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8230,10 +8234,14 @@
       </c>
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="5" t="inlineStr"/>
-      <c r="E147" s="5" t="inlineStr"/>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
@@ -8244,12 +8252,12 @@
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr"/>
@@ -8259,7 +8267,7 @@
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8269,40 +8277,52 @@
       </c>
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr"/>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
-      <c r="L148" s="5" t="inlineStr"/>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M148" s="5" t="inlineStr"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8315,23 +8335,23 @@
       <c r="E149" s="5" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
+          <t>Fonte: ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr"/>
@@ -8341,7 +8361,7 @@
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8354,7 +8374,7 @@
       <c r="E150" s="5" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -8365,22 +8385,26 @@
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L150" s="5" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8393,37 +8417,33 @@
       <c r="E151" s="5" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr"/>
       <c r="L151" s="5" t="inlineStr"/>
       <c r="M151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8433,44 +8453,36 @@
       </c>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E152" s="5" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
-        </is>
-      </c>
-      <c r="K152" s="5" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr"/>
       <c r="M152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8480,48 +8492,40 @@
       </c>
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>soccal-vaz.com</t>
-        </is>
-      </c>
+      <c r="E153" s="5" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L153" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr"/>
       <c r="M153" s="5" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8533,46 +8537,42 @@
       <c r="D154" s="5" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
-        </is>
-      </c>
-      <c r="L154" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
-        </is>
-      </c>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr"/>
       <c r="M154" s="5" t="inlineStr"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8582,36 +8582,48 @@
       </c>
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="5" t="inlineStr"/>
-      <c r="E155" s="5" t="inlineStr"/>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>soccal-vaz.com</t>
+        </is>
+      </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K155" s="5" t="inlineStr"/>
-      <c r="L155" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>António Vaz (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+        </is>
+      </c>
       <c r="M155" s="5" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -8623,42 +8635,46 @@
       <c r="D156" s="5" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
-        </is>
-      </c>
-      <c r="L156" s="5" t="inlineStr"/>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M156" s="5" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -8668,30 +8684,26 @@
       </c>
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="5" t="inlineStr"/>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>southshoreinvest.com</t>
-        </is>
-      </c>
+      <c r="E157" s="5" t="inlineStr"/>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr"/>
@@ -8701,7 +8713,7 @@
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -8713,42 +8725,46 @@
       <c r="D158" s="5" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>sonaesierra.com</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
+          <t>Fonte: rtp.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
-        </is>
-      </c>
-      <c r="L158" s="5" t="inlineStr"/>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+        </is>
+      </c>
       <c r="M158" s="5" t="inlineStr"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -8758,26 +8774,30 @@
       </c>
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="5" t="inlineStr"/>
-      <c r="E159" s="5" t="inlineStr"/>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>southshoreinvest.com</t>
+        </is>
+      </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
+          <t>Fonte: southshoreinvest.com</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr"/>
@@ -8787,7 +8807,7 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -8799,38 +8819,46 @@
       <c r="D160" s="5" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>valentavillas.com</t>
+          <t>squareview.pt</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
-        </is>
-      </c>
-      <c r="K160" s="5" t="inlineStr"/>
-      <c r="L160" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+        </is>
+      </c>
       <c r="M160" s="5" t="inlineStr"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -8843,23 +8871,23 @@
       <c r="E161" s="5" t="inlineStr"/>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: racius.com, idealista.pt</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr"/>
@@ -8869,7 +8897,7 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -8881,42 +8909,38 @@
       <c r="D162" s="5" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>ugp.ie</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K162" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr"/>
       <c r="L162" s="5" t="inlineStr"/>
       <c r="M162" s="5" t="inlineStr"/>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Urban Office</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -8926,34 +8950,26 @@
       </c>
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="5" t="inlineStr"/>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>urbanoffice.pt</t>
-        </is>
-      </c>
+      <c r="E163" s="5" t="inlineStr"/>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Torres Vedras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>Rua Paiva de Andrade 6A, 2560-357</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Torres Prime (Torres Vedras) (Em construção)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Do Grupo Riberalves (&gt;30 anos de história). Nota: site autodenomina-se promotora, mas core histórico é mediação imobiliária</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K163" s="5" t="inlineStr"/>
@@ -8963,7 +8979,7 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -8975,12 +8991,12 @@
       <c r="D164" s="5" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>valedolobo.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
@@ -8988,29 +9004,29 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H164" s="5" t="inlineStr">
-        <is>
-          <t>Parque do Golfe</t>
-        </is>
-      </c>
+      <c r="H164" s="5" t="inlineStr"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+          <t>The Shipyard (Comercialização)</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
-        </is>
-      </c>
-      <c r="K164" s="5" t="inlineStr"/>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L164" s="5" t="inlineStr"/>
       <c r="M164" s="5" t="inlineStr"/>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Office</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -9022,33 +9038,127 @@
       <c r="D165" s="5" t="inlineStr"/>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>vilagale.com</t>
+          <t>urbanoffice.pt</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Torres Vedras</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>Rua Paiva de Andrade 6A, 2560-357</t>
+        </is>
+      </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>Torres Prime (Torres Vedras) (Em construção)</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Do Grupo Riberalves (&gt;30 anos de história). Nota: site autodenomina-se promotora, mas core histórico é mediação imobiliária</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr"/>
       <c r="L165" s="5" t="inlineStr"/>
       <c r="M165" s="5" t="inlineStr"/>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr"/>
+      <c r="D166" s="5" t="inlineStr"/>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>Parque do Golfe</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="inlineStr"/>
+      <c r="L166" s="5" t="inlineStr"/>
+      <c r="M166" s="5" t="inlineStr"/>
+    </row>
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr"/>
+      <c r="D167" s="5" t="inlineStr"/>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr"/>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="inlineStr"/>
+      <c r="L167" s="5" t="inlineStr"/>
+      <c r="M167" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9090,7 +9200,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
@@ -9110,7 +9220,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -9120,7 +9230,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -9140,7 +9250,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M169" headerRowCount="1">
-  <autoFilter ref="A1:M169"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M172" headerRowCount="1">
+  <autoFilter ref="A1:M172"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8 projetos Príncipe Real (Em construção) | DPV Block (Comercialização) | EmbaiXada (Concluído)</t>
+          <t>8 projetos Príncipe Real (Em construção) | DPV Block (Comercialização) | EmbaiXada (Concluído) | Anjos Urban Palace (Lisboa) (Concluído/Comercialização)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
+          <t>Selicomi Portugal (Victoria Group)</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -4659,11 +4659,7 @@
       </c>
       <c r="C74" s="7" t="inlineStr"/>
       <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>altadelisboa.com</t>
-        </is>
-      </c>
+      <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
           <t>Lisboa</t>
@@ -4676,17 +4672,17 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>Rua Manuel Marques 10D, 1º, 1750-171</t>
+          <t>Rua Camilo Castelo Branco 46, 1250</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Alta de Lisboa (Lumiar) (Em construção/Comercialização)</t>
+          <t>CCB46 (Marquês de Pombal/Av. Liberdade) (Comercialização)</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>NIF 501450831. Capital social €0 (SPV de parceria público-privada, sem capital de risco próprio)</t>
+          <t>Adquirido em 2014 pela Selicomi Portugal ao Victoria Group. Ativo de escritórios, não residencial</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr"/>
@@ -4696,7 +4692,7 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -4708,46 +4704,42 @@
       <c r="D75" s="5" t="inlineStr"/>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>shaluinvest.pt</t>
+          <t>altadelisboa.com</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>Rua Marechal Saldanha 697</t>
+          <t>Rua Manuel Marques 10D, 1º, 1750-171</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
+          <t>Alta de Lisboa (Lumiar) (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Fundador e Managing Director: Itai Fridman</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
-        </is>
-      </c>
+          <t>NIF 501450831. Capital social €0 (SPV de parceria público-privada, sem capital de risco próprio)</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr"/>
       <c r="L75" s="5" t="inlineStr"/>
       <c r="M75" s="5" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -4757,10 +4749,14 @@
       </c>
       <c r="C76" s="7" t="inlineStr"/>
       <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -4768,25 +4764,33 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Rua Marechal Saldanha 697</t>
+        </is>
+      </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr"/>
+          <t>Fundador e Managing Director: Itai Fridman</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
       <c r="L76" s="5" t="inlineStr"/>
       <c r="M76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Square Asset Management</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -4795,14 +4799,10 @@
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr"/>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="D77" s="5" t="inlineStr"/>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>squaream.pt</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -4815,37 +4815,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+      <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Cais 5 (Estoril) (Comercialização)</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Vasco Costa (CEO)</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
-        </is>
-      </c>
+          <t>Gestora de ativos regulada pela CMVM, atua como promotor/gestor para fundos como o Signal Capital Partners</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr"/>
+      <c r="L77" s="5" t="inlineStr"/>
       <c r="M77" s="5" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4854,19 +4842,11 @@
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr"/>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>info@ancora-inv.com</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>ancora-inv.com</t>
-        </is>
-      </c>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -4877,156 +4857,136 @@
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
+          <t>Verde Vale (Em construção)</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr"/>
+      <c r="L78" s="5" t="inlineStr"/>
+      <c r="M78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>VIZTA (ex-Nexity Portugal)</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr"/>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>info@ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J78" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K78" s="5" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Antrix</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>info@antrix.pt</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>antrix.pt</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Arish Capital Partners</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -5036,44 +4996,52 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>900 264 096 (ES)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>info@aedashomes.com</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>arishcapitalpartners.com</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Grândola</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
+        </is>
+      </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Fonte: diarioimobiliario.pt</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
@@ -5081,7 +5049,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5096,12 +5064,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>info@carvoeirobranco.com</t>
+          <t>info@antrix.pt</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -5121,22 +5089,22 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (CEO)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
@@ -5144,7 +5112,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5154,56 +5122,52 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>casais@casais.pt</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+        </is>
+      </c>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5213,52 +5177,52 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
+          <t>Erik de Vlieger (CEO)</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -5266,7 +5230,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5276,60 +5240,56 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 305 490</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
-        </is>
-      </c>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5339,18 +5299,22 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
+          <t>+351 253 461 462</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>geral@castro-group.pt</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5358,25 +5322,29 @@
           <t>Braga</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
+        </is>
+      </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
+          <t>Paulo Castro (CEO)</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
@@ -5384,7 +5352,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>DST Real Estate (Grupo dst)</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5394,52 +5362,60 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>+351 253 307 200</t>
+          <t>+351 234 480 570</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>geral@dstsgps.com</t>
+          <t>info@civilria.pt</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>dstsgps.com</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Museu no centro histórico de Braga (Em construção)</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5449,48 +5425,44 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
+          <t>+351 253 089 932</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
+          <t>Diogo Baptista Antunes (CEO)</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
@@ -5498,7 +5470,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>DST Real Estate (Grupo dst)</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5508,56 +5480,52 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
+          <t>+351 253 307 200</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>geral@garcia.pt</t>
+          <t>geral@dstsgps.com</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>dstsgps.com</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Museu no centro histórico de Braga (Em construção)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
+          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5567,52 +5535,48 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>aca@grupo-aca.com</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
+          <t>Reinaldo Teixeira (Administrador)</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
@@ -5620,7 +5584,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5630,47 +5594,47 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
@@ -5679,7 +5643,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5689,52 +5653,52 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
@@ -5742,7 +5706,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5752,43 +5716,47 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
+          <t>+351 253 685 109</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>acrescentar@grupoacrescentar.pt</t>
+        </is>
+      </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr"/>
@@ -5797,7 +5765,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Hievila – Empreendimentos Imobiliários</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5807,52 +5775,60 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 239 091 692</t>
+          <t>+351 253 105 331</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>hievila@hievila.com</t>
+          <t>geral@arliz.co</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>hievila.com</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Rua da Casa Branca 13</t>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Portela Flats (Quinta da Portela, Coimbra) (Em construção)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Fundada 2008</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5862,52 +5838,52 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>273 332 784 (confirmar)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>iLanga Capital (Ohai Resorts)</t>
+          <t>Hievila – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5917,56 +5893,52 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>+351 262 561 800</t>
+          <t>+351 239 091 692</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>info.nazare@ohairesorts.com</t>
+          <t>hievila@hievila.com</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>ohairesorts.com</t>
+          <t>hievila.com</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Nazaré</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Entrada Nacional 242 Km 31.5, 2450-138</t>
+          <t>Rua da Casa Branca 13</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Ohai Peniche (Em construção) | Ohai Nazaré (Concluído/Operação)</t>
+          <t>Portela Flats (Quinta da Portela, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Grupo espanhol de Pelayo Cortina Koplowitz (conde de San Fernando de Peñalver). Tel. alt. 933 089 416</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Pelayo Cortina Koplowitz (fundador)</t>
-        </is>
-      </c>
+          <t>Fundada 2008</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5976,56 +5948,52 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>iLanga Capital (Ohai Resorts)</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -6035,43 +6003,47 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>+351 262 561 800</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>info.nazare@ohairesorts.com</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>ohairesorts.com</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Nazaré</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Entrada Nacional 242 Km 31.5, 2450-138</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Ohai Peniche (Em construção) | Ohai Nazaré (Concluído/Operação)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>Grupo espanhol de Pelayo Cortina Koplowitz (conde de San Fernando de Peñalver). Tel. alt. 933 089 416</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>Pelayo Cortina Koplowitz (fundador)</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr"/>
@@ -6080,7 +6052,7 @@
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -6090,56 +6062,56 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 934 175 642</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>info@pinehill.pt</t>
+          <t>geral@jhomea.pt</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+        </is>
+      </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>José Miguel Afonso (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -6149,60 +6121,52 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>info@quintadolago.com</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Almancil</t>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -6212,52 +6176,56 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Pinheiro (fundador)</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+        </is>
+      </c>
       <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -6267,48 +6235,60 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>+351 289 390 700</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Resort residencial/golfe</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr"/>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -6318,52 +6298,52 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -6373,47 +6353,39 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 939 443 765</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr"/>
@@ -6422,7 +6394,7 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -6432,173 +6404,221 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
+          <t>+351 219 362 960</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>tps.com.pt</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Violas Ferreira (Grupo HVF)</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>+351 227 340 823</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>info@violasferreira.com</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>violasferreira.com</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Espinho</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Rua de Santa Cruz 7, 4500-646</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Edifício Pharmacia (Cedofeita, Porto) (Comercialização) | POP (Porto) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Grupo liderado por Tiago Violas Ferreira</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Tiago Violas Ferreira (líder do grupo)</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
           <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>Fonte: omirante.pt</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr"/>
-      <c r="D106" s="5" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr"/>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H106" s="5" t="inlineStr"/>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="inlineStr"/>
-      <c r="L106" s="5" t="inlineStr"/>
-      <c r="M106" s="5" t="inlineStr"/>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr"/>
-      <c r="D107" s="5" t="inlineStr"/>
-      <c r="E107" s="5" t="inlineStr"/>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa/Grândola/Lagoa</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
-        </is>
-      </c>
-      <c r="M107" s="5" t="inlineStr"/>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Aresta Vitalicia</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr"/>
-      <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr"/>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>WeBuild Castelo (Comercialização)</t>
-        </is>
-      </c>
-      <c r="J108" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K108" s="5" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr"/>
-      <c r="M108" s="5" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6611,7 +6631,7 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -6622,26 +6642,22 @@
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr"/>
       <c r="L109" s="5" t="inlineStr"/>
       <c r="M109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6651,44 +6667,44 @@
       </c>
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
-      <c r="L110" s="5" t="inlineStr"/>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
+        </is>
+      </c>
       <c r="M110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6701,23 +6717,23 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -6727,7 +6743,7 @@
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6740,7 +6756,7 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -6751,22 +6767,26 @@
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
-        </is>
-      </c>
-      <c r="K112" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="L112" s="5" t="inlineStr"/>
       <c r="M112" s="5" t="inlineStr"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6778,38 +6798,42 @@
       <c r="D113" s="5" t="inlineStr"/>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>casasdosotavento.pt</t>
+          <t>baltor.pt</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="inlineStr"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6822,23 +6846,23 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr"/>
@@ -6848,7 +6872,7 @@
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6861,23 +6885,23 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr"/>
@@ -6887,7 +6911,7 @@
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6899,28 +6923,28 @@
       <c r="D116" s="5" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>discoverylandco.com</t>
+          <t>casasdosotavento.pt</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr"/>
@@ -6930,7 +6954,7 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6943,7 +6967,7 @@
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -6954,12 +6978,12 @@
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr"/>
@@ -6969,7 +6993,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -6982,41 +7006,33 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L118" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: diariocoimbra.pt</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr"/>
+      <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -7026,40 +7042,40 @@
       </c>
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: brainsre.news</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr"/>
       <c r="L119" s="5" t="inlineStr"/>
       <c r="M119" s="5" t="inlineStr"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -7072,37 +7088,33 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr"/>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -7112,44 +7124,44 @@
       </c>
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="5" t="inlineStr"/>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -7162,28 +7174,28 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr"/>
@@ -7192,7 +7204,7 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -7205,33 +7217,37 @@
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
+        </is>
+      </c>
       <c r="L123" s="5" t="inlineStr"/>
       <c r="M123" s="5" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7241,36 +7257,44 @@
       </c>
       <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="L124" s="5" t="inlineStr"/>
       <c r="M124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7283,7 +7307,7 @@
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -7294,22 +7318,26 @@
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L125" s="5" t="inlineStr"/>
       <c r="M125" s="5" t="inlineStr"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7319,14 +7347,10 @@
       </c>
       <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
@@ -7337,12 +7361,12 @@
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr"/>
@@ -7352,7 +7376,7 @@
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7362,44 +7386,36 @@
       </c>
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="5" t="inlineStr"/>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr"/>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7409,30 +7425,26 @@
       </c>
       <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="5" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>glowing.pt</t>
-        </is>
-      </c>
+      <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr"/>
@@ -7442,7 +7454,7 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7452,26 +7464,30 @@
       </c>
       <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="5" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>genuinoinvestments.com</t>
+        </is>
+      </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
+          <t>Fonte: genuinoinvestments.com</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr"/>
@@ -7481,7 +7497,7 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7493,25 +7509,33 @@
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="inlineStr"/>
-      <c r="G130" s="7" t="inlineStr"/>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>Faro/Loulé</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr"/>
@@ -7520,7 +7544,7 @@
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7532,23 +7556,23 @@
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>andrejordangroup.pt</t>
+          <t>glowing.pt</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
@@ -7556,18 +7580,14 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K131" s="5" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+      <c r="K131" s="5" t="inlineStr"/>
       <c r="L131" s="5" t="inlineStr"/>
       <c r="M131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7580,7 +7600,7 @@
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -7591,26 +7611,22 @@
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr"/>
       <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7620,44 +7636,36 @@
       </c>
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr"/>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>Oeiras</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr"/>
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L133" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7669,23 +7677,23 @@
       <c r="D134" s="5" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>grupomaisempresas.pt</t>
+          <t>andrejordangroup.pt</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
@@ -7693,14 +7701,18 @@
           <t>Fonte: idealista.pt</t>
         </is>
       </c>
-      <c r="K134" s="5" t="inlineStr"/>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7710,35 +7722,31 @@
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>gruponbportugal.pt</t>
-        </is>
-      </c>
+      <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>Ioav Blanche (presidente)</t>
+          <t>Aníbal Cristina (fundador, 1990)</t>
         </is>
       </c>
       <c r="L135" s="5" t="inlineStr"/>
@@ -7747,7 +7755,7 @@
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7757,44 +7765,44 @@
       </c>
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>pestana.com</t>
-        </is>
-      </c>
+      <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr"/>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M136" s="5" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7806,28 +7814,28 @@
       <c r="D137" s="5" t="inlineStr"/>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr"/>
@@ -7837,7 +7845,7 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7849,38 +7857,42 @@
       <c r="D138" s="5" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr"/>
+          <t>Fonte: gruponb.pt</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7890,36 +7902,44 @@
       </c>
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="5" t="inlineStr"/>
-      <c r="E139" s="5" t="inlineStr"/>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>pestana.com</t>
+        </is>
+      </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7931,46 +7951,38 @@
       <c r="D140" s="5" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>jpaiva.pt</t>
+          <t>hillside.pt</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, hillside.pt</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7982,12 +7994,12 @@
       <c r="D141" s="5" t="inlineStr"/>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>leparc.pt</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -7998,12 +8010,12 @@
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr"/>
@@ -8013,7 +8025,7 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -8023,44 +8035,36 @@
       </c>
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>luxpremium.net</t>
-        </is>
-      </c>
+      <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr">
-        <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr"/>
       <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -8070,40 +8074,48 @@
       </c>
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="5" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr"/>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>jpaiva.pt</t>
+        </is>
+      </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
-      <c r="L143" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -8113,26 +8125,30 @@
       </c>
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr"/>
@@ -8142,7 +8158,7 @@
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -8154,33 +8170,33 @@
       <c r="D145" s="5" t="inlineStr"/>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>maveninvest.pt</t>
+          <t>luxpremium.net</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
+          <t>Fonte: luxpremium.net</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Claude Berda (fundador)</t>
         </is>
       </c>
       <c r="L145" s="5" t="inlineStr"/>
@@ -8189,7 +8205,7 @@
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -8199,48 +8215,40 @@
       </c>
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="E146" s="5" t="inlineStr"/>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: oconnormurphy.ie</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr"/>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8253,23 +8261,23 @@
       <c r="E147" s="5" t="inlineStr"/>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr"/>
@@ -8279,7 +8287,7 @@
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8289,31 +8297,35 @@
       </c>
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr"/>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
+          <t>Fonte: maveninvest.pt</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
+          <t>Yehonatan Gourvitch (CEO)</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr"/>
@@ -8322,7 +8334,7 @@
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8334,38 +8346,46 @@
       <c r="D149" s="5" t="inlineStr"/>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>oconnormurphy.ie</t>
+          <t>mellordc.pt</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
-        </is>
-      </c>
-      <c r="K149" s="5" t="inlineStr"/>
-      <c r="L149" s="5" t="inlineStr"/>
+          <t>Fonte: vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M149" s="5" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8375,14 +8395,10 @@
       </c>
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="5" t="inlineStr"/>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>ombria.com</t>
-        </is>
-      </c>
+      <c r="E150" s="5" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -8390,37 +8406,25 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H150" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+      <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L150" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Fonte: ireland-portugal.com</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr"/>
+      <c r="L150" s="5" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8433,33 +8437,37 @@
       <c r="E151" s="5" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr"/>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
       <c r="L151" s="5" t="inlineStr"/>
       <c r="M151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8469,40 +8477,40 @@
       </c>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr"/>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
-        </is>
-      </c>
-      <c r="K152" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr"/>
       <c r="M152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8512,36 +8520,52 @@
       </c>
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr"/>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K153" s="5" t="inlineStr"/>
-      <c r="L153" s="5" t="inlineStr"/>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M153" s="5" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8554,23 +8578,23 @@
       <c r="E154" s="5" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr"/>
@@ -8580,7 +8604,7 @@
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8593,28 +8617,28 @@
       <c r="E155" s="5" t="inlineStr"/>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
         <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
         </is>
       </c>
       <c r="L155" s="5" t="inlineStr"/>
@@ -8623,7 +8647,7 @@
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -8633,44 +8657,36 @@
       </c>
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="5" t="inlineStr"/>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E156" s="5" t="inlineStr"/>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
-        </is>
-      </c>
-      <c r="K156" s="5" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr"/>
       <c r="L156" s="5" t="inlineStr"/>
       <c r="M156" s="5" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -8680,14 +8696,10 @@
       </c>
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="5" t="inlineStr"/>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>soccal-vaz.com</t>
-        </is>
-      </c>
+      <c r="E157" s="5" t="inlineStr"/>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
@@ -8698,30 +8710,22 @@
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
-        </is>
-      </c>
-      <c r="K157" s="5" t="inlineStr">
-        <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L157" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr"/>
+      <c r="L157" s="5" t="inlineStr"/>
       <c r="M157" s="5" t="inlineStr"/>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -8731,48 +8735,40 @@
       </c>
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="5" t="inlineStr"/>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>solidsentinel.pt</t>
-        </is>
-      </c>
+      <c r="E158" s="5" t="inlineStr"/>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
-        </is>
-      </c>
-      <c r="L158" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
-        </is>
-      </c>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
+      <c r="L158" s="5" t="inlineStr"/>
       <c r="M158" s="5" t="inlineStr"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -8782,36 +8778,44 @@
       </c>
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="5" t="inlineStr"/>
-      <c r="E159" s="5" t="inlineStr"/>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>rodriguesevermelho.com</t>
+        </is>
+      </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K159" s="5" t="inlineStr"/>
+          <t>Fonte: sava.pt, thepreplan.com</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
       <c r="L159" s="5" t="inlineStr"/>
       <c r="M159" s="5" t="inlineStr"/>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -8823,38 +8827,38 @@
       <c r="D160" s="5" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>soccal-vaz.com</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
+          <t>Fonte: eco.sapo.pt</t>
         </is>
       </c>
       <c r="K160" s="5" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
+          <t>António Vaz (fundador e CEO)</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr"/>
@@ -8862,7 +8866,7 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -8874,12 +8878,12 @@
       <c r="D161" s="5" t="inlineStr"/>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>southshoreinvest.com</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
@@ -8890,22 +8894,30 @@
       <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
-        </is>
-      </c>
-      <c r="K161" s="5" t="inlineStr"/>
-      <c r="L161" s="5" t="inlineStr"/>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="inlineStr">
+        <is>
+          <t>Alain Gross (Co-Founder e CEO)</t>
+        </is>
+      </c>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
+        </is>
+      </c>
       <c r="M161" s="5" t="inlineStr"/>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -8915,48 +8927,36 @@
       </c>
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="5" t="inlineStr"/>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>squareview.pt</t>
-        </is>
-      </c>
+      <c r="E162" s="5" t="inlineStr"/>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
-        </is>
-      </c>
-      <c r="K162" s="5" t="inlineStr">
-        <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
-        </is>
-      </c>
-      <c r="L162" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
-        </is>
-      </c>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr"/>
+      <c r="L162" s="5" t="inlineStr"/>
       <c r="M162" s="5" t="inlineStr"/>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -8966,36 +8966,48 @@
       </c>
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="5" t="inlineStr"/>
-      <c r="E163" s="5" t="inlineStr"/>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>sonaesierra.com</t>
+        </is>
+      </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K163" s="5" t="inlineStr"/>
-      <c r="L163" s="5" t="inlineStr"/>
+          <t>Fonte: rtp.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
+        </is>
+      </c>
+      <c r="L163" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+        </is>
+      </c>
       <c r="M163" s="5" t="inlineStr"/>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -9007,28 +9019,28 @@
       <c r="D164" s="5" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>valentavillas.com</t>
+          <t>southshoreinvest.com</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
+          <t>Fonte: southshoreinvest.com</t>
         </is>
       </c>
       <c r="K164" s="5" t="inlineStr"/>
@@ -9038,7 +9050,7 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -9048,36 +9060,48 @@
       </c>
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="5" t="inlineStr"/>
-      <c r="E165" s="5" t="inlineStr"/>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>squareview.pt</t>
+        </is>
+      </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K165" s="5" t="inlineStr"/>
-      <c r="L165" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
+      <c r="L165" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+        </is>
+      </c>
       <c r="M165" s="5" t="inlineStr"/>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -9087,14 +9111,10 @@
       </c>
       <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="5" t="inlineStr"/>
-      <c r="E166" s="5" t="inlineStr">
-        <is>
-          <t>ugp.ie</t>
-        </is>
-      </c>
+      <c r="E166" s="5" t="inlineStr"/>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
@@ -9105,26 +9125,22 @@
       <c r="H166" s="5" t="inlineStr"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K166" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Fonte: racius.com, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="inlineStr"/>
       <c r="L166" s="5" t="inlineStr"/>
       <c r="M166" s="5" t="inlineStr"/>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Urban Office</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -9136,32 +9152,28 @@
       <c r="D167" s="5" t="inlineStr"/>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>urbanoffice.pt</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Torres Vedras</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr">
-        <is>
-          <t>Rua Paiva de Andrade 6A, 2560-357</t>
-        </is>
-      </c>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Torres Prime (Torres Vedras) (Em construção)</t>
+          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
         </is>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Do Grupo Riberalves (&gt;30 anos de história). Nota: site autodenomina-se promotora, mas core histórico é mediação imobiliária</t>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr"/>
@@ -9171,7 +9183,7 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -9181,34 +9193,26 @@
       </c>
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="5" t="inlineStr"/>
-      <c r="E168" s="5" t="inlineStr">
-        <is>
-          <t>valedolobo.com</t>
-        </is>
-      </c>
+      <c r="E168" s="5" t="inlineStr"/>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="inlineStr">
-        <is>
-          <t>Parque do Golfe</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K168" s="5" t="inlineStr"/>
@@ -9218,7 +9222,7 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -9230,33 +9234,174 @@
       <c r="D169" s="5" t="inlineStr"/>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>vilagale.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>The Shipyard (Comercialização)</t>
         </is>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K169" s="5" t="inlineStr"/>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L169" s="5" t="inlineStr"/>
       <c r="M169" s="5" t="inlineStr"/>
+    </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>Urban Office</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr"/>
+      <c r="D170" s="5" t="inlineStr"/>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>urbanoffice.pt</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>Torres Vedras</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>Rua Paiva de Andrade 6A, 2560-357</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr">
+        <is>
+          <t>Torres Prime (Torres Vedras) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="inlineStr">
+        <is>
+          <t>Do Grupo Riberalves (&gt;30 anos de história). Nota: site autodenomina-se promotora, mas core histórico é mediação imobiliária</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="inlineStr"/>
+      <c r="L170" s="5" t="inlineStr"/>
+      <c r="M170" s="5" t="inlineStr"/>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr"/>
+      <c r="D171" s="5" t="inlineStr"/>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>Parque do Golfe</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="inlineStr"/>
+      <c r="L171" s="5" t="inlineStr"/>
+      <c r="M171" s="5" t="inlineStr"/>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr"/>
+      <c r="D172" s="5" t="inlineStr"/>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr"/>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="inlineStr"/>
+      <c r="L172" s="5" t="inlineStr"/>
+      <c r="M172" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9298,7 +9443,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3">
@@ -9308,7 +9453,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
@@ -9318,7 +9463,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -9328,7 +9473,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -9338,7 +9483,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">

--- a/Promotoras_Imobiliarias_Contactos.xlsx
+++ b/Promotoras_Imobiliarias_Contactos.xlsx
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M172" headerRowCount="1">
-  <autoFilter ref="A1:M172"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Promotoras" displayName="Promotoras" ref="A1:M174" headerRowCount="1">
+  <autoFilter ref="A1:M174"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nome da Empresa"/>
     <tableColumn id="2" name="Prioritario"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Lisboa / Porto / Algarve (Comercialização)</t>
+          <t>Lisboa / Porto / Algarve (Comercialização) | Horizon Ocean Gardens (Praia do Forte Novo, Quarteira) (Comercialização)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Cravel (V.N. Gaia) (Comercialização)</t>
+          <t>Quinta de Cravel (V.N. Gaia) (Comercialização) | Fábrica 1921 (Concluído)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Hines Portugal</t>
+          <t>Groundfloor – Premium Investments</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4219,7 +4219,7 @@
       <c r="D64" s="5" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>hines.com</t>
+          <t>theartt.pt</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -4232,33 +4232,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
+      <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
+          <t>The Artt (Campolide) (Comercialização)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Gestora global · sem contacto PT publicado</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
-        </is>
-      </c>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr"/>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Imolote</t>
+          <t>Hines Portugal</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -4270,33 +4262,37 @@
       <c r="D65" s="5" t="inlineStr"/>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>imolote.pt</t>
+          <t>hines.com</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
+          <t>Residência de estudantes Paranhos (Porto) (Em construção) | Castilho 3 (Lisboa) (Em construção)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
+          <t>Gestora global · sem contacto PT publicado</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
+          <t>Vanessa Gelado (Senior Managing Director, Head of Southern Europe)</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr"/>
@@ -4305,7 +4301,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
+          <t>Imolote</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -4315,7 +4311,11 @@
       </c>
       <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>imolote.pt</t>
+        </is>
+      </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
@@ -4329,17 +4329,17 @@
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
+          <t>Monte da Virgem Flats (V.N. Gaia) (Em construção) | 21 projetos entregues (Concluído)</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Co-promoção com investidores · CEO Paulo Vaz Ferreira</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+          <t>Paulo Vaz Ferreira (sócio e CEO desde 2019, confiança moderada)</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>KKR Imo, S.A.</t>
+          <t>JCKL Portugal – Investimentos Imobiliários</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4372,26 +4372,22 @@
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
+          <t>Quarteirão do Rossio (Praça D. Pedro IV/Praça da Figueira) (Concluído/Comercialização)</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
-        </is>
-      </c>
+          <t>100% detido por Global Family Office internacional. Sem telefone confirmado</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Neptune Developments</t>
+          <t>João Magalhães &amp; Alexandre Magalhães (promotores individuais)</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -4401,40 +4397,40 @@
       </c>
       <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>neptune-developments.com</t>
-        </is>
-      </c>
+      <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>BellaMary (Cascais) (Comercialização)</t>
+          <t>Bonjardim 362 (Em construção (conclusão 4T2026))</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr"/>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>João Magalhães e Alexandre Magalhães (promotores individuais)</t>
+        </is>
+      </c>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Onyria Group</t>
+          <t>KKR Imo, S.A.</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4444,14 +4440,10 @@
       </c>
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>onyriagroup.com</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Cascais</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -4462,17 +4454,17 @@
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Onyria Quinta da Marinha Residences (Cascais) (Comercialização)</t>
+          <t>Smart Studios (Janelas Verdes) (Comercialização/Operação)</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Grupo hoteleiro+imobiliário fundado 1986 por José Carlos Pinto Coelho</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+          <t>Vera Kendall (administradora, dados de 2018 · confiança baixa)</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr"/>
@@ -4481,7 +4473,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Portaviv</t>
+          <t>Neptune Developments</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4491,40 +4483,40 @@
       </c>
       <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>neptune-developments.com</t>
+        </is>
+      </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
+          <t>BellaMary (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>Nuno Cunha (Managing Director)</t>
-        </is>
-      </c>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr"/>
       <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>REABILITA</t>
+          <t>Onyria Group</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4536,12 +4528,12 @@
       <c r="D71" s="5" t="inlineStr"/>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>reabilita.pt</t>
+          <t>onyriagroup.com</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cascais</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -4549,29 +4541,29 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Rua do Instituto Industrial nº18, 2º Esq, 1200-225</t>
-        </is>
-      </c>
+      <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Mouzinho da Silveira 21 (Av. Liberdade) (Comercialização) | São Vicente 68 (Alfama) (Comercialização) | Almirante Reis 246 (Areeiro) (Comercialização)</t>
+          <t>Onyria Quinta da Marinha Residences (Cascais) (Comercialização)</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Promoção imobiliária em Lisboa e Cascais desde 2007 (reabilitação urbana + obra nova)</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="inlineStr"/>
+          <t>Grupo hoteleiro+imobiliário fundado 1986 por José Carlos Pinto Coelho</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>José Carlos Pinto Coelho (fundador, 1986)</t>
+        </is>
+      </c>
       <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>REDASSET</t>
+          <t>Portaviv</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -4584,33 +4576,37 @@
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Amadora</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
+          <t>The Factory Residences Campanhã (Em carteira/comercialização)</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr"/>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Nuno Cunha (Managing Director)</t>
+        </is>
+      </c>
       <c r="L72" s="5" t="inlineStr"/>
       <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>RM Promo (JV M2O Group / RJB Home)</t>
+          <t>REABILITA</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -4620,26 +4616,34 @@
       </c>
       <c r="C73" s="7" t="inlineStr"/>
       <c r="D73" s="5" t="inlineStr"/>
-      <c r="E73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>reabilita.pt</t>
+        </is>
+      </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Matosinhos</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Rua do Instituto Industrial nº18, 2º Esq, 1200-225</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>RM Villas (Início obra 1T2026)</t>
+          <t>Mouzinho da Silveira 21 (Av. Liberdade) (Comercialização) | São Vicente 68 (Alfama) (Comercialização) | Almirante Reis 246 (Areeiro) (Comercialização)</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Promoção imobiliária em Lisboa e Cascais desde 2007 (reabilitação urbana + obra nova)</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr"/>
@@ -4649,7 +4653,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Selicomi Portugal (Victoria Group)</t>
+          <t>REDASSET</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -4662,7 +4666,7 @@
       <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Amadora</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -4670,19 +4674,15 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>Rua Camilo Castelo Branco 46, 1250</t>
-        </is>
-      </c>
+      <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>CCB46 (Marquês de Pombal/Av. Liberdade) (Comercialização)</t>
+          <t>Moinho do Guizo (Mina de Água, Amadora) (Planeamento)</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Adquirido em 2014 pela Selicomi Portugal ao Victoria Group. Ativo de escritórios, não residencial</t>
+          <t>Promotor privado em terreno próprio, comercialização sob termos legais definidos</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr"/>
@@ -4692,7 +4692,7 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
+          <t>RM Promo (JV M2O Group / RJB Home)</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -4702,34 +4702,26 @@
       </c>
       <c r="C75" s="7" t="inlineStr"/>
       <c r="D75" s="5" t="inlineStr"/>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>altadelisboa.com</t>
-        </is>
-      </c>
+      <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Matosinhos</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>Rua Manuel Marques 10D, 1º, 1750-171</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Alta de Lisboa (Lumiar) (Em construção/Comercialização)</t>
+          <t>RM Villas (Início obra 1T2026)</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>NIF 501450831. Capital social €0 (SPV de parceria público-privada, sem capital de risco próprio)</t>
+          <t>Fonte: construir.pt</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr"/>
@@ -4739,7 +4731,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Shalu Investments</t>
+          <t>Selicomi Portugal (Victoria Group)</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -4749,48 +4741,40 @@
       </c>
       <c r="C76" s="7" t="inlineStr"/>
       <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>shaluinvest.pt</t>
-        </is>
-      </c>
+      <c r="E76" s="5" t="inlineStr"/>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>Rua Marechal Saldanha 697</t>
+          <t>Rua Camilo Castelo Branco 46, 1250</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
+          <t>CCB46 (Marquês de Pombal/Av. Liberdade) (Comercialização)</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Fundador e Managing Director: Itai Fridman</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>Itai Fridman (Founder &amp; Managing Director)</t>
-        </is>
-      </c>
+          <t>Adquirido em 2014 pela Selicomi Portugal ao Victoria Group. Ativo de escritórios, não residencial</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr"/>
       <c r="L76" s="5" t="inlineStr"/>
       <c r="M76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Square Asset Management</t>
+          <t>SGAL – Sociedade Gestora da Alta de Lisboa</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -4802,7 +4786,7 @@
       <c r="D77" s="5" t="inlineStr"/>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>squaream.pt</t>
+          <t>altadelisboa.com</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -4815,15 +4799,19 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Rua Manuel Marques 10D, 1º, 1750-171</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Cais 5 (Estoril) (Comercialização)</t>
+          <t>Alta de Lisboa (Lumiar) (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Gestora de ativos regulada pela CMVM, atua como promotor/gestor para fundos como o Signal Capital Partners</t>
+          <t>NIF 501450831. Capital social €0 (SPV de parceria público-privada, sem capital de risco próprio)</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr"/>
@@ -4833,7 +4821,7 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Taga Urbanic</t>
+          <t>Shalu Investments</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4843,10 +4831,14 @@
       </c>
       <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>shaluinvest.pt</t>
+        </is>
+      </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -4854,25 +4846,33 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Rua Marechal Saldanha 697</t>
+        </is>
+      </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Verde Vale (Em construção)</t>
+          <t>Portefólio residencial Grande Porto (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>Fonte: imobiliario.publico.pt</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr"/>
+          <t>Fundador e Managing Director: Itai Fridman</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Itai Fridman (Founder &amp; Managing Director)</t>
+        </is>
+      </c>
       <c r="L78" s="5" t="inlineStr"/>
       <c r="M78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>VIZTA (ex-Nexity Portugal)</t>
+          <t>Square Asset Management</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -4881,14 +4881,10 @@
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr"/>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>privacidade@vizta.pt</t>
-        </is>
-      </c>
+      <c r="D79" s="5" t="inlineStr"/>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>vizta.pt</t>
+          <t>squaream.pt</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -4901,37 +4897,25 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
-        </is>
-      </c>
+      <c r="H79" s="5" t="inlineStr"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+          <t>Cais 5 (Estoril) (Comercialização)</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Vasco Costa (CEO)</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
-        </is>
-      </c>
+          <t>Gestora de ativos regulada pela CMVM, atua como promotor/gestor para fundos como o Signal Capital Partners</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr"/>
+      <c r="L79" s="5" t="inlineStr"/>
       <c r="M79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Âncora Investments</t>
+          <t>Taga Urbanic</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -4940,19 +4924,11 @@
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr"/>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>info@ancora-inv.com</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>ancora-inv.com</t>
-        </is>
-      </c>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -4963,156 +4939,136 @@
       <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
+          <t>Verde Vale (Em construção)</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: imobiliario.publico.pt</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>VIZTA (ex-Nexity Portugal)</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>privacidade@vizta.pt</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>vizta.pt</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Ed. Amoreiras Plaza, Rua Carlos Alberto da Mota Pinto 9, piso 4, Esc. 4B2, 1070-374</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Flower Tower Aurora (Leça da Palmeira) (Em construção) | Lisboa Oriental (Olivais/Portela) (Planeamento) | Turquesa (Oeiras) (Concluído)</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Adquirida pela Orion em 2023. Formulário em vizta.pt/contactos</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Vasco Costa (CEO)</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-vasco-costa/</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Âncora Investments</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr"/>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>info@ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>ancora-inv.com</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
           <t>Canelas (V.N. Gaia) + Águas Santas (Maia), com PMA (Planeamento)</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar / Tamir Luria · &gt;70M€ sob gestão</t>
         </is>
       </c>
-      <c r="K80" s="5" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>Elad Shachar e Tamir Luria (co-líderes/investidores)</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamir-luria/</t>
         </is>
       </c>
-      <c r="M80" s="5" t="inlineStr"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>AEDAS Homes + LandCo (Ribamar)</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>900 264 096 (ES)</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>info@aedashomes.com</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>ribamarportimao.com</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>Portimão</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>Ribamar (Praia da Rocha) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Antrix</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>+351 917 498 714</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>info@antrix.pt</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>antrix.pt</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Lagoa</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Arish Capital Partners</t>
+          <t>AEDAS Homes + LandCo (Ribamar)</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5122,44 +5078,52 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
+          <t>900 264 096 (ES)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>info@aedashomes.com</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>arishcapitalpartners.com</t>
+          <t>ribamarportimao.com</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Grândola</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Loja de vendas: Rua dos Três Castelos, Praia da Rocha</t>
+        </is>
+      </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
+          <t>Ribamar (Praia da Rocha) (Em construção)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Fonte: diarioimobiliario.pt</t>
+          <t>Número é linha gratuita espanhola · loja de vendas aberta seg-sáb</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+          <t>José Ignacio Fernández (AEDAS Homes PT) / Javier M. Prieto Ruiz (Diretor Promoção, LandCo)</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+          <t>https://www.linkedin.com/in/javier-m-prieto-ruiz-583b9227/</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
@@ -5167,7 +5131,7 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Branco – Propriedades</t>
+          <t>Antrix</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5182,12 +5146,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>info@carvoeirobranco.com</t>
+          <t>info@antrix.pt</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>carvoeirobranco.com</t>
+          <t>antrix.pt</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -5207,22 +5171,22 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
+          <t>Algarve (vários projetos) (Em construção) | Lisboa, Montijo, Setúbal (Planeamento)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
+          <t>Mesmo CEO (Erik de Vlieger) e mesmo telefone da Carvoeiro Branco</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Erik de Vlieger (CEO)</t>
+          <t>Erik de Vlieger (President, mesmo grupo da Carvoeiro Branco)</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
+          <t>https://www.linkedin.com/in/erik-de-vlieger-12a06a181/</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -5230,7 +5194,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Casais Imobiliária (Grupo Casais)</t>
+          <t>Arish Capital Partners</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5240,56 +5204,52 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>+351 253 305 490</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>casais@casais.pt</t>
-        </is>
-      </c>
+          <t>+971 4 879 0718 (Dubai· escritório Lisboa)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>casais.pt</t>
+          <t>arishcapitalpartners.com</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Grândola</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
+          <t>Sun House Comporta Country (Comercialização (últimas unidades))</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
+          <t>Fonte: diarioimobiliario.pt</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr"/>
+          <t>Rosalía Torres Ruiz-Olivares (Co-founder)</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/rosal%C3%ADa-torres-ruiz-olivares-51702725</t>
+        </is>
+      </c>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Castro Group</t>
+          <t>Carvoeiro Branco – Propriedades</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5299,52 +5259,52 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>+351 253 461 462</t>
+          <t>+351 917 498 714</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>geral@castro-group.pt</t>
+          <t>info@carvoeirobranco.com</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>castro-group.pt</t>
+          <t>carvoeirobranco.com</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Av. 31 de Janeiro 307, 4715-052</t>
+          <t>Rua Jacinto Correia, Bloco A, Loja JLM, Ed. Atrium Lagoa, 8400-398</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Promoção + construção + gestão de ativos (Em construção)</t>
+          <t>JV com TPS (Lagoa, Portimão, Faro) (Planeamento) | Arade Premium Village / Primelife / The Court (Em construção)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>50 anos de história. Fonte: APPII</t>
+          <t>NIF 507849183. Tel. alternativo 960 280 640</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Paulo Castro (CEO)</t>
+          <t>Erik de Vlieger (CEO)</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
+          <t>https://pt.linkedin.com/in/erik-de-vlieger-12a06a181</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
@@ -5352,7 +5312,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Civilria</t>
+          <t>Casais Imobiliária (Grupo Casais)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5362,60 +5322,56 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>+351 234 480 570</t>
+          <t>+351 253 305 490</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>info@civilria.pt</t>
+          <t>casais@casais.pt</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>civilria.pt</t>
+          <t>casais.pt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
+          <t>Rua do Anjo 27, Mire de Tibães, 4700-565</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Portefólio Aveiro (Em construção)</t>
+          <t>MITH – Minho Innovation and Technology Hub (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+          <t>Capital social 5M€, NIF 505271915. Grupo de construção top-5 nacional</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Artur Varum (CEO)</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
-        </is>
-      </c>
+          <t>António Carlos Rodrigues (CEO do Grupo Casais, não específico da divisão imobiliária)</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Dipe Real Estate</t>
+          <t>Castro Group</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5425,18 +5381,22 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>+351 253 089 932</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
+          <t>+351 253 461 462</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>geral@castro-group.pt</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>dipe.pt</t>
+          <t>castro-group.pt</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -5444,25 +5404,29 @@
           <t>Braga</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Av. 31 de Janeiro 307, 4715-052</t>
+        </is>
+      </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Legacy Pure Design (Concluído (fim 2025))</t>
+          <t>Promoção + construção + gestão de ativos (Em construção)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>50 anos de história. Fonte: APPII</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Diogo Baptista Antunes (CEO)</t>
+          <t>Paulo Castro (CEO)</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
+          <t>https://www.linkedin.com/in/paulo-castro-75946a37/</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
@@ -5470,7 +5434,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>DST Real Estate (Grupo dst)</t>
+          <t>Civilria</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5480,52 +5444,60 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>+351 253 307 200</t>
+          <t>+351 234 480 570</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>geral@dstsgps.com</t>
+          <t>info@civilria.pt</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>dstsgps.com</t>
+          <t>civilria.pt</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
+          <t>Rua Cristóvão Pinho Queimado 33, piso 3, Esc. 7, 3800-012</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Museu no centro histórico de Braga (Em construção)</t>
+          <t>Portefólio Aveiro (Em construção)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
+          <t>Promotor vertical (conceção→construção→venda), 25+ anos</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Artur Varum (CEO)</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/artur-varum-63599125</t>
+        </is>
+      </c>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
+          <t>Dipe Real Estate</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5535,48 +5507,44 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>+351 289 381 550</t>
+          <t>+351 253 089 932</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>enolagest.pt</t>
+          <t>dipe.pt</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Greens Vilamoura (Em construção)</t>
+          <t>Legacy Pure Design (Concluído (fim 2025))</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Reinaldo Teixeira (Administrador)</t>
+          <t>Diogo Baptista Antunes (CEO)</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
+          <t>https://pt.linkedin.com/in/diogo-baptista-antunes</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
@@ -5584,7 +5552,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Garcia Garcia</t>
+          <t>DST Real Estate (Grupo dst)</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5594,56 +5562,52 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>+351 253 560 230</t>
+          <t>+351 253 307 200</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>geral@garcia.pt</t>
+          <t>geral@dstsgps.com</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>garcia.pt</t>
+          <t>dstsgps.com</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Santo Tirso</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
+          <t>Rua de Pitancinhos - Palmeira, 4700-727</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
+          <t>Museu no centro histórico de Braga (Em construção)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Design &amp; Build, faturação 173M€ em 2025</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>Miguel Garcia (administrador, confiança moderada)</t>
-        </is>
-      </c>
+          <t>Braço imobiliário do Grupo dst (Domingos da Silva Teixeira)</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
+          <t>Enolagest / Garvetur (Greens Vilamoura)</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5653,52 +5617,48 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>+351 252 308 250</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>aca@grupo-aca.com</t>
-        </is>
-      </c>
+          <t>+351 289 381 550</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>grupo-aca.com</t>
+          <t>enolagest.pt</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Vila Nova de Famalicão</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
+          <t>Rua Melvin Jones, Volta do Gaio, Vilamoura, 8125-406</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
+          <t>Greens Vilamoura (Em construção)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
+          <t>Promotor: Greens Vilamoura Investimentos Imobiliários (grupo Enolagest). Tel. alt. 289 322 488</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Alberto Couto Alves (Presidente/CEO)</t>
+          <t>Reinaldo Teixeira (Administrador)</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
+          <t>https://pt.linkedin.com/in/reinaldo-teixeira-821a3419</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
@@ -5706,7 +5666,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Grupo Acrescentar</t>
+          <t>Garcia Garcia</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5716,47 +5676,47 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>+351 253 685 109</t>
+          <t>+351 253 560 230</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>acrescentar@grupoacrescentar.pt</t>
+          <t>geral@garcia.pt</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>grupoacrescentar.pt</t>
+          <t>garcia.pt</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Santo Tirso</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
+          <t>Rua Comendador António Maria Lopes 15, 4780-424</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
+          <t>Couros Residence (Guimarães) (Concluído) | Arco Living (Santo Tirso) (Concluído) | Residência de estudantes Hines (Porto, Paranhos) (Em construção)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
+          <t>Design &amp; Build, faturação 173M€ em 2025</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ferreira (administrador, confiança moderada)</t>
+          <t>Miguel Garcia (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr"/>
@@ -5765,7 +5725,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Grupo Arliz</t>
+          <t>Grupo ACA / ACA Real Estate (marca Pousio)</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5775,52 +5735,52 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>+351 253 105 331</t>
+          <t>+351 252 308 250</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>geral@arliz.co</t>
+          <t>aca@grupo-aca.com</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>grupoarliz.pt</t>
+          <t>grupo-aca.com</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
+          <t>Vila Nova de Famalicão</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
           <t>Braga</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Parque Industrial de Celeirós 2ª fase</t>
+          <t>Av. dos Descobrimentos, Ed. Las Vegas 3, nº63</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Arc Living (Porto) (Em construção)</t>
+          <t>Pousio (Aveiro, Gaia, Lisboa) (Planeamento)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+          <t>Grupo de construção com 2.000 colaboradores. Fonte: Jornal de Negócios</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Domingos Correia (CEO)</t>
+          <t>Alberto Couto Alves (Presidente/CEO)</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+          <t>https://www.linkedin.com/in/alberto-couto-alves-000343125/</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
@@ -5828,7 +5788,7 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Grupo CVM (Construções Vila Maior)</t>
+          <t>Grupo Acrescentar</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5838,43 +5798,47 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>273 332 784 (confirmar)</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
+          <t>+351 253 685 109</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>acrescentar@grupoacrescentar.pt</t>
+        </is>
+      </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>cvmnet.com</t>
+          <t>grupoacrescentar.pt</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Santa Maria da Feira</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Parque Empresarial A32, Vila Maior</t>
+          <t>Rua Quinta dos Lagos 24, 4700-289 Real</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
+          <t>Green Terrace Porto (Requesende) (Em construção) | Garden Palace (Comercialização) | Strata Private Residence (Comercialização) | Vess Living (Guimarães) (Em construção)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
+          <t>Promove, constrói e vende os próprios projetos. Fonte: diarioimobiliario.pt, idealista/news</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+          <t>Pedro Ferreira (administrador, confiança moderada)</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr"/>
@@ -5883,7 +5847,7 @@
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Hievila – Empreendimentos Imobiliários</t>
+          <t>Grupo Arliz</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5893,52 +5857,60 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>+351 239 091 692</t>
+          <t>+351 253 105 331</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>hievila@hievila.com</t>
+          <t>geral@arliz.co</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>hievila.com</t>
+          <t>grupoarliz.pt</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Rua da Casa Branca 13</t>
+          <t>Parque Industrial de Celeirós 2ª fase</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Portela Flats (Quinta da Portela, Coimbra) (Em construção)</t>
+          <t>Arc Living (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Fundada 2008</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
+          <t>Promotor + construtor. Fonte: idealista/news, construir.pt</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Domingos Correia (CEO)</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domingos-correia-4453ab32/</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>HomeLovers Investment</t>
+          <t>Grupo CVM (Construções Vila Maior)</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5948,52 +5920,52 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>+351 913 470 147</t>
+          <t>273 332 784 (confirmar)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>homelovers.pt</t>
+          <t>cvmnet.com</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santa Maria da Feira</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Parque Empresarial A32, Vila Maior</t>
+        </is>
+      </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Royal Green (V.N. Gaia, Av. Descobrimentos) (Em construção)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Fonte: sapo.pt</t>
+          <t>Telefone vindo do registo — confirmar em cvmnet.com/contactos</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Miguel Tilli (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
-        </is>
-      </c>
+          <t>Severino Ponte (Administração, com Ângelo Marques)</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>iLanga Capital (Ohai Resorts)</t>
+          <t>Hievila – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -6003,56 +5975,52 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>+351 262 561 800</t>
+          <t>+351 239 091 692</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>info.nazare@ohairesorts.com</t>
+          <t>hievila@hievila.com</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>ohairesorts.com</t>
+          <t>hievila.com</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Nazaré</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Entrada Nacional 242 Km 31.5, 2450-138</t>
+          <t>Rua da Casa Branca 13</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Ohai Peniche (Em construção) | Ohai Nazaré (Concluído/Operação)</t>
+          <t>Portela Flats (Quinta da Portela, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Grupo espanhol de Pelayo Cortina Koplowitz (conde de San Fernando de Peñalver). Tel. alt. 933 089 416</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Pelayo Cortina Koplowitz (fundador)</t>
-        </is>
-      </c>
+          <t>Fundada 2008</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>JHOMEA Invest</t>
+          <t>HomeLovers Investment</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -6062,56 +6030,52 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>+351 934 175 642</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>geral@jhomea.pt</t>
-        </is>
-      </c>
+          <t>+351 913 470 147</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>jhomea.pt</t>
+          <t>homelovers.pt</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Vacivus (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
+          <t>Fonte: sapo.pt</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>José Miguel Afonso (CEO/fundador)</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
+          <t>Miguel Tilli (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-tilli-a7a41587/</t>
+        </is>
+      </c>
       <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Metathesis</t>
+          <t>iLanga Capital (Ohai Resorts)</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -6121,43 +6085,47 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>+351 211 650 420</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
+          <t>+351 262 561 800</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>info.nazare@ohairesorts.com</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>metathesis.pt</t>
+          <t>ohairesorts.com</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Nazaré</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>R. Marcos de Assunção nº4A, 2805-290</t>
+          <t>Entrada Nacional 242 Km 31.5, 2450-138</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
+          <t>Ohai Peniche (Em construção) | Ohai Nazaré (Concluído/Operação)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
+          <t>Grupo espanhol de Pelayo Cortina Koplowitz (conde de San Fernando de Peñalver). Tel. alt. 933 089 416</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+          <t>Pelayo Cortina Koplowitz (fundador)</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr"/>
@@ -6166,7 +6134,7 @@
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>JHOMEA Invest</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -6176,56 +6144,56 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>+351 910 936 732</t>
+          <t>+351 934 175 642</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>info@pinehill.pt</t>
+          <t>geral@jhomea.pt</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>pinehill.pt</t>
+          <t>jhomea.pt</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pinho Queimado 56, 3800-012</t>
+        </is>
+      </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
+          <t>Vacivus (Porto) (Em construção)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+          <t>AMI 16355. Escritórios Aveiro (+351 914 444 764) e Lisboa (+351 912 325 143)</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Nuno Pinheiro (fundador)</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
-        </is>
-      </c>
+          <t>José Miguel Afonso (CEO/fundador)</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago Resort</t>
+          <t>Metathesis</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -6235,60 +6203,52 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>+351 289 390 700</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>info@quintadolago.com</t>
-        </is>
-      </c>
+          <t>+351 211 650 420</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>quintadolago.com</t>
+          <t>metathesis.pt</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Almancil</t>
+          <t>R. Marcos de Assunção nº4A, 2805-290</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
+          <t>Reabilitação de imóveis residenciais (Almada) (Em construção)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Resort residencial/golfe</t>
+          <t>Gerente: Maria Elisabete da Fonseca Dionísio Dias. Tel. alt. 967 364 611</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Sean Moriarty (CEO)</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
-        </is>
-      </c>
+          <t>Maria Elisabete da Fonseca Dionísio Dias (gerente)</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Royal Prime</t>
+          <t>Pine Hill</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -6298,52 +6258,56 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>+351 910 181 312</t>
+          <t>+351 910 936 732</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>rgodinho@royalprime.pt</t>
+          <t>info@pinehill.pt</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>royalprime.pt</t>
+          <t>pinehill.pt</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Covilhã</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Castelo Branco</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
-        </is>
-      </c>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Tower Residences (Covilhã) (Concluído)</t>
+          <t>Braga Premium Flats (Comercialização) | 3 novos projetos em Braga (Planeamento)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Contacto comercial Rita Godinho</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
+          <t>Promotora criada em 2025. Fonte: newinbraga.nit.pt, Revista Spot</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Pinheiro (fundador)</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-pinheiro-39968aa4/</t>
+        </is>
+      </c>
       <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Salk Properties Portugal</t>
+          <t>Quinta do Lago Resort</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -6353,48 +6317,60 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>+351 939 443 765</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>+351 289 390 700</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>info@quintadolago.com</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>salkproperties.com</t>
+          <t>quintadolago.com</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
+          <t>Quinta do Lago (real estate do resort) (Comercialização)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Resort residencial/golfe</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
+          <t>Sean Moriarty (CEO)</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/sean-moriarty-6a749133</t>
+        </is>
+      </c>
       <c r="M104" s="2" t="inlineStr"/>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Scale Property Development</t>
+          <t>Royal Prime</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -6404,52 +6380,52 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>+351 219 362 960</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+          <t>+351 910 181 312</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>rgodinho@royalprime.pt</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>scalepropertydevelopment.com</t>
+          <t>royalprime.pt</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Covilhã</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr"/>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>R. Doutor Mário Soares, lote 3, 6200-026</t>
+        </is>
+      </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
+          <t>Tower Residences (Covilhã) (Concluído)</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
-        </is>
-      </c>
+          <t>Contacto comercial Rita Godinho</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TPS – Teixeira, Pinto &amp; Soares</t>
+          <t>Salk Properties Portugal</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -6459,47 +6435,39 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>+351 255 433 572</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>geral@tps.com.pt</t>
-        </is>
-      </c>
+          <t>+351 939 443 765</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>tps.com.pt</t>
+          <t>salkproperties.com</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Alcácer do Sal</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
+          <t>Alcácer Vintage (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
+          <t>João Luís Ferreira (Chairman &amp; Partner)</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr"/>
@@ -6508,7 +6476,7 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Violas Ferreira (Grupo HVF)</t>
+          <t>Scale Property Development</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -6518,56 +6486,52 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>+351 227 340 823</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>info@violasferreira.com</t>
-        </is>
-      </c>
+          <t>+351 219 362 960</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>violasferreira.com</t>
+          <t>scalepropertydevelopment.com</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Espinho</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Aveiro</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Rua de Santa Cruz 7, 4500-646</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Edifício Pharmacia (Cedofeita, Porto) (Comercialização) | POP (Porto) (Em construção)</t>
+          <t>Parque da Cidade – Riverside Living Setúbal (Em construção)</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Grupo liderado por Tiago Violas Ferreira</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Tiago Violas Ferreira (líder do grupo)</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr"/>
+          <t>Diogo Sá Viana Rebelo (Co-Founder)</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-s%C3%A1-viana-rebelo-910104143/</t>
+        </is>
+      </c>
       <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Vomera Group</t>
+          <t>TPS – Teixeira, Pinto &amp; Soares</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -6577,134 +6541,166 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>351 243 078 442</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>+351 255 433 572</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>geral@tps.com.pt</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>vomera.pt</t>
+          <t>tps.com.pt</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Outeiro 677, Z.I. Telões, 4600-758</t>
+        </is>
+      </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+          <t>JV com Carvoeiro Branco (Lagoa, Portimão, Faro) (Planeamento) | One Lush (Caxias) (Em construção)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Fonte: omirante.pt</t>
+          <t>Uma das maiores construtoras nacionais · delegações Lisboa e Algarve</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+          <t>Bruno Fernando Macedo Soares (CEO/Presidente do CA)</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Algarve Property Shops</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Violas Ferreira (Grupo HVF)</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr"/>
-      <c r="D109" s="5" t="inlineStr"/>
-      <c r="E109" s="5" t="inlineStr"/>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Tavira</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr"/>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr"/>
-      <c r="L109" s="5" t="inlineStr"/>
-      <c r="M109" s="5" t="inlineStr"/>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>+351 227 340 823</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>info@violasferreira.com</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>violasferreira.com</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Espinho</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Rua de Santa Cruz 7, 4500-646</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Edifício Pharmacia (Cedofeita, Porto) (Comercialização) | POP (Porto) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Grupo liderado por Tiago Violas Ferreira</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Tiago Violas Ferreira (líder do grupo)</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
     </row>
     <row r="110" ht="30" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>Amorim Luxury</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Vomera Group</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>Nao</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr"/>
-      <c r="D110" s="5" t="inlineStr"/>
-      <c r="E110" s="5" t="inlineStr"/>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa/Grândola/Lagoa</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="inlineStr"/>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
-        </is>
-      </c>
-      <c r="J110" s="5" t="inlineStr">
-        <is>
-          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K110" s="5" t="inlineStr">
-        <is>
-          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
-        </is>
-      </c>
-      <c r="L110" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
-        </is>
-      </c>
-      <c r="M110" s="5" t="inlineStr"/>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>351 243 078 442</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>vomera.pt</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Empreendimento residencial de luxo (nome não divulgado) (Comercialização/Lançamento)</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: omirante.pt</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Sérgio Santos (CEO/fundador, com Delphine Gerardo)</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Aresta Vitalicia</t>
+          <t>Algarve Property Shops</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6717,23 +6713,23 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Varandas de Cabanas (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -6743,7 +6739,7 @@
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Arrow Global Portugal</t>
+          <t>Amorim Luxury</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -6756,37 +6752,41 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Almancil/Quinta do Lago)</t>
+          <t>Lisboa/Grândola/Lagoa</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>The Shore Residences (Comercialização)</t>
+          <t>JNcQUOI House (Av. Liberdade) (Em construção)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+          <t>Fonte: idealista.pt, vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>João Bugalho (CEO)</t>
-        </is>
-      </c>
-      <c r="L112" s="5" t="inlineStr"/>
+          <t>Miguel Guedes de Sousa (Founder &amp; CEO)</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguelguedesdesousa/</t>
+        </is>
+      </c>
       <c r="M112" s="5" t="inlineStr"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Baltor – Engenharia e Construção</t>
+          <t>Aresta Vitalicia</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6796,14 +6796,10 @@
       </c>
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr"/>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>baltor.pt</t>
-        </is>
-      </c>
+      <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Setúbal (sede Viana do Castelo)</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -6814,26 +6810,22 @@
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside III (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ominho.pt</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
-        </is>
-      </c>
+          <t>Fonte: construir.pt</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="inlineStr"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Bond Group</t>
+          <t>Arrow Global Portugal</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6846,33 +6838,37 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Amares</t>
+          <t>Loulé (Almancil/Quinta do Lago)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
+          <t>The Shore Residences (Comercialização)</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr"/>
+          <t>Fonte: idealista.pt, jornaleconomico.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>João Bugalho (CEO)</t>
+        </is>
+      </c>
       <c r="L114" s="5" t="inlineStr"/>
       <c r="M114" s="5" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Branco Real Estate</t>
+          <t>Baltor – Engenharia e Construção</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6882,36 +6878,44 @@
       </c>
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr"/>
-      <c r="E115" s="5" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>baltor.pt</t>
+        </is>
+      </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Setúbal (sede Viana do Castelo)</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Domus (Em construção)</t>
+          <t>Parque da Cidade – Riverside III (Em construção)</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt/empreendimento/35004962</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr"/>
+          <t>Fonte: ominho.pt</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>Paulo Balinha e Bruno Torres (fundadores, 2008)</t>
+        </is>
+      </c>
       <c r="L115" s="5" t="inlineStr"/>
       <c r="M115" s="5" t="inlineStr"/>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Casas do Sotavento</t>
+          <t>Bond Group</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6921,30 +6925,26 @@
       </c>
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr"/>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>casasdosotavento.pt</t>
-        </is>
-      </c>
+      <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Amares</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Boavista Ocean Tavira (Comercialização)</t>
+          <t>José Azevedo Prime Living (Ferreiros, Amares) (Em construção)</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Fonte: boavistaoceantavira.com</t>
+          <t>Grupo imobiliário do Minho. Sem contacto direto confirmado nas fontes</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr"/>
@@ -6954,7 +6954,7 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Confidential Sphere – Investimento Imobiliário</t>
+          <t>Branco Real Estate</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -6967,7 +6967,7 @@
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Silves</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -6978,12 +6978,12 @@
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
+          <t>Domus (Em construção)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Fonte: terraruiva.pt, barlavento.pt</t>
+          <t>Fonte: idealista.pt/empreendimento/35004962</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr"/>
@@ -6993,7 +6993,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>CS Ribeiro</t>
+          <t>Casas do Sotavento</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -7003,26 +7003,30 @@
       </c>
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="5" t="inlineStr"/>
-      <c r="E118" s="5" t="inlineStr"/>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>casasdosotavento.pt</t>
+        </is>
+      </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Guarda (atua Viseu/Coimbra)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
+          <t>Boavista Ocean Tavira (Comercialização)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Fonte: diariocoimbra.pt</t>
+          <t>Fonte: boavistaoceantavira.com</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr"/>
@@ -7032,7 +7036,7 @@
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Discovery Land Company</t>
+          <t>Confidential Sphere – Investimento Imobiliário</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
@@ -7042,30 +7046,26 @@
       </c>
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>discoverylandco.com</t>
-        </is>
-      </c>
+      <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Silves</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
+          <t>Quinta do Pateiro / Silves Hills (Planeamento)</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fonte: brainsre.news</t>
+          <t>Fonte: terraruiva.pt, barlavento.pt</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr"/>
@@ -7075,7 +7075,7 @@
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>DUJA – Sociedade de Construções, Lda</t>
+          <t>CS Ribeiro</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
@@ -7088,23 +7088,23 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Tavira</t>
+          <t>Guarda (atua Viseu/Coimbra)</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Royal Cabanas Beach I e II (Comercialização)</t>
+          <t>The Town Signature (Solum, Coimbra) (Em construção)</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, tavitel.pt</t>
+          <t>Fonte: diariocoimbra.pt</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Emblezart</t>
+          <t>Discovery Land Company</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
@@ -7124,44 +7124,40 @@
       </c>
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="5" t="inlineStr"/>
-      <c r="E121" s="5" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>discoverylandco.com</t>
+        </is>
+      </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Botânico Avenida (Em construção (fase inicial))</t>
+          <t>CostaTerra Golf &amp; Ocean Club (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>David Faria (CEO e sócio único)</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
-        </is>
-      </c>
+          <t>Fonte: brainsre.news</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr"/>
+      <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Encobarra</t>
+          <t>DUJA – Sociedade de Construções, Lda</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
@@ -7174,37 +7170,33 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Aveiro (Aradas)</t>
+          <t>Tavira</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Quinta da Pinheira (Em construção)</t>
+          <t>Royal Cabanas Beach I e II (Comercialização)</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>Aristides Alferes (administrador)</t>
-        </is>
-      </c>
+          <t>Fonte: remax.pt, tavitel.pt</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr"/>
       <c r="L122" s="5" t="inlineStr"/>
       <c r="M122" s="5" t="inlineStr"/>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Estrutural Group</t>
+          <t>Emblezart</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
@@ -7217,37 +7209,41 @@
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Vila Franca de Xira</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Vila Viva (Em construção)</t>
+          <t>Botânico Avenida (Em construção (fase inicial))</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>Hugo Mendes Pinto (Managing Partner)</t>
-        </is>
-      </c>
-      <c r="L123" s="5" t="inlineStr"/>
+          <t>David Faria (CEO e sócio único)</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-faria-a301a466/</t>
+        </is>
+      </c>
       <c r="M123" s="5" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Explorer Investments (Explorer Real Estate)</t>
+          <t>Encobarra</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
@@ -7257,35 +7253,31 @@
       </c>
       <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>explorerinvestments.com</t>
-        </is>
-      </c>
+      <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Aveiro (Aradas)</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
+          <t>Quinta da Pinheira (Em construção)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
+          <t>Fonte: noticiasdeaveiro.pt, terranova.pt</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+          <t>Aristides Alferes (administrador)</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr"/>
@@ -7294,7 +7286,7 @@
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Finangeste, S.A.</t>
+          <t>Estrutural Group</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
@@ -7307,28 +7299,28 @@
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Vila Franca de Xira</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>PUVA (Planeamento/Em construção)</t>
+          <t>Vila Viva (Em construção)</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+          <t>Hugo Mendes Pinto (Managing Partner)</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr"/>
@@ -7337,7 +7329,7 @@
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>FourPromo, Lda (Grupo M2O)</t>
+          <t>Explorer Investments (Explorer Real Estate)</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
@@ -7347,36 +7339,44 @@
       </c>
       <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>explorerinvestments.com</t>
+        </is>
+      </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Vilamoura)</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Rivus (Em construção/Comercialização)</t>
+          <t>CPHP / Penha Longa (Operação/Asset management (desde 2018))</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Fonte: construir.pt, idealista.pt</t>
-        </is>
-      </c>
-      <c r="K126" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth Rothfield (CEO, Founding Partner)</t>
+        </is>
+      </c>
       <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Foz Gala Investments</t>
+          <t>Finangeste, S.A.</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -7389,33 +7389,37 @@
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Figueira da Foz</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
+          <t>PUVA (Planeamento/Em construção)</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, asbeiras.pt</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr"/>
+          <t>Fonte: jornaldenegocios.pt, idealista.pt</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>Paul Henri Schelfhout (Presidente do CA) / Armando Lacerda Queiroz (administrador)</t>
+        </is>
+      </c>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
+          <t>FourPromo, Lda (Grupo M2O)</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
@@ -7428,7 +7432,7 @@
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Loulé (Vilamoura)</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
@@ -7439,12 +7443,12 @@
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Rivus (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+          <t>Fonte: construir.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr"/>
@@ -7454,7 +7458,7 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Genuino Investments</t>
+          <t>Foz Gala Investments</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
@@ -7464,30 +7468,26 @@
       </c>
       <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>genuinoinvestments.com</t>
-        </is>
-      </c>
+      <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Figueira da Foz</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
+          <t>Urbanização antiga fábrica Alberto Gaspar (Planeamento (estudo prévio))</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Fonte: genuinoinvestments.com</t>
+          <t>Fonte: idealista.pt, asbeiras.pt</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr"/>
@@ -7497,7 +7497,7 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
+          <t>Galvana Investimentos Imobiliários e Turísticos, Lda</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -7507,14 +7507,10 @@
       </c>
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>ferreirabuildpower.com</t>
-        </is>
-      </c>
+      <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Faro/Loulé</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
@@ -7525,26 +7521,22 @@
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K130" s="5" t="inlineStr">
-        <is>
-          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
-        </is>
-      </c>
+          <t>Fonte: oconnormurphy.ie, postal.pt</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr"/>
       <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Glowing</t>
+          <t>Genuino Investments</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -7556,28 +7548,28 @@
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>glowing.pt</t>
+          <t>genuinoinvestments.com</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Alcácer do Sal</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>FiniSal (Em construção/Comercialização)</t>
+          <t>Genuíno Resort / Praia da Rocha (Comercialização)</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: genuinoinvestments.com</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr"/>
@@ -7587,7 +7579,7 @@
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Grupo A. Silva &amp; Silva</t>
+          <t>GFH (Grupo Ferreira Holding) / Ferreira Build Power (marca BeLiving)</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -7597,36 +7589,44 @@
       </c>
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>ferreirabuildpower.com</t>
+        </is>
+      </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Seixal</t>
+          <t>Faro/Loulé</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Seixal Baía (Planeamento)</t>
+          <t>BeLiving Faro / BeLiving HCC Loulé (Em construção)</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Fonte: novoperfil.pt</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt, jornaldenegocios.pt</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Silva (CEO Ferreira Build Power)</t>
+        </is>
+      </c>
       <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Guimarães (Portugal)</t>
+          <t>Glowing</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -7638,34 +7638,38 @@
       <c r="D133" s="5" t="inlineStr"/>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>andreguimaraes.com.br</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr"/>
-      <c r="G133" s="7" t="inlineStr"/>
+          <t>glowing.pt</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Alcácer do Sal</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
+          <t>FiniSal (Em construção/Comercialização)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
-        </is>
-      </c>
-      <c r="K133" s="5" t="inlineStr">
-        <is>
-          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr"/>
       <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Grupo André Jordan</t>
+          <t>Grupo A. Silva &amp; Silva</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7675,44 +7679,36 @@
       </c>
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>andrejordangroup.pt</t>
-        </is>
-      </c>
+      <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Seixal</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
+          <t>Seixal Baía (Planeamento)</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
-        </is>
-      </c>
+          <t>Fonte: novoperfil.pt</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr"/>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
+          <t>Grupo André Guimarães (Portugal)</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7722,31 +7718,27 @@
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr"/>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>andreguimaraes.com.br</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr"/>
+      <c r="G135" s="7" t="inlineStr"/>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside IV (Em construção)</t>
+          <t>JV com Overseas (Lisboa) (Planeamento) | Porto, Algarve, Douro, Cascais, Alentejo, Amarante (Em construção)</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+          <t>Entidade PT: André Guimarães - Portugal, Lda (NIF 517865459). Sem contacto PT</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>Aníbal Cristina (fundador, 1990)</t>
+          <t>Fundador falecido· hoje liderado pelos filhos (Brasil), sem responsável PT confirmado</t>
         </is>
       </c>
       <c r="L135" s="5" t="inlineStr"/>
@@ -7755,7 +7747,7 @@
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Grupo Azinor</t>
+          <t>Grupo André Jordan</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7765,10 +7757,14 @@
       </c>
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>andrejordangroup.pt</t>
+        </is>
+      </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -7779,7 +7775,7 @@
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Porto Cruz (Planeamento (consulta pública))</t>
+          <t>Lisbon Green Valley (Belas Clube de Campo) (Em construção)</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
@@ -7789,20 +7785,16 @@
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>Carlos Silva Neves (administrador)</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
-        </is>
-      </c>
+          <t>Gilberto Jordan (CEO desde 2009 · sucede a André Jordan, falecido 2024)</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr"/>
       <c r="M136" s="5" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mais Empresas / Construções Mais</t>
+          <t>Grupo AOC (Aníbal de Oliveira Cristina)</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7812,40 +7804,40 @@
       </c>
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>grupomaisempresas.pt</t>
-        </is>
-      </c>
+      <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Golden Wolf (Em construção)</t>
+          <t>Parque da Cidade – Riverside IV (Em construção)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr"/>
+          <t>Fonte: linkedin.com/company/grupo-aoc</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>Aníbal Cristina (fundador, 1990)</t>
+        </is>
+      </c>
       <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Grupo NB Portugal</t>
+          <t>Grupo Azinor</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
@@ -7855,44 +7847,44 @@
       </c>
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>gruponbportugal.pt</t>
-        </is>
-      </c>
+      <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>NB 2040 / NB Garden (estado não confirmado)</t>
+          <t>Porto Cruz (Planeamento (consulta pública))</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Fonte: gruponb.pt</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
         <is>
-          <t>Ioav Blanche (presidente)</t>
-        </is>
-      </c>
-      <c r="L138" s="5" t="inlineStr"/>
+          <t>Carlos Silva Neves (administrador)</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/carlos-silva-neves-3b0711142</t>
+        </is>
+      </c>
       <c r="M138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Grupo Pestana (Pestana Residences)</t>
+          <t>Grupo Mais Empresas / Construções Mais</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7904,42 +7896,38 @@
       <c r="D139" s="5" t="inlineStr"/>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>pestana.com</t>
+          <t>grupomaisempresas.pt</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Sines/Lagoa</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
+          <t>Golden Wolf (Em construção)</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fonte: publico.pt, construir.pt</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>Dionísio Pestana (Chairman/dono)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr"/>
       <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Hillside House Coimbra, Lda</t>
+          <t>Grupo NB Portugal</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
@@ -7951,12 +7939,12 @@
       <c r="D140" s="5" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>hillside.pt</t>
+          <t>gruponbportugal.pt</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Mealhada (projeto em Coimbra)</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
@@ -7967,22 +7955,26 @@
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
+          <t>NB 2040 / NB Garden (estado não confirmado)</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fonte: remax.pt, hillside.pt</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr"/>
+          <t>Fonte: gruponb.pt</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>Ioav Blanche (presidente)</t>
+        </is>
+      </c>
       <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Iconic Jeunesse, Unipessoal, Lda</t>
+          <t>Grupo Pestana (Pestana Residences)</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -7994,38 +7986,42 @@
       <c r="D141" s="5" t="inlineStr"/>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>zenithresidences.pt</t>
+          <t>pestana.com</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Portimão</t>
+          <t>Sines/Lagoa</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Zenith Residences (Em construção/Planeamento)</t>
+          <t>Pestana Porto Covo Beach Residences (Licenciamento)</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr"/>
+          <t>Fonte: publico.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>Dionísio Pestana (Chairman/dono)</t>
+        </is>
+      </c>
       <c r="L141" s="5" t="inlineStr"/>
       <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Invesquart – Real Estate Promotor</t>
+          <t>Hillside House Coimbra, Lda</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -8035,26 +8031,30 @@
       </c>
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>hillside.pt</t>
+        </is>
+      </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Mealhada (projeto em Coimbra)</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Terraços de Quarteira (Comercialização)</t>
+          <t>Hillside – Areeiro (2ª fase) (Em construção)</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Fonte: facebook.com/TerracosQuarteira</t>
+          <t>Fonte: remax.pt, hillside.pt</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
+          <t>Iconic Jeunesse, Unipessoal, Lda</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
@@ -8076,46 +8076,38 @@
       <c r="D143" s="5" t="inlineStr"/>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>jpaiva.pt</t>
+          <t>zenithresidences.pt</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Portimão</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
+          <t>Zenith Residences (Em construção/Planeamento)</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt</t>
-        </is>
-      </c>
-      <c r="K143" s="5" t="inlineStr">
-        <is>
-          <t>Igor Castro (CEO)</t>
-        </is>
-      </c>
-      <c r="L143" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
-        </is>
-      </c>
+          <t>Fonte: zenithresidences.pt, jamesedition.com</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr"/>
+      <c r="L143" s="5" t="inlineStr"/>
       <c r="M143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Le Parc</t>
+          <t>Invesquart – Real Estate Promotor</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -8125,14 +8117,10 @@
       </c>
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>leparc.pt</t>
-        </is>
-      </c>
+      <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -8143,12 +8131,12 @@
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
+          <t>Terraços de Quarteira (Comercialização)</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+          <t>Fonte: facebook.com/TerracosQuarteira</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr"/>
@@ -8158,7 +8146,7 @@
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Lux Premium</t>
+          <t>JPAIVA Investimentos / JPAIVA Engenharia e Construção</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
@@ -8170,7 +8158,7 @@
       <c r="D145" s="5" t="inlineStr"/>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>luxpremium.net</t>
+          <t>jpaiva.pt</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
@@ -8186,26 +8174,30 @@
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Coimbra Premium (Planeamento)</t>
+          <t>Garden Residence 2 (Antanhol) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Fonte: luxpremium.net</t>
+          <t>Fonte: jpaiva.pt</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>Claude Berda (fundador)</t>
-        </is>
-      </c>
-      <c r="L145" s="5" t="inlineStr"/>
+          <t>Igor Castro (CEO)</t>
+        </is>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-castro-a0026b22b/</t>
+        </is>
+      </c>
       <c r="M145" s="5" t="inlineStr"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>MAJA Construções, S.A.</t>
+          <t>Le Parc</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -8215,10 +8207,14 @@
       </c>
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr"/>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>leparc.pt</t>
+        </is>
+      </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -8229,26 +8225,22 @@
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>Le Parc Faro (Comercialização) | Le Parc Canidelo (V.N. Gaia) (Comercialização)</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fonte: oconnormurphy.ie</t>
-        </is>
-      </c>
-      <c r="K146" s="5" t="inlineStr">
-        <is>
-          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
-        </is>
-      </c>
+          <t>Sem telefone próprio confirmado — número encontrado é da comercializadora JLL</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr"/>
       <c r="L146" s="5" t="inlineStr"/>
       <c r="M146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Mariano Investe – Empreendimentos Imobiliários</t>
+          <t>Lux Premium</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -8258,36 +8250,44 @@
       </c>
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="5" t="inlineStr"/>
-      <c r="E147" s="5" t="inlineStr"/>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>luxpremium.net</t>
+        </is>
+      </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Quinta de São Pedro Valley (Em construção)</t>
+          <t>Coimbra Premium (Planeamento)</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K147" s="5" t="inlineStr"/>
+          <t>Fonte: luxpremium.net</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>Claude Berda (fundador)</t>
+        </is>
+      </c>
       <c r="L147" s="5" t="inlineStr"/>
       <c r="M147" s="5" t="inlineStr"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Maven (Maven Invest)</t>
+          <t>MAJA Construções, S.A.</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -8297,35 +8297,31 @@
       </c>
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>maveninvest.pt</t>
-        </is>
-      </c>
+      <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>WeBuild Castelo (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Fonte: maveninvest.pt</t>
+          <t>Fonte: oconnormurphy.ie</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>Yehonatan Gourvitch (CEO)</t>
+          <t>Manuel António e Jorge Almeida (fundadores, 1972)</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr"/>
@@ -8334,7 +8330,7 @@
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Mello RDC</t>
+          <t>Mariano Investe – Empreendimentos Imobiliários</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -8344,48 +8340,36 @@
       </c>
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>mellordc.pt</t>
-        </is>
-      </c>
+      <c r="E149" s="5" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Grândola (Melides)</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
+          <t>Quinta de São Pedro Valley (Em construção)</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Fonte: vidaimobiliaria.com</t>
-        </is>
-      </c>
-      <c r="K149" s="5" t="inlineStr">
-        <is>
-          <t>António Ribeiro da Cunha (CEO)</t>
-        </is>
-      </c>
-      <c r="L149" s="5" t="inlineStr">
-        <is>
-          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr"/>
+      <c r="L149" s="5" t="inlineStr"/>
       <c r="M149" s="5" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Máscarazul – Mediação Imobiliária, Lda</t>
+          <t>Maven (Maven Invest)</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -8395,36 +8379,44 @@
       </c>
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="5" t="inlineStr"/>
-      <c r="E150" s="5" t="inlineStr"/>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>maveninvest.pt</t>
+        </is>
+      </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Albufeira</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Quinta Dourada (Em construção)</t>
+          <t>WeBuild Castelo (Comercialização)</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ireland-portugal.com</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr"/>
+          <t>Fonte: maveninvest.pt</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>Yehonatan Gourvitch (CEO)</t>
+        </is>
+      </c>
       <c r="L150" s="5" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Nova Atlantic</t>
+          <t>Mello RDC</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -8434,40 +8426,48 @@
       </c>
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="5" t="inlineStr"/>
-      <c r="E151" s="5" t="inlineStr"/>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>mellordc.pt</t>
+        </is>
+      </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Grândola (Melides)</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
+          <t>Projeto hoteleiro em Melides (não divulgado) (Planeamento)</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaleconomico.sapo.pt</t>
+          <t>Fonte: vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>Matan Amitai (co-fundador)</t>
-        </is>
-      </c>
-      <c r="L151" s="5" t="inlineStr"/>
+          <t>António Ribeiro da Cunha (CEO)</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>https://pt.linkedin.com/in/ant%C3%B3nio-ribeiro-da-cunha-77b974112</t>
+        </is>
+      </c>
       <c r="M151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>OCM Portugal (O'Connor Murphy)</t>
+          <t>Máscarazul – Mediação Imobiliária, Lda</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -8477,14 +8477,10 @@
       </c>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="5" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>oconnormurphy.ie</t>
-        </is>
-      </c>
+      <c r="E152" s="5" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Olhão</t>
+          <t>Albufeira</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
@@ -8495,12 +8491,12 @@
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Del Mar Waterfront Living (Comercialização)</t>
+          <t>Quinta Dourada (Em construção)</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jll.pt, delmarliving.pt</t>
+          <t>Fonte: ireland-portugal.com</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr"/>
@@ -8510,7 +8506,7 @@
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Ombria Resort (Grupo Pontos)</t>
+          <t>Nova Atlantic</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -8520,52 +8516,40 @@
       </c>
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="5" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>ombria.com</t>
-        </is>
-      </c>
+      <c r="E153" s="5" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>Loulé</t>
-        </is>
-      </c>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Ombria Algarve (Em construção)</t>
+          <t>GREEN HILLS Viana Residences (Comercialização (arrancou set/2026))</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
+          <t>Fonte: jornaleconomico.sapo.pt</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
-        </is>
-      </c>
-      <c r="L153" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/patricksfreeman/</t>
-        </is>
-      </c>
+          <t>Matan Amitai (co-fundador)</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr"/>
       <c r="M153" s="5" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>PATRIMOINIMMO PORTUGAL</t>
+          <t>OCM Portugal (O'Connor Murphy)</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -8575,10 +8559,14 @@
       </c>
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="5" t="inlineStr"/>
-      <c r="E154" s="5" t="inlineStr"/>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>oconnormurphy.ie</t>
+        </is>
+      </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Olhão</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
@@ -8589,12 +8577,12 @@
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo Hills Residência (Comercialização)</t>
+          <t>Del Mar Waterfront Living (Comercialização)</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Fonte: ferreirabuildpower.com</t>
+          <t>Fonte: jll.pt, delmarliving.pt</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr"/>
@@ -8604,7 +8592,7 @@
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Pelicano – Investimento Imobiliário, S.A.</t>
+          <t>Ombria Resort (Grupo Pontos)</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -8614,40 +8602,52 @@
       </c>
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="5" t="inlineStr"/>
-      <c r="E155" s="5" t="inlineStr"/>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>ombria.com</t>
+        </is>
+      </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Palmela</t>
+          <t>Loulé</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="inlineStr"/>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Palmela Village (Comercialização)</t>
+          <t>Ombria Algarve (Em construção)</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+          <t>Grupo finlandês Pontos · construtor Gabriel Couto</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
         <is>
-          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
-        </is>
-      </c>
-      <c r="L155" s="5" t="inlineStr"/>
+          <t>Patrick Freeman (CEO Ombria desde 2023)· CEO do Grupo Pontos é Timo Kokkila</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricksfreeman/</t>
+        </is>
+      </c>
       <c r="M155" s="5" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Pensaplano</t>
+          <t>PATRIMOINIMMO PORTUGAL</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
@@ -8660,23 +8660,23 @@
       <c r="E156" s="5" t="inlineStr"/>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Eleven (Em construção)</t>
+          <t>Ferragudo Hills Residência (Comercialização)</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt, construir.pt</t>
+          <t>Fonte: ferreirabuildpower.com</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr"/>
@@ -8686,7 +8686,7 @@
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Portugal Slow Living</t>
+          <t>Pelicano – Investimento Imobiliário, S.A.</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -8699,7 +8699,7 @@
       <c r="E157" s="5" t="inlineStr"/>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Montijo</t>
+          <t>Palmela</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
@@ -8710,22 +8710,26 @@
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Monville (Comercialização)</t>
+          <t>Palmela Village (Comercialização)</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
-        </is>
-      </c>
-      <c r="K157" s="5" t="inlineStr"/>
+          <t>Fonte: racius.com, cnnportugal.iol.pt</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>Joaquim Da Cunha Mendes Duarte (Presidente) / Sergio Manuel Mendes Gomes (Administrador)</t>
+        </is>
+      </c>
       <c r="L157" s="5" t="inlineStr"/>
       <c r="M157" s="5" t="inlineStr"/>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Rivage Properties</t>
+          <t>Pensaplano</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
@@ -8738,37 +8742,33 @@
       <c r="E158" s="5" t="inlineStr"/>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Gondomar</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>The View II (Em construção (conclusão 2026))</t>
+          <t>Eleven (Em construção)</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jornaldenegocios.pt</t>
-        </is>
-      </c>
-      <c r="K158" s="5" t="inlineStr">
-        <is>
-          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt, construir.pt</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr"/>
       <c r="L158" s="5" t="inlineStr"/>
       <c r="M158" s="5" t="inlineStr"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
+          <t>Portugal Slow Living</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
@@ -8778,44 +8778,36 @@
       </c>
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="5" t="inlineStr"/>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>rodriguesevermelho.com</t>
-        </is>
-      </c>
+      <c r="E159" s="5" t="inlineStr"/>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Montijo</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Domus (Domus 22 e 23) (Em construção)</t>
+          <t>Monville (Comercialização)</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Fonte: sava.pt, thepreplan.com</t>
-        </is>
-      </c>
-      <c r="K159" s="5" t="inlineStr">
-        <is>
-          <t>Celestino Vermelho Rodrigues (contacto)</t>
-        </is>
-      </c>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr"/>
       <c r="L159" s="5" t="inlineStr"/>
       <c r="M159" s="5" t="inlineStr"/>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Soccal &amp; Vaz Invest</t>
+          <t>Rivage Properties</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -8825,48 +8817,40 @@
       </c>
       <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="5" t="inlineStr"/>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>soccal-vaz.com</t>
-        </is>
-      </c>
+      <c r="E160" s="5" t="inlineStr"/>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Sines</t>
+          <t>Gondomar</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Brisa Mar (Em construção)</t>
+          <t>The View II (Em construção (conclusão 2026))</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Fonte: eco.sapo.pt</t>
+          <t>Fonte: jornaldenegocios.pt</t>
         </is>
       </c>
       <c r="K160" s="5" t="inlineStr">
         <is>
-          <t>António Vaz (fundador e CEO)</t>
-        </is>
-      </c>
-      <c r="L160" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
-        </is>
-      </c>
+          <t>João Ribeiro (CEO e fundador, com Jorge Duarte e Fernando Santos)</t>
+        </is>
+      </c>
+      <c r="L160" s="5" t="inlineStr"/>
       <c r="M160" s="5" t="inlineStr"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Solid Sentinel</t>
+          <t>Rodrigues &amp; Vermelho – Construções, S.A.</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -8878,46 +8862,42 @@
       <c r="D161" s="5" t="inlineStr"/>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>solidsentinel.pt</t>
+          <t>rodriguesevermelho.com</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>NOOBA (Em construção/comercialização)</t>
+          <t>Domus (Domus 22 e 23) (Em construção)</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Fonte: reportugal.vidaimobiliaria.com</t>
+          <t>Fonte: sava.pt, thepreplan.com</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
         <is>
-          <t>Alain Gross (Co-Founder e CEO)</t>
-        </is>
-      </c>
-      <c r="L161" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
-        </is>
-      </c>
+          <t>Celestino Vermelho Rodrigues (contacto)</t>
+        </is>
+      </c>
+      <c r="L161" s="5" t="inlineStr"/>
       <c r="M161" s="5" t="inlineStr"/>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>SOLUM PROGRESS</t>
+          <t>Soccal &amp; Vaz Invest</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -8927,36 +8907,48 @@
       </c>
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="5" t="inlineStr"/>
-      <c r="E162" s="5" t="inlineStr"/>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>soccal-vaz.com</t>
+        </is>
+      </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Sines</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
+          <t>Brisa Mar (Em construção)</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>Fonte: jpaiva.pt, zome.pt</t>
-        </is>
-      </c>
-      <c r="K162" s="5" t="inlineStr"/>
-      <c r="L162" s="5" t="inlineStr"/>
+          <t>Fonte: eco.sapo.pt</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>António Vaz (fundador e CEO)</t>
+        </is>
+      </c>
+      <c r="L162" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-vaz-9444998a/</t>
+        </is>
+      </c>
       <c r="M162" s="5" t="inlineStr"/>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Sonae Sierra</t>
+          <t>Solid Sentinel</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -8968,38 +8960,38 @@
       <c r="D163" s="5" t="inlineStr"/>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>sonaesierra.com</t>
+          <t>solidsentinel.pt</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Porto</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Pulse Lisboa (Em construção)</t>
+          <t>NOOBA (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Fonte: rtp.pt, idealista.pt</t>
+          <t>Fonte: reportugal.vidaimobiliaria.com</t>
         </is>
       </c>
       <c r="K163" s="5" t="inlineStr">
         <is>
-          <t>Fernando Guedes de Oliveira (CEO)</t>
+          <t>Alain Gross (Co-Founder e CEO)</t>
         </is>
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
+          <t>https://www.linkedin.com/in/alain-gross-3351411/</t>
         </is>
       </c>
       <c r="M163" s="5" t="inlineStr"/>
@@ -9007,7 +8999,7 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Southshore Investments</t>
+          <t>SOLUM PROGRESS</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -9017,30 +9009,26 @@
       </c>
       <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="5" t="inlineStr"/>
-      <c r="E164" s="5" t="inlineStr">
-        <is>
-          <t>southshoreinvest.com</t>
-        </is>
-      </c>
+      <c r="E164" s="5" t="inlineStr"/>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Tejo City District (Planeamento)</t>
+          <t>Namora Residence (Solum, Sto. António dos Olivais) (Em construção/comercialização)</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>Fonte: southshoreinvest.com</t>
+          <t>Fonte: jpaiva.pt, zome.pt</t>
         </is>
       </c>
       <c r="K164" s="5" t="inlineStr"/>
@@ -9050,7 +9038,7 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Square View</t>
+          <t>Sonae Sierra</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -9062,38 +9050,38 @@
       <c r="D165" s="5" t="inlineStr"/>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>squareview.pt</t>
+          <t>sonaesierra.com</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Lisboa/Ericeira/Melides</t>
+          <t>Lisboa/Porto</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
+          <t>Pulse Lisboa (Em construção)</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Fonte: squareview.pt</t>
+          <t>Fonte: rtp.pt, idealista.pt</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
         <is>
-          <t>Luis Horta e Costa (CEO/Fundador)</t>
+          <t>Fernando Guedes de Oliveira (CEO)</t>
         </is>
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+          <t>https://pt.linkedin.com/in/fernando-oliveira-9622b817</t>
         </is>
       </c>
       <c r="M165" s="5" t="inlineStr"/>
@@ -9101,7 +9089,7 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Terrace Benefit, Lda</t>
+          <t>Southshore Investments</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -9111,26 +9099,30 @@
       </c>
       <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="5" t="inlineStr"/>
-      <c r="E166" s="5" t="inlineStr"/>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>southshoreinvest.com</t>
+        </is>
+      </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Loulé (Quarteira)</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Forte Novo (Em construção)</t>
+          <t>Tejo City District (Planeamento)</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>Fonte: racius.com, idealista.pt</t>
+          <t>Fonte: southshoreinvest.com</t>
         </is>
       </c>
       <c r="K166" s="5" t="inlineStr"/>
@@ -9140,7 +9132,7 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>The Epic Group</t>
+          <t>Square View</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -9152,38 +9144,46 @@
       <c r="D167" s="5" t="inlineStr"/>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>valentavillas.com</t>
+          <t>squareview.pt</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Ílhavo</t>
+          <t>Lisboa/Ericeira/Melides</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Aveiro</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
+          <t>4 projetos residenciais multifamiliares (nomes não encontrados) (Em desenvolvimento)</t>
         </is>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Sem telefone/CEO confirmados nas fontes</t>
-        </is>
-      </c>
-      <c r="K167" s="5" t="inlineStr"/>
-      <c r="L167" s="5" t="inlineStr"/>
+          <t>Fonte: squareview.pt</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="inlineStr">
+        <is>
+          <t>Luis Horta e Costa (CEO/Fundador)</t>
+        </is>
+      </c>
+      <c r="L167" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-horta-e-costa-377552241/</t>
+        </is>
+      </c>
       <c r="M167" s="5" t="inlineStr"/>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Udra – Grupo San José</t>
+          <t>Terrace Benefit, Lda</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -9196,23 +9196,23 @@
       <c r="E168" s="5" t="inlineStr"/>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Loulé (Quarteira)</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Parque da Cidade – Riverside II (Em construção)</t>
+          <t>Forte Novo (Em construção)</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Fonte: racius.com, idealista.pt</t>
         </is>
       </c>
       <c r="K168" s="5" t="inlineStr"/>
@@ -9222,7 +9222,7 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Urban Green Private (UGP)</t>
+          <t>The Epic Group</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -9234,42 +9234,38 @@
       <c r="D169" s="5" t="inlineStr"/>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>ugp.ie</t>
+          <t>valentavillas.com</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Ílhavo</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Faro</t>
+          <t>Aveiro</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>The Shipyard (Comercialização)</t>
+          <t>Valenta Villas (Ermida, Ílhavo) (Comercialização)</t>
         </is>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Fonte: theshipyard.pt, barlavento.pt</t>
-        </is>
-      </c>
-      <c r="K169" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Coughlan (fundador)</t>
-        </is>
-      </c>
+          <t>Sem telefone/CEO confirmados nas fontes</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="inlineStr"/>
       <c r="L169" s="5" t="inlineStr"/>
       <c r="M169" s="5" t="inlineStr"/>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>Urban Office</t>
+          <t>Udra – Grupo San José</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -9279,34 +9275,26 @@
       </c>
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="5" t="inlineStr"/>
-      <c r="E170" s="5" t="inlineStr">
-        <is>
-          <t>urbanoffice.pt</t>
-        </is>
-      </c>
+      <c r="E170" s="5" t="inlineStr"/>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>Torres Vedras</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="H170" s="5" t="inlineStr">
-        <is>
-          <t>Rua Paiva de Andrade 6A, 2560-357</t>
-        </is>
-      </c>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Torres Prime (Torres Vedras) (Em construção)</t>
+          <t>Parque da Cidade – Riverside II (Em construção)</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>Do Grupo Riberalves (&gt;30 anos de história). Nota: site autodenomina-se promotora, mas core histórico é mediação imobiliária</t>
+          <t>Fonte: idealista.pt</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr"/>
@@ -9316,7 +9304,7 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Vale do Lobo Resort</t>
+          <t>Urban Green Private (UGP)</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -9328,12 +9316,12 @@
       <c r="D171" s="5" t="inlineStr"/>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>valedolobo.com</t>
+          <t>ugp.ie</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Loulé</t>
+          <t>Faro</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
@@ -9341,29 +9329,29 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>Parque do Golfe</t>
-        </is>
-      </c>
+      <c r="H171" s="5" t="inlineStr"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+          <t>The Shipyard (Comercialização)</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
-        </is>
-      </c>
-      <c r="K171" s="5" t="inlineStr"/>
+          <t>Fonte: theshipyard.pt, barlavento.pt</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Coughlan (fundador)</t>
+        </is>
+      </c>
       <c r="L171" s="5" t="inlineStr"/>
       <c r="M171" s="5" t="inlineStr"/>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé</t>
+          <t>Urban Office</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -9375,33 +9363,127 @@
       <c r="D172" s="5" t="inlineStr"/>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>vilagale.com</t>
+          <t>urbanoffice.pt</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Golegã</t>
+          <t>Torres Vedras</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="H172" s="5" t="inlineStr"/>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>Rua Paiva de Andrade 6A, 2560-357</t>
+        </is>
+      </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+          <t>Torres Prime (Torres Vedras) (Em construção)</t>
         </is>
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>Fonte: idealista.pt</t>
+          <t>Do Grupo Riberalves (&gt;30 anos de história). Nota: site autodenomina-se promotora, mas core histórico é mediação imobiliária</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr"/>
       <c r="L172" s="5" t="inlineStr"/>
       <c r="M172" s="5" t="inlineStr"/>
+    </row>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Vale do Lobo Resort</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr"/>
+      <c r="D173" s="5" t="inlineStr"/>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>valedolobo.com</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>Parque do Golfe</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>Vale Real (lotes/moradias em planta) (Planeamento) | Oceano Clube (Comercialização) | The Residences (Comercialização)</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>Adquirido 2022 por fundo assessorado pela Davidson Kempner Capital Management. Promotor/gestor operacional: Kronos Real Estate Group</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="inlineStr"/>
+      <c r="L173" s="5" t="inlineStr"/>
+      <c r="M173" s="5" t="inlineStr"/>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr"/>
+      <c r="D174" s="5" t="inlineStr"/>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>vilagale.com</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>Golegã</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr"/>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>Vila Galé Collection Tejo (Quinta da Cardiga) (Em construção)</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>Fonte: idealista.pt</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="inlineStr"/>
+      <c r="L174" s="5" t="inlineStr"/>
+      <c r="M174" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9443,7 +9525,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
@@ -9463,7 +9545,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -9473,7 +9555,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
